--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t>Vein ID</t>
   </si>
@@ -196,7 +196,7 @@
     <t>vanadium_magnetite: 15</t>
   </si>
   <si>
-    <t>chromite: 60 [1]</t>
+    <t>chromite: 20 [1]</t>
   </si>
   <si>
     <t>gold: 15</t>
@@ -214,9 +214,6 @@
     <t>molybdenite: 30 [1]</t>
   </si>
   <si>
-    <t>molybdenum: 15</t>
-  </si>
-  <si>
     <t>powellite: 15</t>
   </si>
   <si>
@@ -265,10 +262,7 @@
     <t>cooperite: 25 [1]</t>
   </si>
   <si>
-    <t>platinum: 25 [1]</t>
-  </si>
-  <si>
-    <t>palladium: 15</t>
+    <t>platinum: 5 [1]</t>
   </si>
   <si>
     <t>deep_topaz</t>
@@ -313,18 +307,6 @@
     <t>gypsum: 15</t>
   </si>
   <si>
-    <t>normal_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 45</t>
-  </si>
-  <si>
-    <t>ilmenite: 30</t>
-  </si>
-  <si>
-    <t>aluminium: 25</t>
-  </si>
-  <si>
     <t>normal_beryllium</t>
   </si>
   <si>
@@ -547,7 +529,7 @@
     <t>monazite: 25</t>
   </si>
   <si>
-    <t>neodymium: 25</t>
+    <t>neodymium: 5</t>
   </si>
   <si>
     <t>normal_oilsands</t>
@@ -574,628 +556,598 @@
     <t>normal_quartz</t>
   </si>
   <si>
-    <t>quartzite: 65 [1]</t>
-  </si>
-  <si>
-    <t>certus_quartz: 30</t>
+    <t>quartzite: 35 [1]</t>
+  </si>
+  <si>
+    <t>barite: 30</t>
+  </si>
+  <si>
+    <t>asbestos: 15</t>
+  </si>
+  <si>
+    <t>normal_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 45 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 35</t>
+  </si>
+  <si>
+    <t>cinnabar: 20</t>
+  </si>
+  <si>
+    <t>normal_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 40 [1]</t>
+  </si>
+  <si>
+    <t>salt: 30 [1]</t>
+  </si>
+  <si>
+    <t>lepidolite: 15</t>
+  </si>
+  <si>
+    <t>borax: 15</t>
+  </si>
+  <si>
+    <t>normal_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35</t>
+  </si>
+  <si>
+    <t>diatomite: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 25</t>
+  </si>
+  <si>
+    <t>alunite: 15</t>
+  </si>
+  <si>
+    <t>normal_silver</t>
+  </si>
+  <si>
+    <t>galena: 30</t>
+  </si>
+  <si>
+    <t>silver: 15</t>
+  </si>
+  <si>
+    <t>lead: 55 [1]</t>
+  </si>
+  <si>
+    <t>normal_sphalerite</t>
+  </si>
+  <si>
+    <t>sulfur: 35</t>
+  </si>
+  <si>
+    <t>sphalerite: 40 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 25</t>
+  </si>
+  <si>
+    <t>normal_spodumene</t>
+  </si>
+  <si>
+    <t>rock_salt: 20</t>
+  </si>
+  <si>
+    <t>salt: 30</t>
+  </si>
+  <si>
+    <t>spodumene: 35</t>
+  </si>
+  <si>
+    <t>normal_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 35</t>
+  </si>
+  <si>
+    <t>sphalerite: 15</t>
+  </si>
+  <si>
+    <t>normal_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 50 [1]</t>
+  </si>
+  <si>
+    <t>copper: 30</t>
+  </si>
+  <si>
+    <t>stibnite: 20</t>
+  </si>
+  <si>
+    <t>surface_bismuthinite</t>
+  </si>
+  <si>
+    <t>bismuth: 90</t>
+  </si>
+  <si>
+    <t>sulfur: 3</t>
+  </si>
+  <si>
+    <t>lead: 7</t>
+  </si>
+  <si>
+    <t>surface_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 60</t>
+  </si>
+  <si>
+    <t>tin: 40</t>
+  </si>
+  <si>
+    <t>surface_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 55</t>
+  </si>
+  <si>
+    <t>zeolite: 15</t>
+  </si>
+  <si>
+    <t>cassiterite: 5</t>
+  </si>
+  <si>
+    <t>realgar: 15</t>
+  </si>
+  <si>
+    <t>surface_sphalerite</t>
+  </si>
+  <si>
+    <t>sulfur: 55</t>
+  </si>
+  <si>
+    <t>sphalerite: 40</t>
+  </si>
+  <si>
+    <t>pyrite: 5</t>
+  </si>
+  <si>
+    <t>surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 60</t>
+  </si>
+  <si>
+    <t>copper: 20</t>
+  </si>
+  <si>
+    <t>glacio_stone</t>
+  </si>
+  <si>
+    <t>moon_deepslate</t>
+  </si>
+  <si>
+    <t>moon_stone</t>
+  </si>
+  <si>
+    <t>moon_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 25</t>
+  </si>
+  <si>
+    <t>pyrochlore: 40 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 5</t>
+  </si>
+  <si>
+    <t>moon_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 35</t>
+  </si>
+  <si>
+    <t>ilmenite: 40</t>
+  </si>
+  <si>
+    <t>armalcolite: 20</t>
+  </si>
+  <si>
+    <t>moon_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium: 35 [1]</t>
+  </si>
+  <si>
+    <t>emerald: 50 [2]</t>
+  </si>
+  <si>
+    <t>thorium: 1</t>
+  </si>
+  <si>
+    <t>moon_desh</t>
+  </si>
+  <si>
+    <t>desh: 40 [2]</t>
+  </si>
+  <si>
+    <t>ilmenite: 25 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 20</t>
+  </si>
+  <si>
+    <t>armalcolite: 15</t>
+  </si>
+  <si>
+    <t>moon_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite: 25 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 20</t>
+  </si>
+  <si>
+    <t>pentlandite: 25 [1]</t>
+  </si>
+  <si>
+    <t>moon_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 25</t>
+  </si>
+  <si>
+    <t>chromite: 40 [2]</t>
+  </si>
+  <si>
+    <t>moon_mica</t>
+  </si>
+  <si>
+    <t>kyanite: 35 [1]</t>
+  </si>
+  <si>
+    <t>moon_molybdenum</t>
+  </si>
+  <si>
+    <t>moon_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 1</t>
+  </si>
+  <si>
+    <t>moon_pyrolusite</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [2]</t>
+  </si>
+  <si>
+    <t>cobaltite: 25</t>
+  </si>
+  <si>
+    <t>cobalt: 25</t>
+  </si>
+  <si>
+    <t>tantalite: 15</t>
+  </si>
+  <si>
+    <t>moon_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 10</t>
+  </si>
+  <si>
+    <t>certus_quartz: 50 [2]</t>
+  </si>
+  <si>
+    <t>barite: 15</t>
+  </si>
+  <si>
+    <t>moon_redstone</t>
+  </si>
+  <si>
+    <t>moon_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35 [1]</t>
+  </si>
+  <si>
+    <t>soapstone: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 45</t>
+  </si>
+  <si>
+    <t>talc: 15</t>
+  </si>
+  <si>
+    <t>moon_sapphire</t>
+  </si>
+  <si>
+    <t>pyrope: 25</t>
+  </si>
+  <si>
+    <t>olivine: 2</t>
+  </si>
+  <si>
+    <t>moon_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tungstate: 50 [2]</t>
+  </si>
+  <si>
+    <t>lithium: 10</t>
+  </si>
+  <si>
+    <t>moon_sheldonite</t>
+  </si>
+  <si>
+    <t>cooperite: 25</t>
+  </si>
+  <si>
+    <t>platinum: 15</t>
+  </si>
+  <si>
+    <t>nickel: 25</t>
+  </si>
+  <si>
+    <t>moon_silver</t>
+  </si>
+  <si>
+    <t>silver: 45 [1]</t>
+  </si>
+  <si>
+    <t>lead: 25</t>
+  </si>
+  <si>
+    <t>moon_topaz</t>
+  </si>
+  <si>
+    <t>blackstone</t>
+  </si>
+  <si>
+    <t>deepslate</t>
+  </si>
+  <si>
+    <t>dripstone</t>
+  </si>
+  <si>
+    <t>nether_anthracite</t>
+  </si>
+  <si>
+    <t>anthracite: 100</t>
+  </si>
+  <si>
+    <t>nether_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 50 [2]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 35 [1]</t>
+  </si>
+  <si>
+    <t>nether_basaltic_sands</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>fullers_earth: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_beryllium</t>
+  </si>
+  <si>
+    <t>nether_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 40 [2]</t>
+  </si>
+  <si>
+    <t>tin: 60 [2]</t>
+  </si>
+  <si>
+    <t>nether_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 10 [1]</t>
+  </si>
+  <si>
+    <t>copper: 65 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10 [1]</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [2]</t>
+  </si>
+  <si>
+    <t>opal: 40 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>garnet_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_garnierite</t>
+  </si>
+  <si>
+    <t>cobaltite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_goethite</t>
+  </si>
+  <si>
+    <t>goethite: 50 [3]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_gold</t>
+  </si>
+  <si>
+    <t>nether_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 45 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 40 [1]</t>
+  </si>
+  <si>
+    <t>coal: 15</t>
+  </si>
+  <si>
+    <t>nether_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 35 [3]</t>
+  </si>
+  <si>
+    <t>nether_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 25 [1]</t>
+  </si>
+  <si>
+    <t>lapis: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30 [1]</t>
+  </si>
+  <si>
+    <t>talc: 20 [1]</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>pentlandite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 10</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 15 [1]</t>
+  </si>
+  <si>
+    <t>gold: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 30 [1]</t>
+  </si>
+  <si>
+    <t>spessartine: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrolusite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_mica</t>
+  </si>
+  <si>
+    <t>mica: 25 [1]</t>
+  </si>
+  <si>
+    <t>pollucite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_molybdenum</t>
+  </si>
+  <si>
+    <t>powellite: 10</t>
+  </si>
+  <si>
+    <t>nickel: 15</t>
+  </si>
+  <si>
+    <t>nether_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [2]</t>
+  </si>
+  <si>
+    <t>monazite: 25 [1]</t>
+  </si>
+  <si>
+    <t>neodymium: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_naquadah</t>
+  </si>
+  <si>
+    <t>naquadah: 75 [2]</t>
+  </si>
+  <si>
+    <t>plutonium: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 35 [1]</t>
+  </si>
+  <si>
+    <t>magnesite: 25 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_pitchblende</t>
+  </si>
+  <si>
+    <t>nether_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 30 [1]</t>
+  </si>
+  <si>
+    <t>nether_quartz: 65 [2]</t>
   </si>
   <si>
     <t>barite: 25</t>
-  </si>
-  <si>
-    <t>normal_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 45 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 35</t>
-  </si>
-  <si>
-    <t>cinnabar: 20</t>
-  </si>
-  <si>
-    <t>normal_salt</t>
-  </si>
-  <si>
-    <t>rock_salt: 40 [1]</t>
-  </si>
-  <si>
-    <t>salt: 30 [1]</t>
-  </si>
-  <si>
-    <t>lepidolite: 15</t>
-  </si>
-  <si>
-    <t>borax: 15</t>
-  </si>
-  <si>
-    <t>normal_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35</t>
-  </si>
-  <si>
-    <t>diatomite: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 25</t>
-  </si>
-  <si>
-    <t>alunite: 15</t>
-  </si>
-  <si>
-    <t>normal_silver</t>
-  </si>
-  <si>
-    <t>galena: 30</t>
-  </si>
-  <si>
-    <t>silver: 15</t>
-  </si>
-  <si>
-    <t>lead: 55 [1]</t>
-  </si>
-  <si>
-    <t>normal_sphalerite</t>
-  </si>
-  <si>
-    <t>sulfur: 35</t>
-  </si>
-  <si>
-    <t>sphalerite: 40 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 25</t>
-  </si>
-  <si>
-    <t>normal_spodumene</t>
-  </si>
-  <si>
-    <t>rock_salt: 20</t>
-  </si>
-  <si>
-    <t>salt: 30</t>
-  </si>
-  <si>
-    <t>spodumene: 35</t>
-  </si>
-  <si>
-    <t>normal_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 50 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 35</t>
-  </si>
-  <si>
-    <t>sphalerite: 15</t>
-  </si>
-  <si>
-    <t>normal_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 50 [1]</t>
-  </si>
-  <si>
-    <t>copper: 30</t>
-  </si>
-  <si>
-    <t>stibnite: 20</t>
-  </si>
-  <si>
-    <t>surface_bismuthinite</t>
-  </si>
-  <si>
-    <t>bismuth: 90</t>
-  </si>
-  <si>
-    <t>sulfur: 3</t>
-  </si>
-  <si>
-    <t>lead: 7</t>
-  </si>
-  <si>
-    <t>surface_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 60</t>
-  </si>
-  <si>
-    <t>tin: 40</t>
-  </si>
-  <si>
-    <t>surface_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 55</t>
-  </si>
-  <si>
-    <t>zeolite: 15</t>
-  </si>
-  <si>
-    <t>cassiterite: 5</t>
-  </si>
-  <si>
-    <t>realgar: 15</t>
-  </si>
-  <si>
-    <t>surface_sphalerite</t>
-  </si>
-  <si>
-    <t>sulfur: 55</t>
-  </si>
-  <si>
-    <t>sphalerite: 40</t>
-  </si>
-  <si>
-    <t>pyrite: 5</t>
-  </si>
-  <si>
-    <t>surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 60</t>
-  </si>
-  <si>
-    <t>copper: 20</t>
-  </si>
-  <si>
-    <t>glacio_stone</t>
-  </si>
-  <si>
-    <t>moon_deepslate</t>
-  </si>
-  <si>
-    <t>moon_stone</t>
-  </si>
-  <si>
-    <t>moon_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 25</t>
-  </si>
-  <si>
-    <t>pyrochlore: 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 35</t>
-  </si>
-  <si>
-    <t>ilmenite: 40</t>
-  </si>
-  <si>
-    <t>armalcolite: 20</t>
-  </si>
-  <si>
-    <t>moon_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium: 35 [1]</t>
-  </si>
-  <si>
-    <t>emerald: 50 [2]</t>
-  </si>
-  <si>
-    <t>moon_desh</t>
-  </si>
-  <si>
-    <t>desh: 40 [2]</t>
-  </si>
-  <si>
-    <t>ilmenite: 25 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 20</t>
-  </si>
-  <si>
-    <t>armalcolite: 15</t>
-  </si>
-  <si>
-    <t>moon_diopside</t>
-  </si>
-  <si>
-    <t>diopside: 45 [2]</t>
-  </si>
-  <si>
-    <t>trona: 25</t>
-  </si>
-  <si>
-    <t>cobalt: 25</t>
-  </si>
-  <si>
-    <t>tantalite: 15</t>
-  </si>
-  <si>
-    <t>moon_enstatite</t>
-  </si>
-  <si>
-    <t>enstatite: 45 [2]</t>
-  </si>
-  <si>
-    <t>chromite: 30 [1]</t>
-  </si>
-  <si>
-    <t>ilmenite: 15</t>
-  </si>
-  <si>
-    <t>fayalite: 10</t>
-  </si>
-  <si>
-    <t>moon_fayalite</t>
-  </si>
-  <si>
-    <t>enstatite: 10</t>
-  </si>
-  <si>
-    <t>pyrite: 30 [1]</t>
-  </si>
-  <si>
-    <t>fayalite: 45</t>
-  </si>
-  <si>
-    <t>moon_garnierite</t>
-  </si>
-  <si>
-    <t>pentlandite: 25 [1]</t>
-  </si>
-  <si>
-    <t>moon_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 25</t>
-  </si>
-  <si>
-    <t>chromite: 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_mica</t>
-  </si>
-  <si>
-    <t>kyanite: 35 [1]</t>
-  </si>
-  <si>
-    <t>moon_molybdenum</t>
-  </si>
-  <si>
-    <t>moon_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite: 50 [1]</t>
-  </si>
-  <si>
-    <t>moon_olivine</t>
-  </si>
-  <si>
-    <t>diopside: 15 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 65 [2]</t>
-  </si>
-  <si>
-    <t>moon_plutonium</t>
-  </si>
-  <si>
-    <t>tungstate: 35</t>
-  </si>
-  <si>
-    <t>armalcolite: 40 [1]</t>
-  </si>
-  <si>
-    <t>plutonium: 25</t>
-  </si>
-  <si>
-    <t>moon_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 10</t>
-  </si>
-  <si>
-    <t>certus_quartz: 50 [2]</t>
-  </si>
-  <si>
-    <t>barite: 15</t>
-  </si>
-  <si>
-    <t>nether_quartz: 25 [1]</t>
-  </si>
-  <si>
-    <t>moon_redstone</t>
-  </si>
-  <si>
-    <t>moon_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35 [1]</t>
-  </si>
-  <si>
-    <t>soapstone: 25</t>
-  </si>
-  <si>
-    <t>talc: 15</t>
-  </si>
-  <si>
-    <t>moon_sapphire</t>
-  </si>
-  <si>
-    <t>pyrope: 25</t>
-  </si>
-  <si>
-    <t>moon_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tungstate: 50 [2]</t>
-  </si>
-  <si>
-    <t>lithium: 10</t>
-  </si>
-  <si>
-    <t>moon_sheldonite</t>
-  </si>
-  <si>
-    <t>cooperite: 25</t>
-  </si>
-  <si>
-    <t>platinum: 25</t>
-  </si>
-  <si>
-    <t>moon_silver</t>
-  </si>
-  <si>
-    <t>silver: 45 [1]</t>
-  </si>
-  <si>
-    <t>lead: 25</t>
-  </si>
-  <si>
-    <t>blackstone</t>
-  </si>
-  <si>
-    <t>deepslate</t>
-  </si>
-  <si>
-    <t>dripstone</t>
-  </si>
-  <si>
-    <t>nether_anthracite</t>
-  </si>
-  <si>
-    <t>anthracite: 100</t>
-  </si>
-  <si>
-    <t>nether_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 50 [2]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_basaltic_sands</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>granitic_mineral_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>fullers_earth: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 45 [2]</t>
-  </si>
-  <si>
-    <t>ilmenite: 30 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_beryllium</t>
-  </si>
-  <si>
-    <t>nether_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 40 [2]</t>
-  </si>
-  <si>
-    <t>tin: 60 [2]</t>
-  </si>
-  <si>
-    <t>nether_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 10 [1]</t>
-  </si>
-  <si>
-    <t>copper: 65 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10 [1]</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [2]</t>
-  </si>
-  <si>
-    <t>opal: 40 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>garnet_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_garnierite</t>
-  </si>
-  <si>
-    <t>cobaltite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_goethite</t>
-  </si>
-  <si>
-    <t>goethite: 50 [3]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_gold</t>
-  </si>
-  <si>
-    <t>nether_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 45 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 40 [1]</t>
-  </si>
-  <si>
-    <t>coal: 15</t>
-  </si>
-  <si>
-    <t>nether_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 35 [3]</t>
-  </si>
-  <si>
-    <t>nether_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sodalite: 25 [1]</t>
-  </si>
-  <si>
-    <t>lapis: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30 [1]</t>
-  </si>
-  <si>
-    <t>talc: 20 [1]</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>pentlandite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_magnetite</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 15 [1]</t>
-  </si>
-  <si>
-    <t>chromite: 60 [2]</t>
-  </si>
-  <si>
-    <t>gold: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 30 [1]</t>
-  </si>
-  <si>
-    <t>spessartine: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrolusite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_mica</t>
-  </si>
-  <si>
-    <t>mica: 25 [1]</t>
-  </si>
-  <si>
-    <t>bauxite: 25 [1]</t>
-  </si>
-  <si>
-    <t>pollucite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_molybdenum</t>
-  </si>
-  <si>
-    <t>nether_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite: 50 [2]</t>
-  </si>
-  <si>
-    <t>monazite: 25 [1]</t>
-  </si>
-  <si>
-    <t>neodymium: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_naquadah</t>
-  </si>
-  <si>
-    <t>naquadah: 75 [2]</t>
-  </si>
-  <si>
-    <t>plutonium: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_olivine</t>
-  </si>
-  <si>
-    <t>bentonite: 35 [1]</t>
-  </si>
-  <si>
-    <t>magnesite: 25 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_pitchblende</t>
-  </si>
-  <si>
-    <t>nether_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 30 [1]</t>
-  </si>
-  <si>
-    <t>nether_quartz: 65 [2]</t>
   </si>
   <si>
     <t>nether_redstone</t>
@@ -1342,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH49"/>
+  <dimension ref="A1:AH48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.943572998046875" customWidth="1" style="1"/>
@@ -1975,7 +1927,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="1">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D7" s="1">
         <v>0.3</v>
@@ -1987,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
@@ -2096,9 +2048,6 @@
       <c r="L8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="O8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2162,7 +2111,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>42</v>
@@ -2183,10 +2132,10 @@
         <v>24</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>36</v>
@@ -2251,7 +2200,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>31</v>
@@ -2275,16 +2224,16 @@
         <v>8</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>37</v>
@@ -2349,13 +2298,13 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="1">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D11" s="1">
         <v>0.35</v>
@@ -2370,13 +2319,13 @@
         <v>20</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>36</v>
@@ -2441,13 +2390,13 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="1">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="D12" s="1">
         <v>0.3</v>
@@ -2462,16 +2411,13 @@
         <v>30</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>36</v>
@@ -2536,7 +2482,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>31</v>
@@ -2560,16 +2506,16 @@
         <v>7</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>36</v>
@@ -2634,7 +2580,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>42</v>
@@ -2655,13 +2601,13 @@
         <v>34</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>36</v>
@@ -2726,7 +2672,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>31</v>
@@ -2750,16 +2696,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>36</v>
@@ -2824,61 +2770,64 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="D16" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E16" s="1">
         <v>-32</v>
       </c>
       <c r="F16" s="1">
+        <v>50</v>
+      </c>
+      <c r="H16" s="1">
         <v>60</v>
       </c>
-      <c r="G16" s="1">
-        <v>40</v>
+      <c r="I16" s="1">
+        <v>10</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="O16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X16" s="1" t="s">
         <v>36</v>
@@ -2890,7 +2839,7 @@
         <v>36</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB16" s="1" t="s">
         <v>36</v>
@@ -2902,13 +2851,13 @@
         <v>36</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH16" s="1" t="s">
         <v>36</v>
@@ -2916,76 +2865,73 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D17" s="1">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="1">
         <v>-32</v>
       </c>
       <c r="F17" s="1">
-        <v>50</v>
-      </c>
-      <c r="H17" s="1">
-        <v>60</v>
-      </c>
-      <c r="I17" s="1">
-        <v>10</v>
+        <v>75</v>
+      </c>
+      <c r="G17" s="1">
+        <v>40</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="O17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>36</v>
@@ -2997,13 +2943,13 @@
         <v>36</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH17" s="1" t="s">
         <v>36</v>
@@ -3011,7 +2957,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>42</v>
@@ -3032,13 +2978,10 @@
         <v>40</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>36</v>
@@ -3047,16 +2990,16 @@
         <v>36</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U18" s="1" t="s">
         <v>36</v>
@@ -3065,7 +3008,7 @@
         <v>37</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>37</v>
@@ -3077,7 +3020,7 @@
         <v>37</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB18" s="1" t="s">
         <v>36</v>
@@ -3095,7 +3038,7 @@
         <v>36</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH18" s="1" t="s">
         <v>36</v>
@@ -3103,31 +3046,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="1">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="D19" s="1">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E19" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="G19" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>36</v>
@@ -3136,37 +3076,37 @@
         <v>36</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB19" s="1" t="s">
         <v>36</v>
@@ -3184,7 +3124,7 @@
         <v>36</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH19" s="1" t="s">
         <v>36</v>
@@ -3192,55 +3132,64 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="1">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="D20" s="1">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F20" s="1">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G20" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>36</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X20" s="1" t="s">
         <v>36</v>
@@ -3252,7 +3201,7 @@
         <v>36</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB20" s="1" t="s">
         <v>36</v>
@@ -3264,13 +3213,13 @@
         <v>36</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH20" s="1" t="s">
         <v>36</v>
@@ -3278,38 +3227,38 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="1">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="D21" s="1">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E21" s="1">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="1">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G21" s="1">
         <v>40</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="O21" s="1" t="s">
         <v>37</v>
       </c>
@@ -3317,153 +3266,156 @@
         <v>37</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="1">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="D22" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E22" s="1">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="F22" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G22" s="1">
         <v>40</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>126</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -3471,10 +3423,10 @@
         <v>127</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D23" s="1">
         <v>0.4</v>
@@ -3488,26 +3440,26 @@
       <c r="G23" s="1">
         <v>40</v>
       </c>
+      <c r="H23" s="1">
+        <v>12</v>
+      </c>
       <c r="J23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="O23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>36</v>
@@ -3522,7 +3474,7 @@
         <v>36</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>37</v>
@@ -3537,7 +3489,7 @@
         <v>36</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA23" s="1" t="s">
         <v>36</v>
@@ -3552,7 +3504,7 @@
         <v>36</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>36</v>
@@ -3566,41 +3518,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="1">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1">
         <v>0.4</v>
       </c>
       <c r="E24" s="1">
-        <v>-32</v>
+        <v>-64</v>
       </c>
       <c r="F24" s="1">
-        <v>60</v>
+        <v>-16</v>
       </c>
       <c r="G24" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="O24" s="1" t="s">
         <v>37</v>
       </c>
@@ -3608,16 +3557,16 @@
         <v>37</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>37</v>
@@ -3626,75 +3575,75 @@
         <v>37</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C25" s="1">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="D25" s="1">
         <v>0.4</v>
       </c>
       <c r="E25" s="1">
-        <v>-64</v>
+        <v>-32</v>
       </c>
       <c r="F25" s="1">
-        <v>-16</v>
+        <v>75</v>
       </c>
       <c r="G25" s="1">
-        <v>16</v>
-      </c>
-      <c r="H25" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>140</v>
+      <c r="M25" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>37</v>
@@ -3703,99 +3652,99 @@
         <v>37</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="1">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D26" s="1">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E26" s="1">
-        <v>-32</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="1">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="O26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>36</v>
@@ -3810,7 +3759,7 @@
         <v>36</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V26" s="1" t="s">
         <v>36</v>
@@ -3822,7 +3771,7 @@
         <v>36</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z26" s="1" t="s">
         <v>36</v>
@@ -3831,61 +3780,61 @@
         <v>36</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D27" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E27" s="1">
-        <v>-60</v>
+        <v>-32</v>
       </c>
       <c r="F27" s="1">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G27" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
       </c>
@@ -3917,39 +3866,39 @@
         <v>36</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>42</v>
@@ -3958,27 +3907,30 @@
         <v>190</v>
       </c>
       <c r="D28" s="1">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="1">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="1">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G28" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>152</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -4003,25 +3955,25 @@
         <v>36</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC28" s="1" t="s">
         <v>36</v>
@@ -4050,19 +4002,19 @@
         <v>42</v>
       </c>
       <c r="C29" s="1">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D29" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="1">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="F29" s="1">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G29" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>154</v>
@@ -4076,9 +4028,6 @@
       <c r="M29" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="O29" s="1" t="s">
         <v>36</v>
       </c>
@@ -4086,37 +4035,37 @@
         <v>36</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB29" s="1" t="s">
         <v>36</v>
@@ -4134,7 +4083,7 @@
         <v>36</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>36</v>
@@ -4142,43 +4091,43 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="1">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D30" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E30" s="1">
         <v>-32</v>
       </c>
       <c r="F30" s="1">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G30" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="O30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>37</v>
@@ -4193,7 +4142,7 @@
         <v>37</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>36</v>
@@ -4223,7 +4172,7 @@
         <v>36</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>36</v>
@@ -4237,133 +4186,130 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="1">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D31" s="1">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E31" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="G31" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="M31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="O31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="1">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D32" s="1">
         <v>0.25</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F32" s="1">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="O32" s="1" t="s">
         <v>36</v>
       </c>
@@ -4395,7 +4341,7 @@
         <v>37</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z32" s="1" t="s">
         <v>37</v>
@@ -4404,30 +4350,30 @@
         <v>36</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>42</v>
@@ -4436,25 +4382,19 @@
         <v>185</v>
       </c>
       <c r="D33" s="1">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G33" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>36</v>
@@ -4463,37 +4403,37 @@
         <v>36</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB33" s="1" t="s">
         <v>36</v>
@@ -4511,7 +4451,7 @@
         <v>36</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH33" s="1" t="s">
         <v>36</v>
@@ -4519,67 +4459,76 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="1">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D34" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E34" s="1">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F34" s="1">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB34" s="1" t="s">
         <v>36</v>
@@ -4591,13 +4540,13 @@
         <v>36</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AG34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH34" s="1" t="s">
         <v>36</v>
@@ -4605,43 +4554,40 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="1">
+        <v>190</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>-32</v>
+      </c>
+      <c r="F35" s="1">
+        <v>100</v>
+      </c>
+      <c r="G35" s="1">
+        <v>40</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E35" s="1">
-        <v>-40</v>
-      </c>
-      <c r="F35" s="1">
-        <v>30</v>
-      </c>
-      <c r="G35" s="1">
-        <v>26</v>
-      </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="O35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>36</v>
@@ -4656,22 +4602,22 @@
         <v>36</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA35" s="1" t="s">
         <v>36</v>
@@ -4683,16 +4629,16 @@
         <v>36</v>
       </c>
       <c r="AD35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH35" s="1" t="s">
         <v>36</v>
@@ -4700,16 +4646,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D36" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E36" s="1">
         <v>-32</v>
@@ -4721,14 +4667,14 @@
         <v>40</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="O36" s="1" t="s">
         <v>36</v>
       </c>
@@ -4760,10 +4706,10 @@
         <v>36</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA36" s="1" t="s">
         <v>36</v>
@@ -4775,16 +4721,16 @@
         <v>36</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH36" s="1" t="s">
         <v>36</v>
@@ -4792,35 +4738,41 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C37" s="1">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D37" s="1">
         <v>0.4</v>
       </c>
       <c r="E37" s="1">
-        <v>-32</v>
+        <v>30</v>
       </c>
       <c r="F37" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G37" s="1">
         <v>40</v>
       </c>
+      <c r="H37" s="1">
+        <v>4</v>
+      </c>
       <c r="J37" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="M37" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="O37" s="1" t="s">
         <v>36</v>
       </c>
@@ -4834,7 +4786,7 @@
         <v>36</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>36</v>
@@ -4855,10 +4807,10 @@
         <v>36</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB37" s="1" t="s">
         <v>36</v>
@@ -4876,7 +4828,7 @@
         <v>36</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH37" s="1" t="s">
         <v>36</v>
@@ -4884,41 +4836,38 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C38" s="1">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D38" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E38" s="1">
-        <v>30</v>
+        <v>-32</v>
       </c>
       <c r="F38" s="1">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G38" s="1">
         <v>40</v>
       </c>
-      <c r="H38" s="1">
-        <v>4</v>
-      </c>
       <c r="J38" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="O38" s="1" t="s">
         <v>36</v>
       </c>
@@ -4932,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>36</v>
@@ -4941,79 +4890,76 @@
         <v>36</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="1">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D39" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E39" s="1">
         <v>-32</v>
       </c>
       <c r="F39" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G39" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="O39" s="1" t="s">
         <v>36</v>
       </c>
@@ -5036,13 +4982,13 @@
         <v>36</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>37</v>
@@ -5054,36 +5000,36 @@
         <v>36</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="1">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D40" s="1">
         <v>0.4</v>
@@ -5098,19 +5044,19 @@
         <v>40</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="O40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>36</v>
@@ -5125,7 +5071,7 @@
         <v>36</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>36</v>
@@ -5140,69 +5086,75 @@
         <v>37</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA40" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG40" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1">
+        <v>180</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="E41" s="1">
+        <v>20</v>
+      </c>
+      <c r="F41" s="1">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1">
+        <v>35</v>
+      </c>
+      <c r="H41" s="1">
+        <v>6</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1">
-        <v>170</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="E41" s="1">
-        <v>-32</v>
-      </c>
-      <c r="F41" s="1">
-        <v>75</v>
-      </c>
-      <c r="G41" s="1">
-        <v>40</v>
-      </c>
-      <c r="J41" s="1" t="s">
+      <c r="L41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M41" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="O41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q41" s="1" t="s">
         <v>36</v>
@@ -5217,22 +5169,22 @@
         <v>36</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W41" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y41" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA41" s="1" t="s">
         <v>36</v>
@@ -5247,7 +5199,7 @@
         <v>37</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>37</v>
@@ -5261,46 +5213,40 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="1">
+        <v>165</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>210</v>
+      </c>
+      <c r="G42" s="1">
+        <v>45</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="1">
-        <v>180</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.375</v>
-      </c>
-      <c r="E42" s="1">
-        <v>20</v>
-      </c>
-      <c r="F42" s="1">
-        <v>60</v>
-      </c>
-      <c r="G42" s="1">
-        <v>35</v>
-      </c>
-      <c r="H42" s="1">
-        <v>6</v>
-      </c>
-      <c r="J42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="O42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>36</v>
@@ -5315,84 +5261,84 @@
         <v>36</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG42" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="1">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D43" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F43" s="1">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G43" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J43" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="O43" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>36</v>
@@ -5407,7 +5353,7 @@
         <v>36</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>36</v>
@@ -5419,7 +5365,7 @@
         <v>36</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>36</v>
@@ -5428,58 +5374,58 @@
         <v>36</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="1">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D44" s="1">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E44" s="1">
-        <v>-32</v>
+        <v>60</v>
       </c>
       <c r="F44" s="1">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="G44" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J44" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="O44" s="1" t="s">
         <v>36</v>
       </c>
@@ -5487,69 +5433,69 @@
         <v>36</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="1">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D45" s="1">
         <v>0.25</v>
@@ -5564,13 +5510,10 @@
         <v>50</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>36</v>
@@ -5579,16 +5522,16 @@
         <v>36</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U45" s="1" t="s">
         <v>36</v>
@@ -5597,7 +5540,7 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X45" s="1" t="s">
         <v>37</v>
@@ -5609,7 +5552,7 @@
         <v>37</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB45" s="1" t="s">
         <v>36</v>
@@ -5627,7 +5570,7 @@
         <v>36</v>
       </c>
       <c r="AG45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AH45" s="1" t="s">
         <v>36</v>
@@ -5635,37 +5578,43 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="1">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="D46" s="1">
         <v>0.25</v>
       </c>
       <c r="E46" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G46" s="1">
         <v>50</v>
       </c>
       <c r="J46" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M46" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="O46" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q46" s="1" t="s">
         <v>36</v>
@@ -5680,22 +5629,22 @@
         <v>36</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA46" s="1" t="s">
         <v>36</v>
@@ -5710,7 +5659,7 @@
         <v>36</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF46" s="1" t="s">
         <v>36</v>
@@ -5724,38 +5673,35 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="D47" s="1">
         <v>0.25</v>
       </c>
       <c r="E47" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F47" s="1">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G47" s="1">
         <v>50</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="O47" s="1" t="s">
         <v>37</v>
       </c>
@@ -5787,7 +5733,7 @@
         <v>36</v>
       </c>
       <c r="Y47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z47" s="1" t="s">
         <v>36</v>
@@ -5796,36 +5742,36 @@
         <v>36</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AC47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE47" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG47" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AH47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="1">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D48" s="1">
         <v>0.25</v>
@@ -5840,19 +5786,19 @@
         <v>50</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q48" s="1" t="s">
         <v>36</v>
@@ -5867,7 +5813,7 @@
         <v>36</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>36</v>
@@ -5897,7 +5843,7 @@
         <v>37</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>37</v>
@@ -5906,98 +5852,6 @@
         <v>36</v>
       </c>
       <c r="AH48" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="1">
-        <v>140</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E49" s="1">
-        <v>60</v>
-      </c>
-      <c r="F49" s="1">
-        <v>210</v>
-      </c>
-      <c r="G49" s="1">
-        <v>50</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH49" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6008,7 +5862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.286670684814453" customWidth="1" style="1"/>
@@ -6020,11 +5874,11 @@
     <col min="7" max="7" width="9.140625" customWidth="1" style="1"/>
     <col min="8" max="8" width="9.140625" customWidth="1" style="1"/>
     <col min="9" max="9" width="9.140625" customWidth="1" style="1"/>
-    <col min="10" max="10" width="16.826200485229492" customWidth="1" style="1"/>
+    <col min="10" max="10" width="17.362285614013672" customWidth="1" style="1"/>
     <col min="11" max="11" width="23.763607025146484" customWidth="1" style="1"/>
     <col min="12" max="12" width="17.075828552246094" customWidth="1" style="1"/>
-    <col min="13" max="13" width="20.164461135864258" customWidth="1" style="1"/>
-    <col min="14" max="14" width="11.170694351196289" customWidth="1" style="1"/>
+    <col min="13" max="13" width="18.38944435119629" customWidth="1" style="1"/>
+    <col min="14" max="14" width="12.619355201721191" customWidth="1" style="1"/>
     <col min="15" max="15" width="9.140625" customWidth="1" style="1"/>
     <col min="16" max="16" width="9.140625" customWidth="1" style="1"/>
     <col min="17" max="17" width="9.140625" customWidth="1" style="1"/>
@@ -6104,13 +5958,13 @@
         <v>19</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>26</v>
@@ -6118,7 +5972,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
@@ -6130,22 +5984,25 @@
         <v>0.25</v>
       </c>
       <c r="E2" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>36</v>
@@ -6177,37 +6034,34 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="1">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D3" s="1">
         <v>0.3</v>
       </c>
       <c r="E3" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G3" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>36</v>
@@ -6219,13 +6073,13 @@
         <v>36</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>37</v>
@@ -6234,27 +6088,27 @@
         <v>37</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="D4" s="1">
         <v>0.35</v>
       </c>
       <c r="E4" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H4" s="1">
         <v>60</v>
@@ -6263,13 +6117,19 @@
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>107</v>
+        <v>250</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>36</v>
@@ -6287,10 +6147,10 @@
         <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>37</v>
@@ -6301,61 +6161,61 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="1">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="D5" s="1">
         <v>0.3</v>
       </c>
       <c r="E5" s="1">
-        <v>-32</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G5" s="1">
         <v>30</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>36</v>
@@ -6363,7 +6223,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>42</v>
@@ -6372,34 +6232,37 @@
         <v>250</v>
       </c>
       <c r="D6" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="1">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G6" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>263</v>
+        <v>124</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>36</v>
@@ -6414,54 +6277,57 @@
         <v>36</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="1">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="D7" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="1">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>90</v>
       </c>
       <c r="G7" s="1">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>267</v>
+        <v>59</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>269</v>
+        <v>61</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>36</v>
@@ -6487,7 +6353,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>42</v>
@@ -6496,34 +6362,37 @@
         <v>250</v>
       </c>
       <c r="D8" s="1">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="1">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>273</v>
+        <v>167</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>36</v>
@@ -6549,52 +6418,49 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="1">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D9" s="1">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E9" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>132</v>
+        <v>242</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>37</v>
@@ -6603,7 +6469,7 @@
         <v>36</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>36</v>
@@ -6614,114 +6480,111 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="1">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="D10" s="1">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E10" s="1">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>62</v>
+        <v>268</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="1">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D11" s="1">
         <v>0.25</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>171</v>
+        <v>271</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>172</v>
+        <v>272</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>37</v>
@@ -6741,46 +6604,43 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="1">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="D12" s="1">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E12" s="1">
-        <v>-64</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>65</v>
+        <v>276</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>67</v>
+        <v>277</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>37</v>
@@ -6789,21 +6649,21 @@
         <v>37</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>42</v>
@@ -6812,43 +6672,46 @@
         <v>250</v>
       </c>
       <c r="D13" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="1">
-        <v>-32</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>283</v>
+        <v>184</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U13" s="1" t="s">
         <v>36</v>
@@ -6862,52 +6725,52 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="1">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D14" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E14" s="1">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G14" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>36</v>
@@ -6919,45 +6782,54 @@
         <v>36</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="D15" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E15" s="1">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1">
-        <v>15</v>
+        <v>28</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>288</v>
+        <v>71</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>290</v>
+        <v>73</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>36</v>
@@ -6983,49 +6855,46 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D16" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E16" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G16" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>37</v>
@@ -7034,10 +6903,10 @@
         <v>37</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>37</v>
@@ -7045,40 +6914,43 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="1">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D17" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E17" s="1">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G17" s="1">
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>191</v>
+        <v>292</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>192</v>
+        <v>293</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>36</v>
@@ -7090,13 +6962,13 @@
         <v>36</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>36</v>
@@ -7104,37 +6976,37 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D18" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E18" s="1">
-        <v>-32</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G18" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>36</v>
@@ -7143,7 +7015,7 @@
         <v>36</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>37</v>
@@ -7161,252 +7033,72 @@
         <v>37</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="1">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="D19" s="1">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="1">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="G19" s="1">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>302</v>
+        <v>85</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="1">
-        <v>250</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="E20" s="1">
-        <v>-64</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>20</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="1">
-        <v>250</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>-64</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>30</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1">
-        <v>210</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-32</v>
-      </c>
-      <c r="F22" s="1">
-        <v>75</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -7416,7 +7108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.112842559814453" customWidth="1" style="1"/>
@@ -7500,16 +7192,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>19</v>
@@ -7526,7 +7218,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>31</v>
@@ -7550,7 +7242,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>36</v>
@@ -7582,7 +7274,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>42</v>
@@ -7603,13 +7295,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>36</v>
@@ -7641,7 +7333,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>31</v>
@@ -7665,16 +7357,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>37</v>
@@ -7706,16 +7398,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E5" s="1">
         <v>32</v>
@@ -7723,17 +7415,23 @@
       <c r="F5" s="1">
         <v>128</v>
       </c>
-      <c r="G5" s="1">
-        <v>45</v>
+      <c r="H5" s="1">
+        <v>60</v>
+      </c>
+      <c r="I5" s="1">
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>326</v>
+        <v>248</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>328</v>
+        <v>250</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>37</v>
@@ -7765,16 +7463,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D6" s="1">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="1">
         <v>32</v>
@@ -7782,52 +7480,46 @@
       <c r="F6" s="1">
         <v>128</v>
       </c>
-      <c r="H6" s="1">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1">
-        <v>12</v>
+      <c r="G6" s="1">
+        <v>45</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>107</v>
+        <v>314</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>42</v>
@@ -7848,54 +7540,60 @@
         <v>45</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>332</v>
+        <v>113</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="D8" s="1">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E8" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
         <v>128</v>
@@ -7903,17 +7601,20 @@
       <c r="G8" s="1">
         <v>45</v>
       </c>
+      <c r="H8" s="1">
+        <v>8</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>37</v>
@@ -7945,19 +7646,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="D9" s="1">
         <v>0.35</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1">
         <v>128</v>
@@ -7965,23 +7666,20 @@
       <c r="G9" s="1">
         <v>45</v>
       </c>
-      <c r="H9" s="1">
-        <v>8</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>37</v>
@@ -7990,39 +7688,39 @@
         <v>37</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>37</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="1">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="D10" s="1">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1">
         <v>128</v>
@@ -8031,15 +7729,18 @@
         <v>45</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>342</v>
+        <v>257</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>343</v>
+        <v>258</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="M10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>126</v>
       </c>
       <c r="O10" s="1" t="s">
@@ -8049,81 +7750,78 @@
         <v>37</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="1">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="D11" s="1">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E11" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
         <v>128</v>
       </c>
       <c r="G11" s="1">
+        <v>37</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U11" s="1" t="s">
         <v>36</v>
@@ -8137,16 +7835,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="1">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D12" s="1">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -8158,57 +7856,57 @@
         <v>37</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>348</v>
+        <v>43</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>349</v>
+        <v>44</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>45</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -8216,20 +7914,20 @@
       <c r="F13" s="1">
         <v>128</v>
       </c>
-      <c r="G13" s="1">
-        <v>37</v>
+      <c r="H13" s="1">
+        <v>60</v>
+      </c>
+      <c r="I13" s="1">
+        <v>12</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>43</v>
+        <v>334</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>44</v>
+        <v>335</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>36</v>
@@ -8261,16 +7959,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="D14" s="1">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -8278,52 +7976,55 @@
       <c r="F14" s="1">
         <v>128</v>
       </c>
-      <c r="H14" s="1">
-        <v>60</v>
-      </c>
-      <c r="I14" s="1">
-        <v>12</v>
+      <c r="G14" s="1">
+        <v>35</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>352</v>
+        <v>48</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>354</v>
+        <v>338</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>42</v>
@@ -8332,34 +8033,31 @@
         <v>220</v>
       </c>
       <c r="D15" s="1">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F15" s="1">
         <v>128</v>
       </c>
       <c r="G15" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>37</v>
@@ -8388,13 +8086,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D16" s="1">
         <v>0.35</v>
@@ -8406,19 +8104,22 @@
         <v>128</v>
       </c>
       <c r="G16" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>149</v>
+        <v>347</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>36</v>
@@ -8427,128 +8128,125 @@
         <v>37</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="1">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="D17" s="1">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
         <v>128</v>
       </c>
       <c r="G17" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>364</v>
+        <v>157</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D18" s="1">
         <v>0.4</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1">
         <v>128</v>
       </c>
       <c r="G18" s="1">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>58</v>
+        <v>353</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>37</v>
@@ -8580,16 +8278,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="1">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="D19" s="1">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E19" s="1">
         <v>32</v>
@@ -8598,81 +8296,78 @@
         <v>128</v>
       </c>
       <c r="G19" s="1">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>371</v>
+        <v>264</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>168</v>
+        <v>358</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="1">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D20" s="1">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="E20" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
         <v>128</v>
       </c>
       <c r="G20" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>280</v>
+        <v>64</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>375</v>
+        <v>65</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>36</v>
@@ -8704,7 +8399,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>42</v>
@@ -8713,28 +8408,25 @@
         <v>245</v>
       </c>
       <c r="D21" s="1">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1">
         <v>128</v>
       </c>
       <c r="G21" s="1">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>64</v>
+        <v>363</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>65</v>
+        <v>364</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>67</v>
+        <v>365</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>36</v>
@@ -8766,37 +8458,34 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="1">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="D22" s="1">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E22" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="G22" s="1">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>37</v>
@@ -8805,27 +8494,27 @@
         <v>36</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>36</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>42</v>
@@ -8834,22 +8523,28 @@
         <v>250</v>
       </c>
       <c r="D23" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E23" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="G23" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>37</v>
@@ -8858,13 +8553,13 @@
         <v>37</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>36</v>
@@ -8881,78 +8576,72 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="1">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="D24" s="1">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="E24" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1">
         <v>128</v>
       </c>
       <c r="G24" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>387</v>
+        <v>68</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="1">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D25" s="1">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -8961,54 +8650,57 @@
         <v>128</v>
       </c>
       <c r="G25" s="1">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>69</v>
+        <v>375</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>70</v>
+        <v>376</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D26" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -9020,31 +8712,31 @@
         <v>45</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>392</v>
+        <v>184</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>188</v>
+        <v>380</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U26" s="1" t="s">
         <v>36</v>
@@ -9058,34 +8750,37 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="1">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D27" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E27" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F27" s="1">
         <v>128</v>
       </c>
       <c r="G27" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>396</v>
+        <v>383</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -9097,57 +8792,60 @@
         <v>36</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D28" s="1">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E28" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1">
         <v>128</v>
       </c>
       <c r="G28" s="1">
-        <v>50</v>
+        <v>33</v>
+      </c>
+      <c r="H28" s="1">
+        <v>8</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>298</v>
+        <v>71</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>398</v>
+        <v>72</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>202</v>
+        <v>386</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>36</v>
@@ -9179,10 +8877,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C29" s="1">
         <v>180</v>
@@ -9197,22 +8895,16 @@
         <v>128</v>
       </c>
       <c r="G29" s="1">
-        <v>33</v>
-      </c>
-      <c r="H29" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>72</v>
+        <v>388</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>36</v>
@@ -9244,16 +8936,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="1">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="D30" s="1">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -9262,102 +8954,102 @@
         <v>128</v>
       </c>
       <c r="G30" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>405</v>
+        <v>82</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="1">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D31" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1">
         <v>128</v>
       </c>
       <c r="G31" s="1">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>36</v>
@@ -9365,19 +9057,19 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="1">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D32" s="1">
         <v>0.5</v>
       </c>
       <c r="E32" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1">
         <v>128</v>
@@ -9386,37 +9078,37 @@
         <v>45</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>409</v>
+        <v>203</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>36</v>
@@ -9424,34 +9116,34 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="1">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D33" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E33" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
         <v>128</v>
       </c>
       <c r="G33" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>209</v>
+        <v>400</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>37</v>
@@ -9460,13 +9152,13 @@
         <v>37</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>36</v>
@@ -9478,42 +9170,36 @@
         <v>36</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="1">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="D34" s="1">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G34" s="1">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>37</v>
@@ -9522,7 +9208,7 @@
         <v>36</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>36</v>
@@ -9537,33 +9223,39 @@
         <v>36</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="1">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="D35" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E35" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G35" s="1">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>419</v>
+        <v>405</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>36</v>
@@ -9572,60 +9264,66 @@
         <v>37</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D36" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E36" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1">
         <v>128</v>
       </c>
       <c r="G36" s="1">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="H36" s="1">
+        <v>7</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>422</v>
+        <v>85</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>222</v>
+        <v>86</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>37</v>
@@ -9643,77 +9341,12 @@
         <v>36</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="1">
-        <v>180</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>128</v>
-      </c>
-      <c r="G37" s="1">
-        <v>33</v>
-      </c>
-      <c r="H37" s="1">
-        <v>7</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W37" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t>Vein ID</t>
   </si>
@@ -749,10 +749,166 @@
     <t>venus_stone</t>
   </si>
   <si>
-    <t>mars_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 100 [1]</t>
+    <t>deep_chromite</t>
+  </si>
+  <si>
+    <t>redstone: 45</t>
+  </si>
+  <si>
+    <t>thorium: 25</t>
+  </si>
+  <si>
+    <t>uraninite: 20</t>
+  </si>
+  <si>
+    <t>cooperite: 25</t>
+  </si>
+  <si>
+    <t>nickel: 25</t>
+  </si>
+  <si>
+    <t>platinum: 15</t>
+  </si>
+  <si>
+    <t>mars_almandine</t>
+  </si>
+  <si>
+    <t>pyrope: 25</t>
+  </si>
+  <si>
+    <t>mars_apatite</t>
+  </si>
+  <si>
+    <t>mars_coal</t>
+  </si>
+  <si>
+    <t>coal: 50 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 50</t>
+  </si>
+  <si>
+    <t>mars_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 65 [1]</t>
+  </si>
+  <si>
+    <t>mars_galena</t>
+  </si>
+  <si>
+    <t>galena: 30 [1]</t>
+  </si>
+  <si>
+    <t>lead: 25</t>
+  </si>
+  <si>
+    <t>mars_gold</t>
+  </si>
+  <si>
+    <t>mars_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30 [1]</t>
+  </si>
+  <si>
+    <t>mars_neodynium</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [1]</t>
+  </si>
+  <si>
+    <t>mars_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 25 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 20</t>
+  </si>
+  <si>
+    <t>mars_pitchblende</t>
+  </si>
+  <si>
+    <t>pitchblende: 35 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 25</t>
+  </si>
+  <si>
+    <t>mars_quartzite</t>
+  </si>
+  <si>
+    <t>mars_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 20 [1]</t>
+  </si>
+  <si>
+    <t>mars_sapphire</t>
+  </si>
+  <si>
+    <t>green_sapphire: 5 [1]</t>
+  </si>
+  <si>
+    <t>bauxite: 20</t>
+  </si>
+  <si>
+    <t>magnetite: 20</t>
+  </si>
+  <si>
+    <t>gold: 55</t>
+  </si>
+  <si>
+    <t>mars_stibnite</t>
+  </si>
+  <si>
+    <t>mars_sulfur</t>
+  </si>
+  <si>
+    <t>mars_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 30 [1]</t>
+  </si>
+  <si>
+    <t>mars_tungsten</t>
+  </si>
+  <si>
+    <t>scheelite: 45 [2]</t>
+  </si>
+  <si>
+    <t>tungstate: 35</t>
+  </si>
+  <si>
+    <t>bismuth: 90 [1]</t>
+  </si>
+  <si>
+    <t>sulfur: 10</t>
+  </si>
+  <si>
+    <t>cassiterite: 60 [1]</t>
+  </si>
+  <si>
+    <t>surface_hematite</t>
+  </si>
+  <si>
+    <t>surface_nickel_galena</t>
+  </si>
+  <si>
+    <t>sphalerite: 15 [1]</t>
+  </si>
+  <si>
+    <t>silver: 10</t>
+  </si>
+  <si>
+    <t>cobaltite: 10</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 60 [1]</t>
+  </si>
+  <si>
+    <t>redstone: 5</t>
   </si>
   <si>
     <t>glacio_stone</t>
@@ -848,12 +1004,6 @@
     <t>moon_garnierite</t>
   </si>
   <si>
-    <t>garnierite: 25 [1]</t>
-  </si>
-  <si>
-    <t>nickel: 20</t>
-  </si>
-  <si>
     <t>pentlandite: 25 [1]</t>
   </si>
   <si>
@@ -863,12 +1013,6 @@
     <t>green_sapphire: 5</t>
   </si>
   <si>
-    <t>bauxite: 20</t>
-  </si>
-  <si>
-    <t>magnetite: 20</t>
-  </si>
-  <si>
     <t>moon_graphite</t>
   </si>
   <si>
@@ -920,9 +1064,6 @@
     <t>moon_monazite</t>
   </si>
   <si>
-    <t>bastnasite: 50 [1]</t>
-  </si>
-  <si>
     <t>olivine: 1</t>
   </si>
   <si>
@@ -977,9 +1118,6 @@
     <t>moon_sapphire</t>
   </si>
   <si>
-    <t>pyrope: 25</t>
-  </si>
-  <si>
     <t>olivine: 2</t>
   </si>
   <si>
@@ -998,24 +1136,12 @@
     <t>moon_sheldonite</t>
   </si>
   <si>
-    <t>cooperite: 25</t>
-  </si>
-  <si>
-    <t>platinum: 15</t>
-  </si>
-  <si>
-    <t>nickel: 25</t>
-  </si>
-  <si>
     <t>moon_silver</t>
   </si>
   <si>
     <t>silver: 45 [1]</t>
   </si>
   <si>
-    <t>lead: 25</t>
-  </si>
-  <si>
     <t>moon_sphalerite</t>
   </si>
   <si>
@@ -1184,9 +1310,6 @@
     <t>nether_lubricant</t>
   </si>
   <si>
-    <t>soapstone: 30 [1]</t>
-  </si>
-  <si>
     <t>talc: 20 [1]</t>
   </si>
   <si>
@@ -1211,9 +1334,6 @@
     <t>nether_manganese</t>
   </si>
   <si>
-    <t>grossular: 30 [1]</t>
-  </si>
-  <si>
     <t>spessartine: 20 [1]</t>
   </si>
   <si>
@@ -1316,9 +1436,6 @@
     <t>nether_scheelite</t>
   </si>
   <si>
-    <t>scheelite: 45 [2]</t>
-  </si>
-  <si>
     <t>lithium: 20 [1]</t>
   </si>
   <si>
@@ -1328,9 +1445,6 @@
     <t>nether_silver</t>
   </si>
   <si>
-    <t>galena: 30 [1]</t>
-  </si>
-  <si>
     <t>silver: 35 [1]</t>
   </si>
   <si>
@@ -1353,9 +1467,6 @@
   </si>
   <si>
     <t>pyrite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sphalerite: 15 [1]</t>
   </si>
   <si>
     <t>nether_sylvite</t>
@@ -6113,10 +6224,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.822014808654785" customWidth="1" style="3"/>
+    <col min="1" max="1" width="20.848892211914062" customWidth="1" style="3"/>
     <col min="2" max="2" width="14.972405433654785" customWidth="1" style="3"/>
     <col min="3" max="3" width="9.140625" customWidth="1" style="3"/>
     <col min="4" max="4" width="9.140625" customWidth="1" style="3"/>
@@ -6125,11 +6236,11 @@
     <col min="7" max="7" width="9.140625" customWidth="1" style="3"/>
     <col min="8" max="8" width="9.140625" customWidth="1" style="3"/>
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
-    <col min="10" max="10" width="16.645116806030273" customWidth="1" style="3"/>
-    <col min="11" max="11" width="9.140625" customWidth="1" style="3"/>
-    <col min="12" max="12" width="9.140625" customWidth="1" style="3"/>
-    <col min="13" max="13" width="9.140625" customWidth="1" style="3"/>
-    <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
+    <col min="10" max="10" width="20.201292037963867" customWidth="1" style="3"/>
+    <col min="11" max="11" width="23.763607025146484" customWidth="1" style="3"/>
+    <col min="12" max="12" width="19.039091110229492" customWidth="1" style="3"/>
+    <col min="13" max="13" width="18.38944435119629" customWidth="1" style="3"/>
+    <col min="14" max="14" width="12.393258094787598" customWidth="1" style="3"/>
     <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
     <col min="16" max="16" width="9.140625" customWidth="1" style="3"/>
     <col min="17" max="17" width="9.140625" customWidth="1" style="3"/>
@@ -6248,23 +6359,29 @@
         <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="D2" s="3">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="3">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="F2" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>245</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="O2" s="1" t="s">
         <v>37</v>
       </c>
@@ -6277,23 +6394,23 @@
       <c r="R2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>37</v>
+      <c r="S2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>37</v>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>37</v>
@@ -6301,13 +6418,1918 @@
       <c r="Z2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>37</v>
+      <c r="AA2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3">
+        <v>370</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E3" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>60</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3">
+        <v>370</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>60</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3">
+        <v>280</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>65</v>
+      </c>
+      <c r="H5" s="3">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3">
+        <v>220</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3">
+        <v>45</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3">
+        <v>215</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>55</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="3">
+        <v>220</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3">
+        <v>50</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3">
+        <v>215</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3">
+        <v>50</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3">
+        <v>210</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3">
+        <v>40</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3">
+        <v>220</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3">
+        <v>30</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3">
+        <v>215</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3">
+        <v>45</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="3">
+        <v>250</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
+        <v>55</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3">
+        <v>220</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>70</v>
+      </c>
+      <c r="G14" s="3">
+        <v>20</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3">
+        <v>210</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3">
+        <v>40</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3">
+        <v>210</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3">
+        <v>40</v>
+      </c>
+      <c r="H16" s="3">
+        <v>6</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3">
+        <v>230</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>70</v>
+      </c>
+      <c r="G17" s="3">
+        <v>40</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="3">
+        <v>210</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>70</v>
+      </c>
+      <c r="G18" s="3">
+        <v>40</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3">
+        <v>215</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>70</v>
+      </c>
+      <c r="G19" s="3">
+        <v>45</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3">
+        <v>230</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>70</v>
+      </c>
+      <c r="G20" s="3">
+        <v>42</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3">
+        <v>280</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>70</v>
+      </c>
+      <c r="G21" s="3">
+        <v>50</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="3">
+        <v>140</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>80</v>
+      </c>
+      <c r="F22" s="3">
+        <v>180</v>
+      </c>
+      <c r="G22" s="3">
+        <v>45</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3">
+        <v>135</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>80</v>
+      </c>
+      <c r="F23" s="3">
+        <v>180</v>
+      </c>
+      <c r="G23" s="3">
+        <v>45</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3">
+        <v>140</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>80</v>
+      </c>
+      <c r="F24" s="3">
+        <v>180</v>
+      </c>
+      <c r="G24" s="3">
+        <v>45</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="3">
+        <v>150</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>80</v>
+      </c>
+      <c r="F25" s="3">
+        <v>180</v>
+      </c>
+      <c r="G25" s="3">
+        <v>45</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3">
+        <v>140</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>80</v>
+      </c>
+      <c r="F26" s="3">
+        <v>180</v>
+      </c>
+      <c r="G26" s="3">
+        <v>45</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC26" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6415,16 +8437,16 @@
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="X1" s="4" t="s">
         <v>26</v>
@@ -6432,7 +8454,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -6453,16 +8475,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>90</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>36</v>
@@ -6497,7 +8519,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -6518,13 +8540,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>36</v>
@@ -6559,7 +8581,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>98</v>
@@ -6583,16 +8605,16 @@
         <v>10</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>211</v>
@@ -6630,7 +8652,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -6651,16 +8673,16 @@
         <v>40</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>36</v>
@@ -6695,7 +8717,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -6716,16 +8738,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>37</v>
@@ -6760,7 +8782,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -6784,16 +8806,16 @@
         <v>7</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>37</v>
@@ -6828,7 +8850,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -6849,16 +8871,16 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>124</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>126</v>
@@ -6896,7 +8918,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -6920,13 +8942,13 @@
         <v>10</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>130</v>
@@ -6964,7 +8986,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>98</v>
@@ -6988,13 +9010,13 @@
         <v>12</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>36</v>
@@ -7029,7 +9051,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7056,16 +9078,16 @@
         <v>136</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>289</v>
+        <v>337</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>201</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>36</v>
@@ -7100,7 +9122,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -7168,7 +9190,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>42</v>
@@ -7189,13 +9211,13 @@
         <v>70</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>59</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>61</v>
@@ -7236,7 +9258,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -7301,7 +9323,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -7322,7 +9344,7 @@
         <v>35</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>170</v>
@@ -7331,10 +9353,10 @@
         <v>171</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>36</v>
@@ -7369,7 +9391,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -7399,7 +9421,7 @@
         <v>66</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>36</v>
@@ -7434,7 +9456,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>300</v>
+        <v>348</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -7455,7 +9477,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>175</v>
@@ -7464,7 +9486,7 @@
         <v>176</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>37</v>
@@ -7499,7 +9521,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -7520,16 +9542,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>37</v>
@@ -7564,7 +9586,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -7585,16 +9607,16 @@
         <v>60</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>37</v>
@@ -7629,7 +9651,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -7659,7 +9681,7 @@
         <v>191</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>37</v>
@@ -7694,7 +9716,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -7715,16 +9737,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>37</v>
@@ -7759,7 +9781,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -7786,7 +9808,7 @@
         <v>71</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>73</v>
@@ -7795,7 +9817,7 @@
         <v>74</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>36</v>
@@ -7830,7 +9852,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>322</v>
+        <v>368</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -7851,13 +9873,13 @@
         <v>20</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>36</v>
@@ -7892,7 +9914,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -7916,13 +9938,13 @@
         <v>80</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>328</v>
+        <v>250</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>37</v>
@@ -7957,7 +9979,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -7981,13 +10003,13 @@
         <v>203</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>332</v>
+        <v>261</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>36</v>
@@ -8022,7 +10044,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -8043,10 +10065,10 @@
         <v>40</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>335</v>
+        <v>377</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>216</v>
@@ -8084,7 +10106,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>336</v>
+        <v>378</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>42</v>
@@ -8105,16 +10127,16 @@
         <v>40</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>221</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>37</v>
@@ -8149,7 +10171,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8307,16 +10329,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>19</v>
@@ -8333,7 +10355,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8357,7 +10379,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>36</v>
@@ -8389,7 +10411,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -8410,10 +10432,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>91</v>
@@ -8448,7 +10470,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -8472,13 +10494,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>96</v>
@@ -8513,7 +10535,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>98</v>
@@ -8537,13 +10559,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>211</v>
@@ -8578,7 +10600,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -8599,10 +10621,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>36</v>
@@ -8634,7 +10656,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -8655,16 +10677,16 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>113</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>37</v>
@@ -8696,7 +10718,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -8720,16 +10742,16 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>37</v>
@@ -8761,7 +10783,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -8782,13 +10804,13 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>120</v>
@@ -8823,7 +10845,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -8844,16 +10866,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>126</v>
@@ -8888,7 +10910,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -8909,10 +10931,10 @@
         <v>37</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>45</v>
@@ -8950,7 +10972,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -9012,7 +11034,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>98</v>
@@ -9036,13 +11058,13 @@
         <v>12</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>36</v>
@@ -9074,7 +11096,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9098,16 +11120,16 @@
         <v>9</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>138</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>36</v>
@@ -9139,7 +11161,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -9166,7 +11188,7 @@
         <v>49</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>51</v>
@@ -9204,7 +11226,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -9225,13 +11247,13 @@
         <v>40</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>148</v>
@@ -9266,7 +11288,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -9287,16 +11309,16 @@
         <v>41</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>389</v>
+        <v>264</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>157</v>
@@ -9331,7 +11353,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -9352,16 +11374,16 @@
         <v>39</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>162</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>62</v>
@@ -9396,7 +11418,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -9417,13 +11439,13 @@
         <v>45</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>398</v>
+        <v>284</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>399</v>
+        <v>439</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>167</v>
@@ -9458,7 +11480,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -9479,13 +11501,13 @@
         <v>41</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>403</v>
+        <v>443</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>36</v>
@@ -9517,7 +11539,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>404</v>
+        <v>444</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -9544,10 +11566,10 @@
         <v>65</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>405</v>
+        <v>445</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>36</v>
@@ -9579,7 +11601,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -9600,13 +11622,13 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>36</v>
@@ -9638,7 +11660,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -9659,10 +11681,10 @@
         <v>32</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>37</v>
@@ -9694,7 +11716,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -9715,13 +11737,13 @@
         <v>31</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>417</v>
+        <v>457</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>183</v>
@@ -9756,7 +11778,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -9812,7 +11834,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -9833,13 +11855,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>37</v>
@@ -9871,7 +11893,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>42</v>
@@ -9895,10 +11917,10 @@
         <v>189</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>36</v>
@@ -9930,7 +11952,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>42</v>
@@ -9951,13 +11973,13 @@
         <v>50</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>201</v>
@@ -9992,7 +12014,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -10022,10 +12044,10 @@
         <v>72</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>36</v>
@@ -10057,7 +12079,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>432</v>
+        <v>472</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -10078,13 +12100,13 @@
         <v>25</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>433</v>
+        <v>286</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>36</v>
@@ -10116,7 +12138,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -10146,7 +12168,7 @@
         <v>82</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>37</v>
@@ -10178,7 +12200,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>42</v>
@@ -10199,13 +12221,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>437</v>
+        <v>260</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>36</v>
@@ -10237,7 +12259,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>42</v>
@@ -10258,13 +12280,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>208</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>37</v>
@@ -10296,7 +12318,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>42</v>
@@ -10317,13 +12339,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>446</v>
+        <v>293</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>37</v>
@@ -10355,7 +12377,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>42</v>
@@ -10376,7 +12398,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>36</v>
@@ -10408,7 +12430,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>42</v>
@@ -10429,10 +12451,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>221</v>
@@ -10467,7 +12489,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1004,7 +1004,7 @@
     <t>moon_desh</t>
   </si>
   <si>
-    <t>desh: 25 [2]</t>
+    <t>desh: 25</t>
   </si>
   <si>
     <t>ilmenite: 30 [1]</t>
@@ -1169,10 +1169,13 @@
     <t>moon_sphalerite</t>
   </si>
   <si>
-    <t>desh: 15</t>
+    <t>desh: 10</t>
   </si>
   <si>
     <t>sphalerite: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 40</t>
   </si>
   <si>
     <t>moon_tetrahedrite</t>
@@ -10361,7 +10364,7 @@
         <v>385</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>36</v>
@@ -10396,7 +10399,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10417,16 +10420,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>222</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -10461,7 +10464,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10619,16 +10622,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>19</v>
@@ -10645,7 +10648,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10669,7 +10672,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>35</v>
@@ -10701,7 +10704,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10722,10 +10725,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10760,7 +10763,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10784,13 +10787,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10825,7 +10828,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10890,7 +10893,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -10911,10 +10914,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>35</v>
@@ -10946,7 +10949,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11008,7 +11011,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11029,16 +11032,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>114</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
@@ -11070,7 +11073,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11094,16 +11097,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>36</v>
@@ -11135,7 +11138,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11156,13 +11159,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>121</v>
@@ -11197,7 +11200,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11224,7 +11227,7 @@
         <v>277</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>338</v>
@@ -11262,7 +11265,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11283,10 +11286,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11324,7 +11327,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11386,7 +11389,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11410,13 +11413,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>35</v>
@@ -11448,7 +11451,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11472,10 +11475,10 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>139</v>
@@ -11513,7 +11516,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11540,7 +11543,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11578,7 +11581,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11599,13 +11602,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>149</v>
@@ -11640,7 +11643,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11664,13 +11667,13 @@
         <v>272</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>158</v>
@@ -11705,7 +11708,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11726,16 +11729,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>163</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11770,7 +11773,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11794,10 +11797,10 @@
         <v>290</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>168</v>
@@ -11832,7 +11835,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11856,10 +11859,10 @@
         <v>354</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>35</v>
@@ -11891,7 +11894,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -11918,10 +11921,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>35</v>
@@ -11953,7 +11956,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -11974,13 +11977,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -12012,7 +12015,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12033,7 +12036,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>36</v>
@@ -12065,7 +12068,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12086,13 +12089,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>184</v>
@@ -12127,7 +12130,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12186,7 +12189,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12207,13 +12210,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -12245,7 +12248,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12269,10 +12272,10 @@
         <v>190</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>35</v>
@@ -12304,7 +12307,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12328,10 +12331,10 @@
         <v>371</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>202</v>
@@ -12366,7 +12369,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12396,10 +12399,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>35</v>
@@ -12431,7 +12434,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12452,13 +12455,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>35</v>
@@ -12490,7 +12493,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12514,10 +12517,10 @@
         <v>264</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>35</v>
@@ -12549,7 +12552,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12570,13 +12573,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>209</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>36</v>
@@ -12608,7 +12611,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12629,13 +12632,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>36</v>
@@ -12667,7 +12670,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12688,7 +12691,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>35</v>
@@ -12720,7 +12723,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12741,10 +12744,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>222</v>
@@ -12779,7 +12782,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
   <si>
     <t>Vein ID</t>
   </si>
@@ -896,6 +896,9 @@
     <t>tungstate: 35</t>
   </si>
   <si>
+    <t>mars_surface_bismuthinite</t>
+  </si>
+  <si>
     <t>bismuth: 20 [1]</t>
   </si>
   <si>
@@ -908,6 +911,9 @@
     <t>gypsum: 10</t>
   </si>
   <si>
+    <t>mars_surface_cassiterite</t>
+  </si>
+  <si>
     <t>cassiterite: 55 [1]</t>
   </si>
   <si>
@@ -917,19 +923,22 @@
     <t>saltpeter: 10</t>
   </si>
   <si>
-    <t>surface_hematite</t>
+    <t>mars_surface_hematite</t>
   </si>
   <si>
     <t>calcite: 5</t>
   </si>
   <si>
-    <t>surface_nickel_galena</t>
+    <t>mars_surface_nickel_galena</t>
   </si>
   <si>
     <t>silver: 10</t>
   </si>
   <si>
     <t>cobaltite: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_tetrahedrite</t>
   </si>
   <si>
     <t>tetrahedrite: 60 [1]</t>
@@ -6263,7 +6272,7 @@
   <dimension ref="A1:AE27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.774301528930664" customWidth="1" style="3"/>
+    <col min="1" max="1" width="26.277278900146484" customWidth="1" style="3"/>
     <col min="2" max="2" width="14.972405433654785" customWidth="1" style="3"/>
     <col min="3" max="3" width="9.140625" customWidth="1" style="3"/>
     <col min="4" max="4" width="9.140625" customWidth="1" style="3"/>
@@ -8198,7 +8207,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8219,16 +8228,16 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -8284,7 +8293,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>228</v>
+        <v>298</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8305,13 +8314,13 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>35</v>
@@ -8367,7 +8376,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8397,7 +8406,7 @@
         <v>55</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>35</v>
@@ -8453,7 +8462,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8483,10 +8492,10 @@
         <v>204</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>35</v>
@@ -8542,7 +8551,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8563,7 +8572,7 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>242</v>
@@ -8572,7 +8581,7 @@
         <v>222</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>35</v>
@@ -8730,16 +8739,16 @@
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="X1" s="4" t="s">
         <v>26</v>
@@ -8747,7 +8756,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8768,16 +8777,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>35</v>
@@ -8812,7 +8821,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8833,13 +8842,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>35</v>
@@ -8874,7 +8883,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -8898,16 +8907,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>212</v>
@@ -8945,7 +8954,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -8966,16 +8975,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>35</v>
@@ -9010,7 +9019,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9075,7 +9084,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9096,16 +9105,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>36</v>
@@ -9140,7 +9149,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9164,16 +9173,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
@@ -9208,7 +9217,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9238,7 +9247,7 @@
         <v>125</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>127</v>
@@ -9276,7 +9285,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9306,7 +9315,7 @@
         <v>268</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>131</v>
@@ -9344,7 +9353,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9368,13 +9377,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>35</v>
@@ -9409,7 +9418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9436,16 +9445,16 @@
         <v>137</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>202</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>35</v>
@@ -9480,7 +9489,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9548,7 +9557,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9569,13 +9578,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9616,7 +9625,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9681,7 +9690,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9702,7 +9711,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>171</v>
@@ -9711,10 +9720,10 @@
         <v>172</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>35</v>
@@ -9749,7 +9758,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9779,7 +9788,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>35</v>
@@ -9814,7 +9823,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9844,7 +9853,7 @@
         <v>177</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>36</v>
@@ -9879,7 +9888,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -9900,16 +9909,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>36</v>
@@ -9944,7 +9953,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -9965,16 +9974,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>36</v>
@@ -10009,7 +10018,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10039,7 +10048,7 @@
         <v>192</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>36</v>
@@ -10074,7 +10083,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10095,16 +10104,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>36</v>
@@ -10139,7 +10148,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10175,7 +10184,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -10210,7 +10219,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10231,13 +10240,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>35</v>
@@ -10272,7 +10281,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10296,13 +10305,13 @@
         <v>204</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>265</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>35</v>
@@ -10337,7 +10346,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10358,13 +10367,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>36</v>
@@ -10399,7 +10408,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10420,16 +10429,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>222</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -10464,7 +10473,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10622,16 +10631,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>19</v>
@@ -10648,7 +10657,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10672,7 +10681,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>35</v>
@@ -10704,7 +10713,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10725,10 +10734,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10763,7 +10772,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10787,13 +10796,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10828,7 +10837,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10852,13 +10861,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>212</v>
@@ -10893,7 +10902,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -10914,10 +10923,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>35</v>
@@ -10949,7 +10958,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11011,7 +11020,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11032,16 +11041,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>114</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
@@ -11073,7 +11082,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11097,16 +11106,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>36</v>
@@ -11138,7 +11147,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11159,13 +11168,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>121</v>
@@ -11200,7 +11209,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11227,10 +11236,10 @@
         <v>277</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>127</v>
@@ -11265,7 +11274,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11286,10 +11295,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11327,7 +11336,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11389,7 +11398,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11413,13 +11422,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>35</v>
@@ -11451,7 +11460,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11475,16 +11484,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>139</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>35</v>
@@ -11516,7 +11525,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11543,7 +11552,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11581,7 +11590,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11602,13 +11611,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>149</v>
@@ -11643,7 +11652,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11667,13 +11676,13 @@
         <v>272</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>158</v>
@@ -11708,7 +11717,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11729,16 +11738,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>163</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11773,7 +11782,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11797,10 +11806,10 @@
         <v>290</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>168</v>
@@ -11835,7 +11844,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11856,13 +11865,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>35</v>
@@ -11894,7 +11903,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -11921,10 +11930,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>35</v>
@@ -11956,7 +11965,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -11977,13 +11986,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -12015,7 +12024,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12036,7 +12045,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>36</v>
@@ -12068,7 +12077,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12089,13 +12098,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>184</v>
@@ -12130,7 +12139,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12189,7 +12198,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12210,13 +12219,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -12248,7 +12257,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12272,10 +12281,10 @@
         <v>190</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>35</v>
@@ -12307,7 +12316,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12328,13 +12337,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>202</v>
@@ -12369,7 +12378,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12399,10 +12408,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>35</v>
@@ -12434,7 +12443,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12455,13 +12464,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>35</v>
@@ -12493,7 +12502,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12517,10 +12526,10 @@
         <v>264</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>35</v>
@@ -12552,7 +12561,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12573,13 +12582,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>209</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>36</v>
@@ -12611,7 +12620,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12632,13 +12641,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>36</v>
@@ -12670,7 +12679,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12691,7 +12700,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>35</v>
@@ -12723,7 +12732,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12744,10 +12753,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>222</v>
@@ -12782,7 +12791,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
   <si>
     <t>Vein ID</t>
   </si>
@@ -338,6 +338,9 @@
     <t>lead: 11</t>
   </si>
   <si>
+    <t>silver: 10</t>
+  </si>
+  <si>
     <t>normal_cassiterite</t>
   </si>
   <si>
@@ -827,6 +830,21 @@
     <t>electrotine: 20</t>
   </si>
   <si>
+    <t>mars_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 45 [1]</t>
+  </si>
+  <si>
+    <t>coal: 25</t>
+  </si>
+  <si>
+    <t>diamond: 20</t>
+  </si>
+  <si>
+    <t>hematite: 10</t>
+  </si>
+  <si>
     <t>mars_hematite</t>
   </si>
   <si>
@@ -911,9 +929,6 @@
     <t>bismuth: 20 [1]</t>
   </si>
   <si>
-    <t>hematite: 10</t>
-  </si>
-  <si>
     <t>sulfur: 10</t>
   </si>
   <si>
@@ -941,9 +956,6 @@
     <t>mars_surface_nickel_galena</t>
   </si>
   <si>
-    <t>silver: 10</t>
-  </si>
-  <si>
     <t>cobaltite: 10</t>
   </si>
   <si>
@@ -1317,9 +1329,6 @@
   </si>
   <si>
     <t>nether_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 45 [1]</t>
   </si>
   <si>
     <t>diamond: 40 [1]</t>
@@ -2534,7 +2543,7 @@
         <v>-20</v>
       </c>
       <c r="G10" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>72</v>
@@ -3210,6 +3219,9 @@
       <c r="L17" s="3" t="s">
         <v>106</v>
       </c>
+      <c r="M17" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
       </c>
@@ -3273,7 +3285,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -3294,10 +3306,10 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -3362,7 +3374,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -3383,7 +3395,7 @@
         <v>60</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
@@ -3448,7 +3460,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -3469,16 +3481,16 @@
         <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -3543,7 +3555,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -3564,16 +3576,16 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -3638,7 +3650,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -3659,19 +3671,19 @@
         <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -3736,7 +3748,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -3763,13 +3775,13 @@
         <v>47</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>36</v>
@@ -3834,7 +3846,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>38</v>
@@ -3858,13 +3870,13 @@
         <v>6</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -3929,7 +3941,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>38</v>
@@ -3953,16 +3965,16 @@
         <v>9</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -4027,7 +4039,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -4048,13 +4060,13 @@
         <v>40</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>55</v>
@@ -4122,7 +4134,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -4143,16 +4155,16 @@
         <v>40</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -4217,7 +4229,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -4238,16 +4250,16 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -4312,7 +4324,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -4333,19 +4345,19 @@
         <v>36</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -4410,7 +4422,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
@@ -4431,16 +4443,16 @@
         <v>30</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -4505,7 +4517,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -4526,16 +4538,16 @@
         <v>30</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>36</v>
@@ -4600,7 +4612,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -4621,16 +4633,16 @@
         <v>36</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -4695,7 +4707,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -4716,13 +4728,13 @@
         <v>35</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>35</v>
@@ -4787,7 +4799,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -4808,7 +4820,7 @@
         <v>55</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>35</v>
@@ -4873,7 +4885,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -4894,16 +4906,16 @@
         <v>26</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>36</v>
@@ -4968,7 +4980,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -4989,13 +5001,13 @@
         <v>40</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>35</v>
@@ -5060,7 +5072,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>
@@ -5081,13 +5093,13 @@
         <v>40</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>35</v>
@@ -5152,7 +5164,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>38</v>
@@ -5176,16 +5188,16 @@
         <v>4</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>35</v>
@@ -5250,7 +5262,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>31</v>
@@ -5271,16 +5283,16 @@
         <v>40</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>35</v>
@@ -5345,7 +5357,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>31</v>
@@ -5366,13 +5378,13 @@
         <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>35</v>
@@ -5437,7 +5449,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>31</v>
@@ -5458,13 +5470,13 @@
         <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>36</v>
@@ -5529,7 +5541,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>38</v>
@@ -5553,16 +5565,16 @@
         <v>6</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>35</v>
@@ -5627,7 +5639,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
@@ -5648,13 +5660,13 @@
         <v>45</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>36</v>
@@ -5719,7 +5731,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
@@ -5740,13 +5752,13 @@
         <v>40</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>35</v>
@@ -5811,7 +5823,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
@@ -5832,16 +5844,16 @@
         <v>50</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>35</v>
@@ -5906,7 +5918,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
@@ -5927,10 +5939,10 @@
         <v>50</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>35</v>
@@ -5995,7 +6007,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>31</v>
@@ -6016,16 +6028,16 @@
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>36</v>
@@ -6090,7 +6102,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
@@ -6111,13 +6123,13 @@
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>36</v>
@@ -6182,7 +6194,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
@@ -6203,13 +6215,13 @@
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>35</v>
@@ -6279,7 +6291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.277278900146484" customWidth="1" style="3"/>
@@ -6398,10 +6410,10 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>26</v>
@@ -6410,12 +6422,12 @@
         <v>28</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6436,13 +6448,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6498,7 +6510,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6522,7 +6534,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6581,7 +6593,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6605,13 +6617,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6667,7 +6679,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6694,7 +6706,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -6703,7 +6715,7 @@
         <v>79</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -6759,7 +6771,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -6789,7 +6801,7 @@
         <v>92</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -6845,7 +6857,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>99</v>
@@ -6875,7 +6887,7 @@
         <v>101</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -6931,7 +6943,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -6952,10 +6964,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7011,7 +7023,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7032,16 +7044,16 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -7097,7 +7109,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7118,16 +7130,16 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -7183,7 +7195,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7204,16 +7216,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -7269,13 +7281,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D12" s="3">
         <v>0.4</v>
@@ -7284,28 +7296,31 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>70</v>
-      </c>
-      <c r="G12" s="3">
-        <v>40</v>
+        <v>120</v>
+      </c>
+      <c r="H12" s="3">
+        <v>60</v>
+      </c>
+      <c r="I12" s="3">
+        <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>36</v>
+      <c r="Q12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>35</v>
@@ -7313,29 +7328,29 @@
       <c r="S12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>36</v>
+      <c r="T12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>36</v>
+      <c r="W12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB12" s="1" t="s">
         <v>36</v>
@@ -7349,22 +7364,22 @@
       <c r="AE12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF12" s="2" t="s">
-        <v>35</v>
+      <c r="AF12" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="3">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D13" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -7376,28 +7391,22 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>272</v>
+        <v>145</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>273</v>
+        <v>144</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>35</v>
+      <c r="Q13" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>35</v>
@@ -7414,8 +7423,8 @@
       <c r="V13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W13" s="1" t="s">
-        <v>36</v>
+      <c r="W13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X13" s="1" t="s">
         <v>36</v>
@@ -7423,8 +7432,8 @@
       <c r="Y13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z13" s="1" t="s">
-        <v>36</v>
+      <c r="Z13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA13" s="1" t="s">
         <v>36</v>
@@ -7438,8 +7447,8 @@
       <c r="AD13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>36</v>
+      <c r="AE13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF13" s="2" t="s">
         <v>35</v>
@@ -7447,16 +7456,16 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="3">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D14" s="3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -7465,40 +7474,46 @@
         <v>70</v>
       </c>
       <c r="G14" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>114</v>
+        <v>280</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>35</v>
+      <c r="Q14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>36</v>
@@ -7506,40 +7521,40 @@
       <c r="X14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>35</v>
+      <c r="Y14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC14" s="2" t="s">
-        <v>35</v>
+      <c r="AC14" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>36</v>
+      <c r="AE14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D15" s="3">
         <v>0.4</v>
@@ -7551,19 +7566,19 @@
         <v>70</v>
       </c>
       <c r="G15" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -7574,61 +7589,61 @@
       <c r="R15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>36</v>
+      <c r="S15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>36</v>
+      <c r="V15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC15" s="1" t="s">
-        <v>36</v>
+      <c r="AC15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>35</v>
+      <c r="AE15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="3">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D16" s="3">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -7637,52 +7652,55 @@
         <v>70</v>
       </c>
       <c r="G16" s="3">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>283</v>
+        <v>126</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>35</v>
+      <c r="Q16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>36</v>
+      <c r="T16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>35</v>
+      <c r="W16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB16" s="1" t="s">
         <v>36</v>
@@ -7696,22 +7714,22 @@
       <c r="AE16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF16" s="1" t="s">
-        <v>36</v>
+      <c r="AF16" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D17" s="3">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -7720,19 +7738,16 @@
         <v>70</v>
       </c>
       <c r="G17" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>187</v>
+        <v>250</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7740,35 +7755,35 @@
       <c r="Q17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>36</v>
+      <c r="R17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>36</v>
@@ -7788,16 +7803,16 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3">
         <v>210</v>
       </c>
       <c r="D18" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -7808,20 +7823,17 @@
       <c r="G18" s="3">
         <v>40</v>
       </c>
-      <c r="H18" s="3">
-        <v>6</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -7844,8 +7856,8 @@
       <c r="V18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W18" s="1" t="s">
-        <v>36</v>
+      <c r="W18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>35</v>
@@ -7868,8 +7880,8 @@
       <c r="AD18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE18" s="2" t="s">
-        <v>35</v>
+      <c r="AE18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>36</v>
@@ -7877,10 +7889,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3">
         <v>210</v>
@@ -7897,23 +7909,26 @@
       <c r="G19" s="3">
         <v>40</v>
       </c>
+      <c r="H19" s="3">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="s">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q19" s="1" t="s">
-        <v>36</v>
+      <c r="Q19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>36</v>
@@ -7921,29 +7936,29 @@
       <c r="S19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T19" s="2" t="s">
-        <v>35</v>
+      <c r="T19" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V19" s="1" t="s">
-        <v>36</v>
+      <c r="V19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>35</v>
+      <c r="X19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB19" s="1" t="s">
         <v>36</v>
@@ -7954,8 +7969,8 @@
       <c r="AD19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>36</v>
+      <c r="AE19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>36</v>
@@ -7963,16 +7978,16 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="3">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D20" s="3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -7981,19 +7996,19 @@
         <v>70</v>
       </c>
       <c r="G20" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>35</v>
@@ -8019,14 +8034,14 @@
       <c r="W20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X20" s="2" t="s">
-        <v>35</v>
+      <c r="X20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z20" s="1" t="s">
-        <v>36</v>
+      <c r="Z20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA20" s="2" t="s">
         <v>35</v>
@@ -8034,14 +8049,14 @@
       <c r="AB20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC20" s="2" t="s">
-        <v>35</v>
+      <c r="AC20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE20" s="2" t="s">
-        <v>35</v>
+      <c r="AE20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>36</v>
@@ -8049,16 +8064,16 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="3">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D21" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -8067,19 +8082,19 @@
         <v>70</v>
       </c>
       <c r="G21" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>166</v>
+        <v>296</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -8093,17 +8108,17 @@
       <c r="S21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>36</v>
+      <c r="T21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>35</v>
+      <c r="V21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>35</v>
@@ -8111,23 +8126,23 @@
       <c r="Y21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>36</v>
+      <c r="Z21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC21" s="1" t="s">
-        <v>36</v>
+      <c r="AC21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE21" s="1" t="s">
-        <v>36</v>
+      <c r="AE21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF21" s="1" t="s">
         <v>36</v>
@@ -8135,16 +8150,16 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="3">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="D22" s="3">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -8153,19 +8168,19 @@
         <v>70</v>
       </c>
       <c r="G22" s="3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8191,11 +8206,11 @@
       <c r="W22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>35</v>
+      <c r="X22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>35</v>
@@ -8203,8 +8218,8 @@
       <c r="AA22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB22" s="2" t="s">
-        <v>35</v>
+      <c r="AB22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>36</v>
@@ -8215,43 +8230,43 @@
       <c r="AE22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF22" s="2" t="s">
-        <v>35</v>
+      <c r="AF22" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="3">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="D23" s="3">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="E23" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G23" s="3">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -8268,29 +8283,29 @@
       <c r="T23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="U23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>36</v>
+      <c r="U23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>36</v>
+      <c r="Y23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB23" s="1" t="s">
-        <v>36</v>
+      <c r="AB23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC23" s="1" t="s">
         <v>36</v>
@@ -8301,19 +8316,19 @@
       <c r="AE23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF23" s="1" t="s">
-        <v>36</v>
+      <c r="AF23" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D24" s="3">
         <v>0.25</v>
@@ -8328,14 +8343,17 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>304</v>
       </c>
+      <c r="M24" s="3" t="s">
+        <v>305</v>
+      </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
       </c>
@@ -8390,13 +8408,13 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="3">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3">
         <v>0.25</v>
@@ -8411,16 +8429,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>143</v>
+        <v>308</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8476,13 +8491,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3">
         <v>0.25</v>
@@ -8497,19 +8512,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>280</v>
+        <v>144</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8565,13 +8577,13 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3">
         <v>0.25</v>
@@ -8586,16 +8598,19 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>311</v>
+        <v>219</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>312</v>
+        <v>107</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8646,6 +8661,92 @@
         <v>36</v>
       </c>
       <c r="AF27" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3">
+        <v>140</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>80</v>
+      </c>
+      <c r="F28" s="3">
+        <v>180</v>
+      </c>
+      <c r="G28" s="3">
+        <v>45</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF28" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8754,16 +8855,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8771,7 +8872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8792,16 +8893,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -8836,7 +8937,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8857,13 +8958,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -8898,7 +8999,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -8922,19 +9023,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -8969,7 +9070,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -8990,16 +9091,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9034,7 +9135,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9058,13 +9159,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9099,7 +9200,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9120,16 +9221,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9164,7 +9265,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9188,16 +9289,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9232,7 +9333,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9253,19 +9354,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -9300,7 +9401,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9324,16 +9425,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -9368,7 +9469,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9392,13 +9493,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9433,7 +9534,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9457,19 +9558,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9504,7 +9605,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9525,19 +9626,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>35</v>
@@ -9572,7 +9673,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9593,13 +9694,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9640,7 +9741,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9661,16 +9762,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
@@ -9705,7 +9806,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9726,19 +9827,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9773,7 +9874,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9803,7 +9904,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -9838,7 +9939,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9859,16 +9960,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -9903,7 +10004,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -9924,16 +10025,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -9968,7 +10069,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -9989,16 +10090,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10033,7 +10134,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10054,16 +10155,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10098,7 +10199,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10119,16 +10220,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10163,7 +10264,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10190,7 +10291,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10199,7 +10300,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10234,7 +10335,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10255,13 +10356,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10296,7 +10397,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10317,16 +10418,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10361,7 +10462,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10382,13 +10483,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10423,7 +10524,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10444,16 +10545,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10488,7 +10589,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10647,16 +10748,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10673,7 +10774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10697,7 +10798,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10729,7 +10830,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10750,10 +10851,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10788,7 +10889,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10812,13 +10913,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10853,7 +10954,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10877,16 +10978,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>36</v>
@@ -10918,7 +11019,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -10939,10 +11040,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -10974,7 +11075,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11004,7 +11105,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11036,7 +11137,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11057,16 +11158,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11098,7 +11199,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11122,16 +11223,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11163,7 +11264,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11184,16 +11285,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -11225,7 +11326,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11246,19 +11347,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -11290,7 +11391,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11311,10 +11412,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11352,7 +11453,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11414,7 +11515,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11438,13 +11539,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>434</v>
+        <v>272</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11476,7 +11577,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11500,16 +11601,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11541,7 +11642,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11568,7 +11669,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11606,7 +11707,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11627,16 +11728,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -11668,7 +11769,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11689,19 +11790,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -11733,7 +11834,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11754,16 +11855,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11798,7 +11899,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11819,16 +11920,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -11860,7 +11961,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11881,13 +11982,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -11919,7 +12020,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -11946,10 +12047,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -11981,7 +12082,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12002,13 +12103,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12040,7 +12141,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12061,7 +12162,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12093,7 +12194,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12114,16 +12215,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>36</v>
@@ -12155,13 +12256,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="3">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D26" s="3">
         <v>0.55</v>
@@ -12173,7 +12274,7 @@
         <v>128</v>
       </c>
       <c r="G26" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>72</v>
@@ -12214,7 +12315,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12235,13 +12336,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12273,7 +12374,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12294,13 +12395,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12332,7 +12433,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12353,16 +12454,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -12394,7 +12495,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12424,10 +12525,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12459,7 +12560,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12480,13 +12581,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12518,7 +12619,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12539,13 +12640,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12577,7 +12678,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12598,13 +12699,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12636,7 +12737,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12657,13 +12758,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12695,7 +12796,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12716,7 +12817,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12748,7 +12849,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12769,13 +12870,13 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>35</v>
@@ -12807,7 +12908,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t>Vein ID</t>
   </si>
@@ -914,481 +914,493 @@
     <t>mars_tantalite</t>
   </si>
   <si>
+    <t>grossular: 10</t>
+  </si>
+  <si>
+    <t>spessartine: 10</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tantalite: 35 [1]</t>
+  </si>
+  <si>
+    <t>mars_tungsten</t>
+  </si>
+  <si>
+    <t>tungstate: 35</t>
+  </si>
+  <si>
+    <t>mars_surface_bismuthinite</t>
+  </si>
+  <si>
+    <t>bismuth: 20 [1]</t>
+  </si>
+  <si>
+    <t>sulfur: 10</t>
+  </si>
+  <si>
+    <t>gypsum: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 55 [1]</t>
+  </si>
+  <si>
+    <t>tin: 35</t>
+  </si>
+  <si>
+    <t>saltpeter: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_hematite</t>
+  </si>
+  <si>
+    <t>calcite: 5</t>
+  </si>
+  <si>
+    <t>mars_surface_nickel_galena</t>
+  </si>
+  <si>
+    <t>cobaltite: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 60 [1]</t>
+  </si>
+  <si>
+    <t>redstone: 5</t>
+  </si>
+  <si>
+    <t>glacio_stone</t>
+  </si>
+  <si>
+    <t>moon_deepslate</t>
+  </si>
+  <si>
+    <t>moon_stone</t>
+  </si>
+  <si>
+    <t>moon_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 25</t>
+  </si>
+  <si>
+    <t>pyrochlore: 40 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 5</t>
+  </si>
+  <si>
+    <t>moon_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 35 [1]</t>
+  </si>
+  <si>
+    <t>ilmenite: 40 [1]</t>
+  </si>
+  <si>
+    <t>armalcolite: 20</t>
+  </si>
+  <si>
+    <t>moon_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium: 35 [1]</t>
+  </si>
+  <si>
+    <t>emerald: 50 [2]</t>
+  </si>
+  <si>
+    <t>thorium: 1</t>
+  </si>
+  <si>
+    <t>moon_cassiterite</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 30 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 5</t>
+  </si>
+  <si>
+    <t>cassiterite: 35 [1]</t>
+  </si>
+  <si>
+    <t>tin: 15</t>
+  </si>
+  <si>
+    <t>moon_sheldonite</t>
+  </si>
+  <si>
+    <t>moon_desh</t>
+  </si>
+  <si>
+    <t>desh: 25</t>
+  </si>
+  <si>
+    <t>ilmenite: 30 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 25</t>
+  </si>
+  <si>
+    <t>moon_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10</t>
+  </si>
+  <si>
+    <t>yellow_garnet: 15</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [1]</t>
+  </si>
+  <si>
+    <t>opal: 40 [1]</t>
+  </si>
+  <si>
+    <t>moon_garnierite</t>
+  </si>
+  <si>
+    <t>pentlandite: 25 [1]</t>
+  </si>
+  <si>
+    <t>moon_gold</t>
+  </si>
+  <si>
+    <t>magnetite: 20</t>
+  </si>
+  <si>
+    <t>moon_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 50 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 35</t>
+  </si>
+  <si>
+    <t>olivine: 10</t>
+  </si>
+  <si>
+    <t>moon_gypsum</t>
+  </si>
+  <si>
+    <t>calcite: 25</t>
+  </si>
+  <si>
+    <t>gypsum: 35 [1]</t>
+  </si>
+  <si>
+    <t>moon_lubricant</t>
+  </si>
+  <si>
+    <t>moon_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 25</t>
+  </si>
+  <si>
+    <t>chromite: 40 [2]</t>
+  </si>
+  <si>
+    <t>moon_manganese</t>
+  </si>
+  <si>
+    <t>moon_mica</t>
+  </si>
+  <si>
+    <t>kyanite: 35 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 15</t>
+  </si>
+  <si>
+    <t>moon_molybdenum</t>
+  </si>
+  <si>
+    <t>moon_monazite</t>
+  </si>
+  <si>
+    <t>olivine: 1</t>
+  </si>
+  <si>
+    <t>moon_pyrolusite</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [2]</t>
+  </si>
+  <si>
+    <t>cobaltite: 25</t>
+  </si>
+  <si>
+    <t>cobalt: 25</t>
+  </si>
+  <si>
+    <t>tantalite: 15</t>
+  </si>
+  <si>
+    <t>moon_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 20</t>
+  </si>
+  <si>
+    <t>certus_quartz: 45 [2]</t>
+  </si>
+  <si>
+    <t>nether_quartz: 30 [1]</t>
+  </si>
+  <si>
+    <t>barite: 5</t>
+  </si>
+  <si>
+    <t>moon_redstone</t>
+  </si>
+  <si>
+    <t>moon_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35 [1]</t>
+  </si>
+  <si>
+    <t>soapstone: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 45</t>
+  </si>
+  <si>
+    <t>talc: 15</t>
+  </si>
+  <si>
+    <t>moon_sapphire</t>
+  </si>
+  <si>
+    <t>olivine: 2</t>
+  </si>
+  <si>
+    <t>moon_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tungstate: 50 [2]</t>
+  </si>
+  <si>
+    <t>lithium: 10</t>
+  </si>
+  <si>
+    <t>moon_silver</t>
+  </si>
+  <si>
+    <t>silver: 45 [1]</t>
+  </si>
+  <si>
+    <t>moon_sphalerite</t>
+  </si>
+  <si>
+    <t>desh: 10</t>
+  </si>
+  <si>
+    <t>sphalerite: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 40</t>
+  </si>
+  <si>
+    <t>moon_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>copper: 15</t>
+  </si>
+  <si>
+    <t>chalcocite: 25</t>
+  </si>
+  <si>
+    <t>moon_topaz</t>
+  </si>
+  <si>
+    <t>blackstone</t>
+  </si>
+  <si>
+    <t>deepslate</t>
+  </si>
+  <si>
+    <t>dripstone</t>
+  </si>
+  <si>
+    <t>nether_anthracite</t>
+  </si>
+  <si>
+    <t>anthracite: 100</t>
+  </si>
+  <si>
+    <t>nether_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 50 [2]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 35 [1]</t>
+  </si>
+  <si>
+    <t>nether_basaltic_sands</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>fullers_earth: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_beryllium</t>
+  </si>
+  <si>
+    <t>nether_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 40 [2]</t>
+  </si>
+  <si>
+    <t>tin: 60 [2]</t>
+  </si>
+  <si>
+    <t>nether_sheldonite</t>
+  </si>
+  <si>
+    <t>nether_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 10 [1]</t>
+  </si>
+  <si>
+    <t>copper: 65 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10 [1]</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [2]</t>
+  </si>
+  <si>
+    <t>opal: 40 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>garnet_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_garnierite</t>
+  </si>
+  <si>
+    <t>cobaltite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_goethite</t>
+  </si>
+  <si>
+    <t>goethite: 50 [3]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_gold</t>
+  </si>
+  <si>
+    <t>nether_graphite</t>
+  </si>
+  <si>
+    <t>diamond: 40 [1]</t>
+  </si>
+  <si>
+    <t>coal: 15</t>
+  </si>
+  <si>
+    <t>nether_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20 [1]</t>
+  </si>
+  <si>
+    <t>calcite: 30 [1]</t>
+  </si>
+  <si>
+    <t>nether_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 35 [3]</t>
+  </si>
+  <si>
+    <t>nether_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 25 [1]</t>
+  </si>
+  <si>
+    <t>lapis: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30 [1]</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>pentlandite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 10</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 15 [1]</t>
+  </si>
+  <si>
+    <t>gold: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_manganese</t>
+  </si>
+  <si>
     <t>grossular: 30 [1]</t>
-  </si>
-  <si>
-    <t>mars_tungsten</t>
-  </si>
-  <si>
-    <t>tungstate: 35</t>
-  </si>
-  <si>
-    <t>mars_surface_bismuthinite</t>
-  </si>
-  <si>
-    <t>bismuth: 20 [1]</t>
-  </si>
-  <si>
-    <t>sulfur: 10</t>
-  </si>
-  <si>
-    <t>gypsum: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 55 [1]</t>
-  </si>
-  <si>
-    <t>tin: 35</t>
-  </si>
-  <si>
-    <t>saltpeter: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_hematite</t>
-  </si>
-  <si>
-    <t>calcite: 5</t>
-  </si>
-  <si>
-    <t>mars_surface_nickel_galena</t>
-  </si>
-  <si>
-    <t>cobaltite: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 60 [1]</t>
-  </si>
-  <si>
-    <t>redstone: 5</t>
-  </si>
-  <si>
-    <t>glacio_stone</t>
-  </si>
-  <si>
-    <t>moon_deepslate</t>
-  </si>
-  <si>
-    <t>moon_stone</t>
-  </si>
-  <si>
-    <t>moon_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 25</t>
-  </si>
-  <si>
-    <t>pyrochlore: 40 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 5</t>
-  </si>
-  <si>
-    <t>moon_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 35 [1]</t>
-  </si>
-  <si>
-    <t>ilmenite: 40 [1]</t>
-  </si>
-  <si>
-    <t>armalcolite: 20</t>
-  </si>
-  <si>
-    <t>moon_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium: 35 [1]</t>
-  </si>
-  <si>
-    <t>emerald: 50 [2]</t>
-  </si>
-  <si>
-    <t>thorium: 1</t>
-  </si>
-  <si>
-    <t>moon_cassiterite</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 30 [1]</t>
-  </si>
-  <si>
-    <t>zeolite: 5</t>
-  </si>
-  <si>
-    <t>cassiterite: 35 [1]</t>
-  </si>
-  <si>
-    <t>tin: 15</t>
-  </si>
-  <si>
-    <t>moon_sheldonite</t>
-  </si>
-  <si>
-    <t>moon_desh</t>
-  </si>
-  <si>
-    <t>desh: 25</t>
-  </si>
-  <si>
-    <t>ilmenite: 30 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 25</t>
-  </si>
-  <si>
-    <t>moon_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10</t>
-  </si>
-  <si>
-    <t>yellow_garnet: 15</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [1]</t>
-  </si>
-  <si>
-    <t>opal: 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_garnierite</t>
-  </si>
-  <si>
-    <t>pentlandite: 25 [1]</t>
-  </si>
-  <si>
-    <t>moon_gold</t>
-  </si>
-  <si>
-    <t>magnetite: 20</t>
-  </si>
-  <si>
-    <t>moon_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 50 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 35</t>
-  </si>
-  <si>
-    <t>olivine: 10</t>
-  </si>
-  <si>
-    <t>moon_gypsum</t>
-  </si>
-  <si>
-    <t>calcite: 25</t>
-  </si>
-  <si>
-    <t>gypsum: 35 [1]</t>
-  </si>
-  <si>
-    <t>moon_lubricant</t>
-  </si>
-  <si>
-    <t>moon_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 25</t>
-  </si>
-  <si>
-    <t>chromite: 40 [2]</t>
-  </si>
-  <si>
-    <t>moon_manganese</t>
-  </si>
-  <si>
-    <t>moon_mica</t>
-  </si>
-  <si>
-    <t>kyanite: 35 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 15</t>
-  </si>
-  <si>
-    <t>moon_molybdenum</t>
-  </si>
-  <si>
-    <t>moon_monazite</t>
-  </si>
-  <si>
-    <t>olivine: 1</t>
-  </si>
-  <si>
-    <t>moon_pyrolusite</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40 [2]</t>
-  </si>
-  <si>
-    <t>cobaltite: 25</t>
-  </si>
-  <si>
-    <t>cobalt: 25</t>
-  </si>
-  <si>
-    <t>tantalite: 15</t>
-  </si>
-  <si>
-    <t>moon_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 20</t>
-  </si>
-  <si>
-    <t>certus_quartz: 45 [2]</t>
-  </si>
-  <si>
-    <t>nether_quartz: 30 [1]</t>
-  </si>
-  <si>
-    <t>barite: 5</t>
-  </si>
-  <si>
-    <t>moon_redstone</t>
-  </si>
-  <si>
-    <t>moon_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35 [1]</t>
-  </si>
-  <si>
-    <t>soapstone: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 45</t>
-  </si>
-  <si>
-    <t>talc: 15</t>
-  </si>
-  <si>
-    <t>moon_sapphire</t>
-  </si>
-  <si>
-    <t>olivine: 2</t>
-  </si>
-  <si>
-    <t>moon_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tungstate: 50 [2]</t>
-  </si>
-  <si>
-    <t>lithium: 10</t>
-  </si>
-  <si>
-    <t>moon_silver</t>
-  </si>
-  <si>
-    <t>silver: 45 [1]</t>
-  </si>
-  <si>
-    <t>moon_sphalerite</t>
-  </si>
-  <si>
-    <t>desh: 10</t>
-  </si>
-  <si>
-    <t>sphalerite: 50 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 40</t>
-  </si>
-  <si>
-    <t>moon_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 40 [1]</t>
-  </si>
-  <si>
-    <t>copper: 15</t>
-  </si>
-  <si>
-    <t>chalcocite: 25</t>
-  </si>
-  <si>
-    <t>moon_topaz</t>
-  </si>
-  <si>
-    <t>blackstone</t>
-  </si>
-  <si>
-    <t>deepslate</t>
-  </si>
-  <si>
-    <t>dripstone</t>
-  </si>
-  <si>
-    <t>nether_anthracite</t>
-  </si>
-  <si>
-    <t>anthracite: 100</t>
-  </si>
-  <si>
-    <t>nether_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 50 [2]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_basaltic_sands</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>granitic_mineral_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>fullers_earth: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_beryllium</t>
-  </si>
-  <si>
-    <t>nether_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 40 [2]</t>
-  </si>
-  <si>
-    <t>tin: 60 [2]</t>
-  </si>
-  <si>
-    <t>nether_sheldonite</t>
-  </si>
-  <si>
-    <t>nether_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 10 [1]</t>
-  </si>
-  <si>
-    <t>copper: 65 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10 [1]</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [2]</t>
-  </si>
-  <si>
-    <t>opal: 40 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>garnet_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_garnierite</t>
-  </si>
-  <si>
-    <t>cobaltite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_goethite</t>
-  </si>
-  <si>
-    <t>goethite: 50 [3]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_gold</t>
-  </si>
-  <si>
-    <t>nether_graphite</t>
-  </si>
-  <si>
-    <t>diamond: 40 [1]</t>
-  </si>
-  <si>
-    <t>coal: 15</t>
-  </si>
-  <si>
-    <t>nether_gypsum</t>
-  </si>
-  <si>
-    <t>borax: 20 [1]</t>
-  </si>
-  <si>
-    <t>calcite: 30 [1]</t>
-  </si>
-  <si>
-    <t>nether_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 35 [3]</t>
-  </si>
-  <si>
-    <t>nether_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sodalite: 25 [1]</t>
-  </si>
-  <si>
-    <t>lapis: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30 [1]</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>pentlandite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 10</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 15 [1]</t>
-  </si>
-  <si>
-    <t>gold: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_manganese</t>
   </si>
   <si>
     <t>spessartine: 20 [1]</t>
@@ -8174,13 +8186,13 @@
         <v>299</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>167</v>
+        <v>300</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8236,7 +8248,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8260,7 +8272,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>83</v>
@@ -8322,7 +8334,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8343,16 +8355,16 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>275</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8408,7 +8420,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8429,13 +8441,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8491,7 +8503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8521,7 +8533,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8577,7 +8589,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8610,7 +8622,7 @@
         <v>107</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8666,7 +8678,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8687,7 +8699,7 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>243</v>
@@ -8696,7 +8708,7 @@
         <v>223</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8855,16 +8867,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8872,7 +8884,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8893,16 +8905,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -8937,7 +8949,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8958,13 +8970,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -8999,7 +9011,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9023,16 +9035,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>213</v>
@@ -9070,7 +9082,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9091,16 +9103,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9135,7 +9147,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9200,7 +9212,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9221,16 +9233,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9265,7 +9277,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9289,16 +9301,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9333,7 +9345,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9363,7 +9375,7 @@
         <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>128</v>
@@ -9401,7 +9413,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9431,7 +9443,7 @@
         <v>269</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>132</v>
@@ -9469,7 +9481,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9493,13 +9505,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9534,7 +9546,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9561,16 +9573,16 @@
         <v>138</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9605,7 +9617,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9673,7 +9685,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9694,13 +9706,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9741,7 +9753,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9806,7 +9818,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9827,7 +9839,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>172</v>
@@ -9836,10 +9848,10 @@
         <v>173</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9874,7 +9886,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9904,7 +9916,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -9939,7 +9951,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9969,7 +9981,7 @@
         <v>178</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10004,7 +10016,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10025,16 +10037,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10069,7 +10081,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10090,16 +10102,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10134,7 +10146,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10164,7 +10176,7 @@
         <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10199,7 +10211,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10220,16 +10232,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10264,7 +10276,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10300,7 +10312,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10335,7 +10347,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10356,13 +10368,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10397,7 +10409,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10421,13 +10433,13 @@
         <v>205</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>266</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10462,7 +10474,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10483,13 +10495,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10524,7 +10536,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10545,16 +10557,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>223</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10589,7 +10601,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10748,16 +10760,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10774,7 +10786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10798,7 +10810,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10830,7 +10842,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10851,10 +10863,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10889,7 +10901,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10913,13 +10925,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10954,7 +10966,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10978,13 +10990,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>213</v>
@@ -11019,7 +11031,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11040,10 +11052,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -11075,7 +11087,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11137,7 +11149,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11158,16 +11170,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11199,7 +11211,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11223,16 +11235,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11264,7 +11276,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11285,13 +11297,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>122</v>
@@ -11326,7 +11338,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11353,10 +11365,10 @@
         <v>286</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>128</v>
@@ -11391,7 +11403,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11412,10 +11424,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11453,7 +11465,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11515,7 +11527,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11542,10 +11554,10 @@
         <v>272</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11577,7 +11589,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11601,16 +11613,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>140</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11642,7 +11654,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11669,7 +11681,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11707,7 +11719,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11728,13 +11740,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>150</v>
@@ -11769,7 +11781,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11790,16 +11802,16 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>279</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>159</v>
@@ -11834,7 +11846,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11855,16 +11867,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>164</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11899,7 +11911,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11920,13 +11932,13 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>299</v>
+        <v>461</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>169</v>
@@ -11961,7 +11973,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11982,13 +11994,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12020,7 +12032,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12047,10 +12059,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12082,7 +12094,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12103,13 +12115,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12141,16 +12153,16 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D24" s="3">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -12162,7 +12174,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12194,7 +12206,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12215,13 +12227,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>185</v>
@@ -12256,7 +12268,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12315,7 +12327,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12336,13 +12348,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12374,7 +12386,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12398,10 +12410,10 @@
         <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12433,7 +12445,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12454,13 +12466,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>203</v>
@@ -12495,7 +12507,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12525,10 +12537,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12560,7 +12572,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12581,13 +12593,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12619,7 +12631,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12643,10 +12655,10 @@
         <v>265</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12678,7 +12690,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12699,13 +12711,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12737,7 +12749,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12758,13 +12770,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12796,7 +12808,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12817,7 +12829,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12849,7 +12861,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12870,10 +12882,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>223</v>
@@ -12908,7 +12920,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t>Vein ID</t>
   </si>
@@ -851,532 +851,535 @@
     <t>mars_lubricant</t>
   </si>
   <si>
-    <t>soapstone: 10</t>
+    <t>soapstone: 15</t>
+  </si>
+  <si>
+    <t>talc: 15</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 5</t>
+  </si>
+  <si>
+    <t>trona: 25</t>
+  </si>
+  <si>
+    <t>pentlandite: 5</t>
+  </si>
+  <si>
+    <t>mars_neodynium</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [1]</t>
+  </si>
+  <si>
+    <t>mars_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 25 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 20</t>
+  </si>
+  <si>
+    <t>mars_pitchblende</t>
+  </si>
+  <si>
+    <t>pitchblende: 35 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 25</t>
+  </si>
+  <si>
+    <t>mars_quartzite</t>
+  </si>
+  <si>
+    <t>mars_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 20 [1]</t>
+  </si>
+  <si>
+    <t>mars_stibnite</t>
+  </si>
+  <si>
+    <t>mars_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 15</t>
+  </si>
+  <si>
+    <t>pyrite: 45</t>
+  </si>
+  <si>
+    <t>sphalerite: 25</t>
+  </si>
+  <si>
+    <t>mars_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 10</t>
+  </si>
+  <si>
+    <t>spessartine: 10</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tantalite: 35 [1]</t>
+  </si>
+  <si>
+    <t>mars_tungsten</t>
+  </si>
+  <si>
+    <t>tungstate: 35</t>
+  </si>
+  <si>
+    <t>mars_surface_bismuthinite</t>
+  </si>
+  <si>
+    <t>bismuth: 20 [1]</t>
+  </si>
+  <si>
+    <t>sulfur: 10</t>
+  </si>
+  <si>
+    <t>gypsum: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 55 [1]</t>
+  </si>
+  <si>
+    <t>tin: 35</t>
+  </si>
+  <si>
+    <t>saltpeter: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_hematite</t>
+  </si>
+  <si>
+    <t>calcite: 5</t>
+  </si>
+  <si>
+    <t>mars_surface_nickel_galena</t>
+  </si>
+  <si>
+    <t>cobaltite: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 60 [1]</t>
+  </si>
+  <si>
+    <t>redstone: 5</t>
+  </si>
+  <si>
+    <t>glacio_stone</t>
+  </si>
+  <si>
+    <t>moon_deepslate</t>
+  </si>
+  <si>
+    <t>moon_stone</t>
+  </si>
+  <si>
+    <t>moon_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 25</t>
+  </si>
+  <si>
+    <t>pyrochlore: 40 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 5</t>
+  </si>
+  <si>
+    <t>moon_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 35 [1]</t>
+  </si>
+  <si>
+    <t>ilmenite: 40 [1]</t>
+  </si>
+  <si>
+    <t>armalcolite: 20</t>
+  </si>
+  <si>
+    <t>moon_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium: 35 [1]</t>
+  </si>
+  <si>
+    <t>emerald: 50 [2]</t>
+  </si>
+  <si>
+    <t>thorium: 1</t>
+  </si>
+  <si>
+    <t>moon_cassiterite</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 30 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 5</t>
+  </si>
+  <si>
+    <t>cassiterite: 35 [1]</t>
+  </si>
+  <si>
+    <t>tin: 15</t>
+  </si>
+  <si>
+    <t>moon_sheldonite</t>
+  </si>
+  <si>
+    <t>moon_desh</t>
+  </si>
+  <si>
+    <t>desh: 25</t>
+  </si>
+  <si>
+    <t>ilmenite: 30 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 25</t>
+  </si>
+  <si>
+    <t>moon_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10</t>
+  </si>
+  <si>
+    <t>yellow_garnet: 15</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [1]</t>
+  </si>
+  <si>
+    <t>opal: 40 [1]</t>
+  </si>
+  <si>
+    <t>moon_garnierite</t>
+  </si>
+  <si>
+    <t>pentlandite: 25 [1]</t>
+  </si>
+  <si>
+    <t>moon_gold</t>
+  </si>
+  <si>
+    <t>magnetite: 20</t>
+  </si>
+  <si>
+    <t>moon_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 50 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 35</t>
+  </si>
+  <si>
+    <t>olivine: 10</t>
+  </si>
+  <si>
+    <t>moon_gypsum</t>
+  </si>
+  <si>
+    <t>calcite: 25</t>
+  </si>
+  <si>
+    <t>gypsum: 35 [1]</t>
+  </si>
+  <si>
+    <t>moon_lubricant</t>
+  </si>
+  <si>
+    <t>moon_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 25</t>
+  </si>
+  <si>
+    <t>chromite: 40 [2]</t>
+  </si>
+  <si>
+    <t>moon_manganese</t>
+  </si>
+  <si>
+    <t>moon_mica</t>
+  </si>
+  <si>
+    <t>kyanite: 35 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 15</t>
+  </si>
+  <si>
+    <t>moon_molybdenum</t>
+  </si>
+  <si>
+    <t>moon_monazite</t>
+  </si>
+  <si>
+    <t>olivine: 1</t>
+  </si>
+  <si>
+    <t>moon_pyrolusite</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [2]</t>
+  </si>
+  <si>
+    <t>cobaltite: 25</t>
+  </si>
+  <si>
+    <t>cobalt: 25</t>
+  </si>
+  <si>
+    <t>tantalite: 15</t>
+  </si>
+  <si>
+    <t>moon_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 20</t>
+  </si>
+  <si>
+    <t>certus_quartz: 45 [2]</t>
+  </si>
+  <si>
+    <t>nether_quartz: 30 [1]</t>
+  </si>
+  <si>
+    <t>barite: 5</t>
+  </si>
+  <si>
+    <t>moon_redstone</t>
+  </si>
+  <si>
+    <t>moon_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35 [1]</t>
+  </si>
+  <si>
+    <t>soapstone: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 45</t>
+  </si>
+  <si>
+    <t>moon_sapphire</t>
+  </si>
+  <si>
+    <t>olivine: 2</t>
+  </si>
+  <si>
+    <t>moon_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tungstate: 50 [2]</t>
+  </si>
+  <si>
+    <t>lithium: 10</t>
+  </si>
+  <si>
+    <t>moon_silver</t>
+  </si>
+  <si>
+    <t>silver: 45 [1]</t>
+  </si>
+  <si>
+    <t>moon_sphalerite</t>
+  </si>
+  <si>
+    <t>desh: 10</t>
+  </si>
+  <si>
+    <t>sphalerite: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 40</t>
+  </si>
+  <si>
+    <t>moon_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>copper: 15</t>
+  </si>
+  <si>
+    <t>chalcocite: 25</t>
+  </si>
+  <si>
+    <t>moon_topaz</t>
+  </si>
+  <si>
+    <t>blackstone</t>
+  </si>
+  <si>
+    <t>deepslate</t>
+  </si>
+  <si>
+    <t>dripstone</t>
+  </si>
+  <si>
+    <t>nether_anthracite</t>
+  </si>
+  <si>
+    <t>anthracite: 100</t>
+  </si>
+  <si>
+    <t>nether_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 50 [2]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 35 [1]</t>
+  </si>
+  <si>
+    <t>nether_basaltic_sands</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>fullers_earth: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_beryllium</t>
+  </si>
+  <si>
+    <t>nether_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 40 [2]</t>
+  </si>
+  <si>
+    <t>tin: 60 [2]</t>
+  </si>
+  <si>
+    <t>nether_sheldonite</t>
+  </si>
+  <si>
+    <t>nether_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 10 [1]</t>
+  </si>
+  <si>
+    <t>copper: 65 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10 [1]</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [2]</t>
+  </si>
+  <si>
+    <t>opal: 40 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>garnet_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_garnierite</t>
+  </si>
+  <si>
+    <t>cobaltite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_goethite</t>
+  </si>
+  <si>
+    <t>goethite: 50 [3]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_gold</t>
+  </si>
+  <si>
+    <t>nether_graphite</t>
+  </si>
+  <si>
+    <t>diamond: 40 [1]</t>
+  </si>
+  <si>
+    <t>coal: 15</t>
+  </si>
+  <si>
+    <t>nether_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20 [1]</t>
+  </si>
+  <si>
+    <t>calcite: 30 [1]</t>
+  </si>
+  <si>
+    <t>nether_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 35 [3]</t>
+  </si>
+  <si>
+    <t>nether_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 25 [1]</t>
+  </si>
+  <si>
+    <t>lapis: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30 [1]</t>
   </si>
   <si>
     <t>talc: 20 [1]</t>
-  </si>
-  <si>
-    <t>trona: 15</t>
-  </si>
-  <si>
-    <t>pentlandite: 5</t>
-  </si>
-  <si>
-    <t>mars_neodynium</t>
-  </si>
-  <si>
-    <t>bastnasite: 50 [1]</t>
-  </si>
-  <si>
-    <t>mars_nickel</t>
-  </si>
-  <si>
-    <t>garnierite: 25 [1]</t>
-  </si>
-  <si>
-    <t>nickel: 20</t>
-  </si>
-  <si>
-    <t>mars_pitchblende</t>
-  </si>
-  <si>
-    <t>pitchblende: 35 [1]</t>
-  </si>
-  <si>
-    <t>hematite: 25</t>
-  </si>
-  <si>
-    <t>mars_quartzite</t>
-  </si>
-  <si>
-    <t>mars_salt</t>
-  </si>
-  <si>
-    <t>rock_salt: 20 [1]</t>
-  </si>
-  <si>
-    <t>mars_stibnite</t>
-  </si>
-  <si>
-    <t>mars_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 15</t>
-  </si>
-  <si>
-    <t>pyrite: 45</t>
-  </si>
-  <si>
-    <t>sphalerite: 25</t>
-  </si>
-  <si>
-    <t>mars_tantalite</t>
-  </si>
-  <si>
-    <t>grossular: 10</t>
-  </si>
-  <si>
-    <t>spessartine: 10</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tantalite: 35 [1]</t>
-  </si>
-  <si>
-    <t>mars_tungsten</t>
-  </si>
-  <si>
-    <t>tungstate: 35</t>
-  </si>
-  <si>
-    <t>mars_surface_bismuthinite</t>
-  </si>
-  <si>
-    <t>bismuth: 20 [1]</t>
-  </si>
-  <si>
-    <t>sulfur: 10</t>
-  </si>
-  <si>
-    <t>gypsum: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 55 [1]</t>
-  </si>
-  <si>
-    <t>tin: 35</t>
-  </si>
-  <si>
-    <t>saltpeter: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_hematite</t>
-  </si>
-  <si>
-    <t>calcite: 5</t>
-  </si>
-  <si>
-    <t>mars_surface_nickel_galena</t>
-  </si>
-  <si>
-    <t>cobaltite: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 60 [1]</t>
-  </si>
-  <si>
-    <t>redstone: 5</t>
-  </si>
-  <si>
-    <t>glacio_stone</t>
-  </si>
-  <si>
-    <t>moon_deepslate</t>
-  </si>
-  <si>
-    <t>moon_stone</t>
-  </si>
-  <si>
-    <t>moon_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 25</t>
-  </si>
-  <si>
-    <t>pyrochlore: 40 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 5</t>
-  </si>
-  <si>
-    <t>moon_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 35 [1]</t>
-  </si>
-  <si>
-    <t>ilmenite: 40 [1]</t>
-  </si>
-  <si>
-    <t>armalcolite: 20</t>
-  </si>
-  <si>
-    <t>moon_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium: 35 [1]</t>
-  </si>
-  <si>
-    <t>emerald: 50 [2]</t>
-  </si>
-  <si>
-    <t>thorium: 1</t>
-  </si>
-  <si>
-    <t>moon_cassiterite</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 30 [1]</t>
-  </si>
-  <si>
-    <t>zeolite: 5</t>
-  </si>
-  <si>
-    <t>cassiterite: 35 [1]</t>
-  </si>
-  <si>
-    <t>tin: 15</t>
-  </si>
-  <si>
-    <t>moon_sheldonite</t>
-  </si>
-  <si>
-    <t>moon_desh</t>
-  </si>
-  <si>
-    <t>desh: 25</t>
-  </si>
-  <si>
-    <t>ilmenite: 30 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 25</t>
-  </si>
-  <si>
-    <t>moon_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10</t>
-  </si>
-  <si>
-    <t>yellow_garnet: 15</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [1]</t>
-  </si>
-  <si>
-    <t>opal: 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_garnierite</t>
-  </si>
-  <si>
-    <t>pentlandite: 25 [1]</t>
-  </si>
-  <si>
-    <t>moon_gold</t>
-  </si>
-  <si>
-    <t>magnetite: 20</t>
-  </si>
-  <si>
-    <t>moon_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 50 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 35</t>
-  </si>
-  <si>
-    <t>olivine: 10</t>
-  </si>
-  <si>
-    <t>moon_gypsum</t>
-  </si>
-  <si>
-    <t>calcite: 25</t>
-  </si>
-  <si>
-    <t>gypsum: 35 [1]</t>
-  </si>
-  <si>
-    <t>moon_lubricant</t>
-  </si>
-  <si>
-    <t>moon_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 25</t>
-  </si>
-  <si>
-    <t>chromite: 40 [2]</t>
-  </si>
-  <si>
-    <t>moon_manganese</t>
-  </si>
-  <si>
-    <t>moon_mica</t>
-  </si>
-  <si>
-    <t>kyanite: 35 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 15</t>
-  </si>
-  <si>
-    <t>moon_molybdenum</t>
-  </si>
-  <si>
-    <t>moon_monazite</t>
-  </si>
-  <si>
-    <t>olivine: 1</t>
-  </si>
-  <si>
-    <t>moon_pyrolusite</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40 [2]</t>
-  </si>
-  <si>
-    <t>cobaltite: 25</t>
-  </si>
-  <si>
-    <t>cobalt: 25</t>
-  </si>
-  <si>
-    <t>tantalite: 15</t>
-  </si>
-  <si>
-    <t>moon_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 20</t>
-  </si>
-  <si>
-    <t>certus_quartz: 45 [2]</t>
-  </si>
-  <si>
-    <t>nether_quartz: 30 [1]</t>
-  </si>
-  <si>
-    <t>barite: 5</t>
-  </si>
-  <si>
-    <t>moon_redstone</t>
-  </si>
-  <si>
-    <t>moon_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35 [1]</t>
-  </si>
-  <si>
-    <t>soapstone: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 45</t>
-  </si>
-  <si>
-    <t>talc: 15</t>
-  </si>
-  <si>
-    <t>moon_sapphire</t>
-  </si>
-  <si>
-    <t>olivine: 2</t>
-  </si>
-  <si>
-    <t>moon_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tungstate: 50 [2]</t>
-  </si>
-  <si>
-    <t>lithium: 10</t>
-  </si>
-  <si>
-    <t>moon_silver</t>
-  </si>
-  <si>
-    <t>silver: 45 [1]</t>
-  </si>
-  <si>
-    <t>moon_sphalerite</t>
-  </si>
-  <si>
-    <t>desh: 10</t>
-  </si>
-  <si>
-    <t>sphalerite: 50 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 40</t>
-  </si>
-  <si>
-    <t>moon_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 40 [1]</t>
-  </si>
-  <si>
-    <t>copper: 15</t>
-  </si>
-  <si>
-    <t>chalcocite: 25</t>
-  </si>
-  <si>
-    <t>moon_topaz</t>
-  </si>
-  <si>
-    <t>blackstone</t>
-  </si>
-  <si>
-    <t>deepslate</t>
-  </si>
-  <si>
-    <t>dripstone</t>
-  </si>
-  <si>
-    <t>nether_anthracite</t>
-  </si>
-  <si>
-    <t>anthracite: 100</t>
-  </si>
-  <si>
-    <t>nether_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 50 [2]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_basaltic_sands</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>granitic_mineral_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>fullers_earth: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_beryllium</t>
-  </si>
-  <si>
-    <t>nether_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 40 [2]</t>
-  </si>
-  <si>
-    <t>tin: 60 [2]</t>
-  </si>
-  <si>
-    <t>nether_sheldonite</t>
-  </si>
-  <si>
-    <t>nether_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 10 [1]</t>
-  </si>
-  <si>
-    <t>copper: 65 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10 [1]</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [2]</t>
-  </si>
-  <si>
-    <t>opal: 40 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>garnet_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_garnierite</t>
-  </si>
-  <si>
-    <t>cobaltite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_goethite</t>
-  </si>
-  <si>
-    <t>goethite: 50 [3]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_gold</t>
-  </si>
-  <si>
-    <t>nether_graphite</t>
-  </si>
-  <si>
-    <t>diamond: 40 [1]</t>
-  </si>
-  <si>
-    <t>coal: 15</t>
-  </si>
-  <si>
-    <t>nether_gypsum</t>
-  </si>
-  <si>
-    <t>borax: 20 [1]</t>
-  </si>
-  <si>
-    <t>calcite: 30 [1]</t>
-  </si>
-  <si>
-    <t>nether_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 35 [3]</t>
-  </si>
-  <si>
-    <t>nether_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sodalite: 25 [1]</t>
-  </si>
-  <si>
-    <t>lapis: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30 [1]</t>
   </si>
   <si>
     <t>glauconite_sand: 25 [1]</t>
@@ -6317,7 +6320,7 @@
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
     <col min="10" max="10" width="18.350568771362305" customWidth="1" style="3"/>
     <col min="11" max="11" width="23.763607025146484" customWidth="1" style="3"/>
-    <col min="12" max="12" width="19.039091110229492" customWidth="1" style="3"/>
+    <col min="12" max="12" width="17.945432662963867" customWidth="1" style="3"/>
     <col min="13" max="13" width="18.38944435119629" customWidth="1" style="3"/>
     <col min="14" max="14" width="13.724266052246094" customWidth="1" style="3"/>
     <col min="15" max="15" width="11.552298545837402" customWidth="1" style="3"/>
@@ -7495,13 +7498,13 @@
         <v>279</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>115</v>
@@ -7560,7 +7563,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7581,7 +7584,7 @@
         <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>177</v>
@@ -7646,7 +7649,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7667,10 +7670,10 @@
         <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>126</v>
@@ -7732,7 +7735,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -7753,13 +7756,13 @@
         <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>250</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7815,7 +7818,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7901,7 +7904,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -7925,7 +7928,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>214</v>
@@ -7990,7 +7993,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8097,13 +8100,13 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>131</v>
@@ -8162,7 +8165,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8183,16 +8186,16 @@
         <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8248,7 +8251,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8272,7 +8275,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>83</v>
@@ -8334,7 +8337,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8355,16 +8358,16 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>275</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8420,7 +8423,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8441,13 +8444,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8503,7 +8506,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8533,7 +8536,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8589,7 +8592,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8613,7 +8616,7 @@
         <v>219</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>205</v>
@@ -8622,7 +8625,7 @@
         <v>107</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8678,7 +8681,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8699,7 +8702,7 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>243</v>
@@ -8708,7 +8711,7 @@
         <v>223</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8867,16 +8870,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8884,7 +8887,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8905,16 +8908,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -8949,7 +8952,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8970,13 +8973,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9011,7 +9014,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9035,16 +9038,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>213</v>
@@ -9082,7 +9085,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9103,16 +9106,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9147,7 +9150,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9212,7 +9215,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9233,16 +9236,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9277,7 +9280,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9301,16 +9304,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9345,7 +9348,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9366,16 +9369,16 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>128</v>
@@ -9413,7 +9416,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9443,7 +9446,7 @@
         <v>269</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>132</v>
@@ -9481,7 +9484,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9505,13 +9508,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9546,7 +9549,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9573,16 +9576,16 @@
         <v>138</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9617,7 +9620,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9685,7 +9688,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9706,13 +9709,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9753,7 +9756,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9818,7 +9821,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9839,7 +9842,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>172</v>
@@ -9848,10 +9851,10 @@
         <v>173</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9886,7 +9889,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9916,7 +9919,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -9951,7 +9954,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9972,7 +9975,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>177</v>
@@ -9981,7 +9984,7 @@
         <v>178</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10016,7 +10019,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10037,16 +10040,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10081,7 +10084,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10102,16 +10105,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10146,7 +10149,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10176,7 +10179,7 @@
         <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10211,7 +10214,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10232,16 +10235,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>387</v>
+        <v>279</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10439,7 +10442,7 @@
         <v>266</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10990,13 +10993,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>213</v>
@@ -11117,7 +11120,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11359,16 +11362,16 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>435</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>128</v>
@@ -11622,7 +11625,7 @@
         <v>140</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11805,13 +11808,13 @@
         <v>453</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>279</v>
+        <v>454</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>159</v>
@@ -11846,7 +11849,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11867,16 +11870,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>164</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11911,7 +11914,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11932,13 +11935,13 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>169</v>
@@ -11973,7 +11976,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11994,13 +11997,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12032,7 +12035,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12059,10 +12062,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12094,7 +12097,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12115,13 +12118,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12153,7 +12156,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12174,7 +12177,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12206,7 +12209,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12227,13 +12230,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>185</v>
@@ -12268,7 +12271,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12327,7 +12330,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12348,13 +12351,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12386,7 +12389,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12410,10 +12413,10 @@
         <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12445,7 +12448,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12466,13 +12469,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>203</v>
@@ -12507,7 +12510,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12537,10 +12540,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12572,7 +12575,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12593,13 +12596,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12631,7 +12634,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12655,10 +12658,10 @@
         <v>265</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12690,7 +12693,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12711,13 +12714,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12749,7 +12752,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12770,13 +12773,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12808,7 +12811,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12829,7 +12832,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12861,7 +12864,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12882,10 +12885,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>223</v>
@@ -12920,7 +12923,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
   <si>
     <t>Vein ID</t>
   </si>
@@ -675,6 +675,15 @@
   </si>
   <si>
     <t>sphalerite: 15</t>
+  </si>
+  <si>
+    <t>normal_tarkianite</t>
+  </si>
+  <si>
+    <t>oilsands: 35</t>
+  </si>
+  <si>
+    <t>tarkianite: 35</t>
   </si>
   <si>
     <t>normal_tetrahedrite</t>
@@ -1626,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.943572998046875" customWidth="1" style="3"/>
@@ -5746,22 +5755,25 @@
         <v>220</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C44" s="3">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D44" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E44" s="3">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>75</v>
-      </c>
-      <c r="G44" s="3">
-        <v>40</v>
+        <v>80</v>
+      </c>
+      <c r="H44" s="3">
+        <v>60</v>
+      </c>
+      <c r="I44" s="3">
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>221</v>
@@ -5770,13 +5782,16 @@
         <v>222</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>35</v>
+        <v>138</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>35</v>
@@ -5790,153 +5805,150 @@
       <c r="U44" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>35</v>
+      <c r="V44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA44" s="2" t="s">
-        <v>35</v>
+      <c r="Y44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG44" s="1" t="s">
-        <v>36</v>
+      <c r="AC44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG44" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI44" s="1" t="s">
-        <v>36</v>
+      <c r="AI44" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D45" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E45" s="3">
-        <v>60</v>
+        <v>-32</v>
       </c>
       <c r="F45" s="3">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G45" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="P45" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>36</v>
+      <c r="R45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE45" s="2" t="s">
-        <v>35</v>
+      <c r="W45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF45" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI45" s="2" t="s">
-        <v>35</v>
+      <c r="AG45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI45" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="3">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D46" s="3">
         <v>0.25</v>
@@ -5951,28 +5963,34 @@
         <v>50</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>230</v>
       </c>
+      <c r="M46" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="P46" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U46" s="2" t="s">
-        <v>35</v>
+      <c r="R46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>35</v>
@@ -5980,8 +5998,8 @@
       <c r="W46" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X46" s="2" t="s">
-        <v>35</v>
+      <c r="X46" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y46" s="1" t="s">
         <v>36</v>
@@ -5992,8 +6010,8 @@
       <c r="AA46" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB46" s="2" t="s">
-        <v>35</v>
+      <c r="AB46" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC46" s="2" t="s">
         <v>35</v>
@@ -6010,8 +6028,8 @@
       <c r="AG46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH46" s="2" t="s">
-        <v>35</v>
+      <c r="AH46" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI46" s="2" t="s">
         <v>35</v>
@@ -6025,16 +6043,16 @@
         <v>31</v>
       </c>
       <c r="C47" s="3">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="D47" s="3">
         <v>0.25</v>
       </c>
       <c r="E47" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F47" s="3">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G47" s="3">
         <v>50</v>
@@ -6045,17 +6063,11 @@
       <c r="K47" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>36</v>
+      <c r="P47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>35</v>
@@ -6069,23 +6081,23 @@
       <c r="U47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>35</v>
+      <c r="V47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y47" s="2" t="s">
-        <v>35</v>
+      <c r="Y47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA47" s="2" t="s">
-        <v>35</v>
+      <c r="AA47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>35</v>
@@ -6099,8 +6111,8 @@
       <c r="AE47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF47" s="1" t="s">
-        <v>36</v>
+      <c r="AF47" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG47" s="2" t="s">
         <v>35</v>
@@ -6114,35 +6126,38 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="3">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="D48" s="3">
         <v>0.25</v>
       </c>
       <c r="E48" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F48" s="3">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G48" s="3">
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="M48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="P48" s="1" t="s">
         <v>36</v>
       </c>
@@ -6173,8 +6188,8 @@
       <c r="Y48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z48" s="1" t="s">
-        <v>36</v>
+      <c r="Z48" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA48" s="2" t="s">
         <v>35</v>
@@ -6182,37 +6197,37 @@
       <c r="AB48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE48" s="1" t="s">
-        <v>36</v>
+      <c r="AC48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE48" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG48" s="1" t="s">
-        <v>36</v>
+      <c r="AG48" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI48" s="1" t="s">
-        <v>36</v>
+      <c r="AI48" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="3">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D49" s="3">
         <v>0.25</v>
@@ -6227,19 +6242,19 @@
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>35</v>
+      <c r="P49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>35</v>
@@ -6253,8 +6268,8 @@
       <c r="U49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V49" s="2" t="s">
-        <v>35</v>
+      <c r="V49" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>35</v>
@@ -6283,8 +6298,8 @@
       <c r="AE49" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF49" s="2" t="s">
-        <v>35</v>
+      <c r="AF49" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AG49" s="1" t="s">
         <v>36</v>
@@ -6293,6 +6308,98 @@
         <v>35</v>
       </c>
       <c r="AI49" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="3">
+        <v>140</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>60</v>
+      </c>
+      <c r="F50" s="3">
+        <v>210</v>
+      </c>
+      <c r="G50" s="3">
+        <v>50</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI50" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6422,10 +6529,10 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>26</v>
@@ -6434,12 +6541,12 @@
         <v>28</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6466,7 +6573,7 @@
         <v>192</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6522,7 +6629,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6546,7 +6653,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6605,7 +6712,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6629,13 +6736,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6691,7 +6798,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6718,7 +6825,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -6783,7 +6890,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -6869,7 +6976,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>99</v>
@@ -6899,7 +7006,7 @@
         <v>101</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -6955,7 +7062,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -6976,10 +7083,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7035,7 +7142,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7056,10 +7163,10 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>116</v>
@@ -7121,7 +7228,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7142,13 +7249,13 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>206</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>115</v>
@@ -7207,7 +7314,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7228,13 +7335,13 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>132</v>
@@ -7293,7 +7400,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>99</v>
@@ -7317,16 +7424,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -7382,7 +7489,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -7468,7 +7575,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -7489,19 +7596,19 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>115</v>
@@ -7560,7 +7667,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7581,7 +7688,7 @@
         <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>177</v>
@@ -7646,7 +7753,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7667,10 +7774,10 @@
         <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>126</v>
@@ -7732,7 +7839,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -7753,13 +7860,13 @@
         <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7815,7 +7922,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7901,7 +8008,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -7925,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>214</v>
@@ -7990,7 +8097,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -8011,13 +8118,13 @@
         <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>115</v>
@@ -8076,7 +8183,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8097,13 +8204,13 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>131</v>
@@ -8162,7 +8269,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8183,16 +8290,16 @@
         <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8248,7 +8355,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8272,7 +8379,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>83</v>
@@ -8334,7 +8441,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8355,16 +8462,16 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8420,7 +8527,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8441,13 +8548,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8503,7 +8610,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8533,7 +8640,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8589,7 +8696,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8613,7 +8720,7 @@
         <v>219</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>205</v>
@@ -8622,7 +8729,7 @@
         <v>107</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8678,7 +8785,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8699,16 +8806,16 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8867,16 +8974,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8884,7 +8991,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8905,16 +9012,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -8949,7 +9056,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8970,13 +9077,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9011,7 +9118,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9035,16 +9142,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>213</v>
@@ -9082,7 +9189,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9103,16 +9210,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9147,7 +9254,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9171,13 +9278,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9212,7 +9319,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9233,16 +9340,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9277,7 +9384,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9301,16 +9408,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9345,7 +9452,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9366,16 +9473,16 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>128</v>
@@ -9413,7 +9520,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9437,13 +9544,13 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>132</v>
@@ -9481,7 +9588,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9505,13 +9612,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9546,7 +9653,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9573,16 +9680,16 @@
         <v>138</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9617,7 +9724,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9685,7 +9792,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9706,13 +9813,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9753,7 +9860,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9818,7 +9925,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9839,7 +9946,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>172</v>
@@ -9848,10 +9955,10 @@
         <v>173</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9886,7 +9993,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9916,7 +10023,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -9951,7 +10058,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9972,7 +10079,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>177</v>
@@ -9981,7 +10088,7 @@
         <v>178</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10016,7 +10123,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10037,16 +10144,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10081,7 +10188,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10102,16 +10209,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10146,7 +10253,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10176,7 +10283,7 @@
         <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10211,7 +10318,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10232,16 +10339,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10276,7 +10383,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10303,7 +10410,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10312,7 +10419,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10347,7 +10454,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10368,13 +10475,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10409,7 +10516,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10433,13 +10540,13 @@
         <v>205</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10474,7 +10581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10495,13 +10602,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10536,7 +10643,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10557,16 +10664,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10601,7 +10708,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10760,16 +10867,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10786,7 +10893,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10810,7 +10917,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10842,7 +10949,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10863,10 +10970,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10901,7 +11008,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10925,13 +11032,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10966,7 +11073,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10990,13 +11097,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>213</v>
@@ -11031,7 +11138,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11052,10 +11159,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -11087,7 +11194,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11117,7 +11224,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11149,7 +11256,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11170,16 +11277,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11211,7 +11318,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11235,16 +11342,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11276,7 +11383,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11297,13 +11404,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>122</v>
@@ -11338,7 +11445,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11359,16 +11466,16 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>128</v>
@@ -11403,7 +11510,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11424,10 +11531,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11465,7 +11572,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11527,7 +11634,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11551,13 +11658,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11589,7 +11696,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11613,16 +11720,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>140</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11654,7 +11761,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11681,7 +11788,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11719,7 +11826,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11740,13 +11847,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>150</v>
@@ -11781,7 +11888,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11802,16 +11909,16 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>159</v>
@@ -11846,7 +11953,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11867,16 +11974,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>164</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11911,7 +12018,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11932,13 +12039,13 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>169</v>
@@ -11973,7 +12080,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11994,13 +12101,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12032,7 +12139,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12059,10 +12166,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12094,7 +12201,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12115,13 +12222,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12153,7 +12260,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12174,7 +12281,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12206,7 +12313,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12227,13 +12334,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>185</v>
@@ -12268,7 +12375,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12327,7 +12434,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12348,13 +12455,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12386,7 +12493,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12410,10 +12517,10 @@
         <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12445,7 +12552,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12466,13 +12573,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>203</v>
@@ -12507,7 +12614,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12537,10 +12644,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12572,7 +12679,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12593,13 +12700,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12631,7 +12738,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12652,13 +12759,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12690,7 +12797,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12711,13 +12818,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12749,7 +12856,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12770,13 +12877,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12808,7 +12915,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12829,7 +12936,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12861,7 +12968,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12882,13 +12989,13 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>35</v>
@@ -12920,7 +13027,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -5758,16 +5758,16 @@
         <v>99</v>
       </c>
       <c r="C44" s="3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D44" s="3">
         <v>0.35</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F44" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H44" s="3">
         <v>60</v>
@@ -5793,17 +5793,17 @@
       <c r="Q44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>35</v>
+      <c r="R44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>36</v>
@@ -5811,41 +5811,41 @@
       <c r="W44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X44" s="2" t="s">
-        <v>35</v>
+      <c r="X44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z44" s="2" t="s">
-        <v>35</v>
+      <c r="Z44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE44" s="2" t="s">
-        <v>35</v>
+      <c r="AB44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE44" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI44" s="2" t="s">
-        <v>35</v>
+      <c r="AG44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI44" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="45">

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -680,10 +680,10 @@
     <t>normal_tarkianite</t>
   </si>
   <si>
+    <t>tarkianite: 35</t>
+  </si>
+  <si>
     <t>oilsands: 35</t>
-  </si>
-  <si>
-    <t>tarkianite: 35</t>
   </si>
   <si>
     <t>normal_tetrahedrite</t>
@@ -5758,7 +5758,7 @@
         <v>99</v>
       </c>
       <c r="C44" s="3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D44" s="3">
         <v>0.35</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t>Vein ID</t>
   </si>
@@ -344,10 +344,13 @@
     <t>normal_cassiterite</t>
   </si>
   <si>
-    <t>cassiterite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tin: 60 [1]</t>
+    <t>cassiterite: 35 [1]</t>
+  </si>
+  <si>
+    <t>tin: 55 [1]</t>
+  </si>
+  <si>
+    <t>saltpeter: 10</t>
   </si>
   <si>
     <t>normal_coal</t>
@@ -713,10 +716,10 @@
     <t>surface_cassiterite</t>
   </si>
   <si>
-    <t>cassiterite: 60</t>
-  </si>
-  <si>
-    <t>tin: 40</t>
+    <t>cassiterite: 55</t>
+  </si>
+  <si>
+    <t>tin: 35</t>
   </si>
   <si>
     <t>surface_copper</t>
@@ -959,12 +962,6 @@
     <t>cassiterite: 55 [1]</t>
   </si>
   <si>
-    <t>tin: 35</t>
-  </si>
-  <si>
-    <t>saltpeter: 10</t>
-  </si>
-  <si>
     <t>mars_surface_hematite</t>
   </si>
   <si>
@@ -1038,9 +1035,6 @@
   </si>
   <si>
     <t>zeolite: 5</t>
-  </si>
-  <si>
-    <t>cassiterite: 35 [1]</t>
   </si>
   <si>
     <t>tin: 15</t>
@@ -3332,6 +3326,9 @@
       <c r="K18" s="3" t="s">
         <v>110</v>
       </c>
+      <c r="L18" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
       </c>
@@ -3395,7 +3392,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -3416,7 +3413,7 @@
         <v>60</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
@@ -3481,7 +3478,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -3502,16 +3499,16 @@
         <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -3576,7 +3573,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -3597,16 +3594,16 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -3671,7 +3668,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -3692,19 +3689,19 @@
         <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -3769,7 +3766,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -3796,13 +3793,13 @@
         <v>47</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>36</v>
@@ -3867,7 +3864,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>38</v>
@@ -3891,13 +3888,13 @@
         <v>6</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -3962,7 +3959,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>38</v>
@@ -3986,16 +3983,16 @@
         <v>9</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -4060,7 +4057,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -4081,13 +4078,13 @@
         <v>40</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>55</v>
@@ -4155,7 +4152,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -4176,16 +4173,16 @@
         <v>40</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -4250,7 +4247,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -4271,16 +4268,16 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -4345,7 +4342,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -4366,19 +4363,19 @@
         <v>36</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
@@ -4464,16 +4461,16 @@
         <v>30</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -4559,16 +4556,16 @@
         <v>30</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>36</v>
@@ -4633,7 +4630,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -4654,16 +4651,16 @@
         <v>36</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -4728,7 +4725,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -4749,13 +4746,13 @@
         <v>35</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>35</v>
@@ -4820,7 +4817,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -4841,7 +4838,7 @@
         <v>55</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>35</v>
@@ -4906,7 +4903,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -4927,16 +4924,16 @@
         <v>26</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>36</v>
@@ -5001,7 +4998,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -5022,13 +5019,13 @@
         <v>40</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>35</v>
@@ -5093,7 +5090,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>
@@ -5114,13 +5111,13 @@
         <v>40</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>35</v>
@@ -5185,7 +5182,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>38</v>
@@ -5209,16 +5206,16 @@
         <v>4</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>35</v>
@@ -5283,7 +5280,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>31</v>
@@ -5304,16 +5301,16 @@
         <v>40</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>35</v>
@@ -5378,7 +5375,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>31</v>
@@ -5399,13 +5396,13 @@
         <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>35</v>
@@ -5470,7 +5467,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>31</v>
@@ -5491,13 +5488,13 @@
         <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>36</v>
@@ -5562,7 +5559,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>38</v>
@@ -5586,16 +5583,16 @@
         <v>6</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>35</v>
@@ -5660,7 +5657,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
@@ -5681,13 +5678,13 @@
         <v>45</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>36</v>
@@ -5752,7 +5749,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>99</v>
@@ -5776,16 +5773,16 @@
         <v>10</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>36</v>
@@ -5850,7 +5847,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
@@ -5871,13 +5868,13 @@
         <v>40</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>35</v>
@@ -5942,7 +5939,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
@@ -5963,13 +5960,13 @@
         <v>50</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>107</v>
@@ -6037,7 +6034,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>31</v>
@@ -6058,10 +6055,13 @@
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>35</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
@@ -6147,16 +6147,16 @@
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>36</v>
@@ -6221,7 +6221,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
@@ -6242,13 +6242,13 @@
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>36</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>31</v>
@@ -6334,13 +6334,13 @@
         <v>50</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>35</v>
@@ -6529,10 +6529,10 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>26</v>
@@ -6541,12 +6541,12 @@
         <v>28</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6567,13 +6567,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6653,7 +6653,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6736,13 +6736,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6798,7 +6798,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6825,7 +6825,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -6834,7 +6834,7 @@
         <v>79</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -6890,7 +6890,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -6920,7 +6920,7 @@
         <v>92</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -6976,7 +6976,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>99</v>
@@ -7006,7 +7006,7 @@
         <v>101</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -7062,7 +7062,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -7083,10 +7083,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7142,7 +7142,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7163,16 +7163,16 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7249,16 +7249,16 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7335,16 +7335,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -7400,7 +7400,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>99</v>
@@ -7424,16 +7424,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -7510,13 +7510,13 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>55</v>
@@ -7575,7 +7575,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -7596,22 +7596,22 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -7667,7 +7667,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7688,16 +7688,16 @@
         <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7774,16 +7774,16 @@
         <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -7839,7 +7839,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -7860,13 +7860,13 @@
         <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7943,16 +7943,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -8008,7 +8008,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -8032,16 +8032,16 @@
         <v>6</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -8118,16 +8118,16 @@
         <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>35</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8204,16 +8204,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -8269,7 +8269,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8290,16 +8290,16 @@
         <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8355,7 +8355,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8379,13 +8379,13 @@
         <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>83</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8462,16 +8462,16 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8548,13 +8548,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>314</v>
+        <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>315</v>
+        <v>111</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8610,7 +8610,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8631,16 +8631,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8696,7 +8696,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8717,19 +8717,19 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>107</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8785,7 +8785,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8806,16 +8806,16 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8974,16 +8974,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -9012,16 +9012,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -9056,7 +9056,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -9077,13 +9077,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9118,7 +9118,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9142,19 +9142,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9210,16 +9210,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9254,7 +9254,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9278,13 +9278,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9319,7 +9319,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9340,16 +9340,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9384,7 +9384,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9408,16 +9408,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9473,19 +9473,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -9520,7 +9520,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9544,16 +9544,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -9588,7 +9588,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9612,13 +9612,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9677,19 +9677,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9724,7 +9724,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9745,19 +9745,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>35</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9813,13 +9813,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9860,7 +9860,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9881,16 +9881,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
@@ -9925,7 +9925,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9946,19 +9946,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -10023,7 +10023,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -10079,16 +10079,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10144,16 +10144,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10209,16 +10209,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10253,7 +10253,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10274,16 +10274,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10339,16 +10339,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>389</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10383,7 +10383,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10410,7 +10410,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10419,7 +10419,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10475,13 +10475,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10516,7 +10516,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10537,16 +10537,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10602,13 +10602,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10664,16 +10664,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10708,7 +10708,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10867,16 +10867,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10917,7 +10917,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10949,7 +10949,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10970,10 +10970,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -11008,7 +11008,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -11032,13 +11032,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -11097,16 +11097,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>36</v>
@@ -11138,7 +11138,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11159,10 +11159,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -11194,7 +11197,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11224,7 +11227,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11256,7 +11259,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11277,16 +11280,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11318,7 +11321,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11342,16 +11345,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11383,7 +11386,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11404,16 +11407,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -11445,7 +11448,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11466,19 +11469,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -11510,7 +11513,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11531,10 +11534,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11572,7 +11575,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11634,7 +11637,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11658,13 +11661,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11696,7 +11699,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11720,16 +11723,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11761,7 +11764,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11788,7 +11791,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11826,7 +11829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11847,16 +11850,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="M17" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -11888,7 +11891,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11909,19 +11912,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>458</v>
-      </c>
       <c r="N18" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -11953,7 +11956,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11974,16 +11977,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -12018,7 +12021,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -12039,16 +12042,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -12080,7 +12083,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -12101,13 +12104,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12139,7 +12142,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12166,10 +12169,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12201,7 +12204,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12222,13 +12225,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12260,7 +12263,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12281,7 +12284,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12313,7 +12316,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12334,16 +12337,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>482</v>
-      </c>
       <c r="M25" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>36</v>
@@ -12375,7 +12378,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12434,7 +12437,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12455,13 +12458,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12493,7 +12496,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12514,13 +12517,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12552,7 +12555,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12573,16 +12576,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -12614,7 +12617,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12644,10 +12647,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12679,7 +12682,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12700,13 +12703,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12738,7 +12741,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12759,13 +12762,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12797,7 +12800,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12818,13 +12821,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12856,7 +12859,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12877,13 +12880,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12915,7 +12918,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12936,7 +12939,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12968,7 +12971,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12989,13 +12992,13 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>35</v>
@@ -13027,7 +13030,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1563,16 +1563,28 @@
     <t>venus_manual_salt</t>
   </si>
   <si>
-    <t>salt: 50</t>
-  </si>
-  <si>
-    <t>spodumene: 15</t>
+    <t>salt: 80</t>
+  </si>
+  <si>
+    <t>rock_salt: 10</t>
+  </si>
+  <si>
+    <t>lepidolite: 5</t>
+  </si>
+  <si>
+    <t>spodumene: 5</t>
   </si>
   <si>
     <t>venus_manual_sulfur</t>
   </si>
   <si>
-    <t>sulfur: 50</t>
+    <t>sulfur: 80</t>
+  </si>
+  <si>
+    <t>pyrite: 15</t>
+  </si>
+  <si>
+    <t>sphalerite: 5</t>
   </si>
 </sst>
 </file>
@@ -13130,8 +13142,8 @@
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
     <col min="10" max="10" width="9.682135581970215" customWidth="1" style="3"/>
     <col min="11" max="11" width="12.619355201721191" customWidth="1" style="3"/>
-    <col min="12" max="12" width="13.423484802246094" customWidth="1" style="3"/>
-    <col min="13" max="13" width="15.053228378295898" customWidth="1" style="3"/>
+    <col min="12" max="12" width="12.329827308654785" customWidth="1" style="3"/>
+    <col min="13" max="13" width="13.95957088470459" customWidth="1" style="3"/>
     <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
     <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
     <col min="16" max="16" width="9.140625" customWidth="1" style="3"/>
@@ -13225,7 +13237,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3">
         <v>0.2</v>
@@ -13246,13 +13258,13 @@
         <v>515</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>214</v>
+        <v>516</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>198</v>
+        <v>517</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13275,13 +13287,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3">
         <v>0.2</v>
@@ -13293,16 +13305,16 @@
         <v>65</v>
       </c>
       <c r="G3" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>219</v>
+        <v>521</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>220</v>
+        <v>522</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1543,12 +1543,6 @@
   </si>
   <si>
     <t>sphalerite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_sylvite</t>
-  </si>
-  <si>
-    <t>sylvite: 100</t>
   </si>
   <si>
     <t>nether_tetrahedrite</t>
@@ -10898,7 +10892,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.112842559814453" customWidth="1" style="3"/>
@@ -13041,84 +13035,96 @@
         <v>31</v>
       </c>
       <c r="C35" s="3">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="D35" s="3">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F35" s="3">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G35" s="3">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>510</v>
       </c>
+      <c r="K35" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R35" s="2" t="s">
-        <v>35</v>
+      <c r="R35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="S35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T35" s="2" t="s">
-        <v>35</v>
+      <c r="T35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V35" s="2" t="s">
-        <v>35</v>
+      <c r="V35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X35" s="2" t="s">
-        <v>35</v>
+      <c r="X35" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C36" s="3">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E36" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
         <v>128</v>
       </c>
       <c r="G36" s="3">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="H36" s="3">
+        <v>7</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>512</v>
+        <v>85</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>513</v>
+        <v>86</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>36</v>
@@ -13135,78 +13141,13 @@
       <c r="U36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V36" s="1" t="s">
-        <v>36</v>
+      <c r="V36" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X36" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="3">
-        <v>180</v>
-      </c>
-      <c r="D37" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3">
-        <v>128</v>
-      </c>
-      <c r="G37" s="3">
-        <v>33</v>
-      </c>
-      <c r="H37" s="3">
-        <v>7</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X37" s="2" t="s">
+      <c r="X36" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -13320,7 +13261,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -13344,16 +13285,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13376,7 +13317,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -13397,13 +13338,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>Vein ID</t>
   </si>
@@ -285,6 +285,12 @@
     <t>bornite: 15</t>
   </si>
   <si>
+    <t>desert_oilsands</t>
+  </si>
+  <si>
+    <t>oilsands: 100 [1]</t>
+  </si>
+  <si>
     <t>normal_apatite</t>
   </si>
   <si>
@@ -559,9 +565,6 @@
   </si>
   <si>
     <t>normal_oilsands</t>
-  </si>
-  <si>
-    <t>oilsands: 100 [1]</t>
   </si>
   <si>
     <t>normal_olivine</t>
@@ -1654,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AI51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.943572998046875" customWidth="1" style="3"/>
@@ -2951,132 +2954,120 @@
         <v>31</v>
       </c>
       <c r="C14" s="3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D14" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E14" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>35</v>
+      <c r="R14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>36</v>
+      <c r="W14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>36</v>
+      <c r="AG14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3">
+        <v>170</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>20</v>
+      </c>
+      <c r="F15" s="3">
+        <v>120</v>
+      </c>
+      <c r="G15" s="3">
+        <v>34</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="3">
-        <v>160</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-32</v>
-      </c>
-      <c r="F15" s="3">
-        <v>60</v>
-      </c>
-      <c r="G15" s="3">
-        <v>48</v>
-      </c>
-      <c r="H15" s="3">
-        <v>9</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>36</v>
+      <c r="Q15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>35</v>
@@ -3093,17 +3084,17 @@
       <c r="V15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>35</v>
+      <c r="W15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>35</v>
+      <c r="Y15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA15" s="1" t="s">
         <v>36</v>
@@ -3111,64 +3102,67 @@
       <c r="AB15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE15" s="2" t="s">
-        <v>35</v>
+      <c r="AC15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG15" s="2" t="s">
-        <v>35</v>
+      <c r="AG15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI15" s="2" t="s">
-        <v>35</v>
+      <c r="AI15" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D16" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E16" s="3">
         <v>-32</v>
       </c>
       <c r="F16" s="3">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="G16" s="3">
+        <v>48</v>
       </c>
       <c r="H16" s="3">
-        <v>60</v>
-      </c>
-      <c r="I16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>36</v>
+        <v>98</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>36</v>
@@ -3185,8 +3179,8 @@
       <c r="U16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>36</v>
+      <c r="V16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>35</v>
@@ -3200,8 +3194,8 @@
       <c r="Z16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA16" s="2" t="s">
-        <v>35</v>
+      <c r="AA16" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>35</v>
@@ -3215,8 +3209,8 @@
       <c r="AE16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF16" s="1" t="s">
-        <v>36</v>
+      <c r="AF16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>35</v>
@@ -3230,76 +3224,76 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="D17" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E17" s="3">
         <v>-32</v>
       </c>
       <c r="F17" s="3">
-        <v>75</v>
-      </c>
-      <c r="G17" s="3">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="H17" s="3">
+        <v>60</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>36</v>
+      <c r="P17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>36</v>
+      <c r="AA17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC17" s="2" t="s">
         <v>35</v>
@@ -3310,14 +3304,14 @@
       <c r="AE17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF17" s="2" t="s">
-        <v>35</v>
+      <c r="AF17" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH17" s="1" t="s">
-        <v>36</v>
+      <c r="AH17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI17" s="2" t="s">
         <v>35</v>
@@ -3325,7 +3319,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -3346,31 +3340,34 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>35</v>
+      <c r="R18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>35</v>
@@ -3378,8 +3375,8 @@
       <c r="W18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X18" s="2" t="s">
-        <v>35</v>
+      <c r="X18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y18" s="1" t="s">
         <v>36</v>
@@ -3390,8 +3387,8 @@
       <c r="AA18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB18" s="2" t="s">
-        <v>35</v>
+      <c r="AB18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC18" s="2" t="s">
         <v>35</v>
@@ -3408,8 +3405,8 @@
       <c r="AG18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH18" s="2" t="s">
-        <v>35</v>
+      <c r="AH18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI18" s="2" t="s">
         <v>35</v>
@@ -3417,27 +3414,33 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="3">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="D19" s="3">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F19" s="3">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G19" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>113</v>
       </c>
       <c r="P19" s="2" t="s">
@@ -3446,38 +3449,38 @@
       <c r="Q19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>36</v>
+      <c r="R19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>35</v>
+      <c r="W19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>36</v>
+      <c r="AA19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC19" s="2" t="s">
         <v>35</v>
@@ -3494,8 +3497,8 @@
       <c r="AG19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH19" s="1" t="s">
-        <v>36</v>
+      <c r="AH19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI19" s="2" t="s">
         <v>35</v>
@@ -3509,58 +3512,49 @@
         <v>31</v>
       </c>
       <c r="C20" s="3">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="D20" s="3">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E20" s="3">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="G20" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>36</v>
+      <c r="P20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X20" s="2" t="s">
-        <v>35</v>
+      <c r="X20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>35</v>
@@ -3571,8 +3565,8 @@
       <c r="AA20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB20" s="2" t="s">
-        <v>35</v>
+      <c r="AB20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC20" s="2" t="s">
         <v>35</v>
@@ -3583,14 +3577,14 @@
       <c r="AE20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF20" s="1" t="s">
-        <v>36</v>
+      <c r="AF20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH20" s="2" t="s">
-        <v>35</v>
+      <c r="AH20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI20" s="2" t="s">
         <v>35</v>
@@ -3598,206 +3592,203 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="3">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="D21" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="3">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="F21" s="3">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G21" s="3">
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>36</v>
+      <c r="R21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>36</v>
+      <c r="W21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI21" s="1" t="s">
-        <v>36</v>
+      <c r="AG21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="3">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="D22" s="3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E22" s="3">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F22" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G22" s="3">
         <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>35</v>
+      <c r="P22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X22" s="2" t="s">
-        <v>35</v>
+      <c r="X22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI22" s="2" t="s">
-        <v>35</v>
+      <c r="Z22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3">
         <v>0.4</v>
@@ -3811,26 +3802,26 @@
       <c r="G23" s="3">
         <v>40</v>
       </c>
-      <c r="H23" s="3">
-        <v>12</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="K23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>36</v>
+      <c r="P23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>35</v>
@@ -3844,8 +3835,8 @@
       <c r="U23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V23" s="1" t="s">
-        <v>36</v>
+      <c r="V23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>36</v>
@@ -3859,8 +3850,8 @@
       <c r="Z23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA23" s="1" t="s">
-        <v>36</v>
+      <c r="AA23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>35</v>
@@ -3874,8 +3865,8 @@
       <c r="AE23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF23" s="1" t="s">
-        <v>36</v>
+      <c r="AF23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>35</v>
@@ -3889,55 +3880,58 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="3">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="D24" s="3">
         <v>0.4</v>
       </c>
       <c r="E24" s="3">
-        <v>-64</v>
+        <v>-32</v>
       </c>
       <c r="F24" s="3">
-        <v>-16</v>
+        <v>60</v>
       </c>
       <c r="G24" s="3">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H24" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>36</v>
+      <c r="R24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>36</v>
@@ -3945,85 +3939,82 @@
       <c r="W24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X24" s="1" t="s">
-        <v>36</v>
+      <c r="X24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Y24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z24" s="1" t="s">
-        <v>36</v>
+      <c r="Z24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>36</v>
+      <c r="AB24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI24" s="1" t="s">
-        <v>36</v>
+      <c r="AG24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="3">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="3">
-        <v>-32</v>
+        <v>-64</v>
       </c>
       <c r="F25" s="3">
-        <v>60</v>
+        <v>-16</v>
       </c>
       <c r="G25" s="3">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H25" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>35</v>
+      <c r="P25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>36</v>
@@ -4037,109 +4028,112 @@
       <c r="U25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>35</v>
+      <c r="V25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>35</v>
+      <c r="Y25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>35</v>
+      <c r="AC25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AI25" s="2" t="s">
-        <v>35</v>
+      <c r="AI25" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D26" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E26" s="3">
         <v>-32</v>
       </c>
       <c r="F26" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G26" s="3">
         <v>40</v>
       </c>
+      <c r="H26" s="3">
+        <v>9</v>
+      </c>
       <c r="J26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>36</v>
+      <c r="P26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X26" s="2" t="s">
-        <v>35</v>
+      <c r="X26" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y26" s="2" t="s">
         <v>35</v>
@@ -4150,8 +4144,8 @@
       <c r="AA26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB26" s="2" t="s">
-        <v>35</v>
+      <c r="AB26" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC26" s="2" t="s">
         <v>35</v>
@@ -4162,14 +4156,14 @@
       <c r="AE26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF26" s="1" t="s">
-        <v>36</v>
+      <c r="AF26" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH26" s="2" t="s">
-        <v>35</v>
+      <c r="AH26" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI26" s="2" t="s">
         <v>35</v>
@@ -4177,43 +4171,43 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="3">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="D27" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E27" s="3">
-        <v>-60</v>
+        <v>-32</v>
       </c>
       <c r="F27" s="3">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G27" s="3">
         <v>40</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="M27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>35</v>
@@ -4227,8 +4221,8 @@
       <c r="U27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V27" s="2" t="s">
-        <v>35</v>
+      <c r="V27" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>35</v>
@@ -4239,8 +4233,8 @@
       <c r="Y27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z27" s="1" t="s">
-        <v>36</v>
+      <c r="Z27" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA27" s="2" t="s">
         <v>35</v>
@@ -4248,62 +4242,62 @@
       <c r="AB27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG27" s="1" t="s">
-        <v>36</v>
+      <c r="AC27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG27" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI27" s="1" t="s">
-        <v>36</v>
+      <c r="AI27" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="3">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D28" s="3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="3">
-        <v>-32</v>
+        <v>-60</v>
       </c>
       <c r="F28" s="3">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="G28" s="3">
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
       </c>
@@ -4334,40 +4328,40 @@
       <c r="Y28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z28" s="2" t="s">
-        <v>35</v>
+      <c r="Z28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB28" s="1" t="s">
-        <v>36</v>
+      <c r="AB28" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE28" s="2" t="s">
-        <v>35</v>
+      <c r="AD28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG28" s="2" t="s">
-        <v>35</v>
+      <c r="AG28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI28" s="2" t="s">
-        <v>35</v>
+      <c r="AI28" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -4376,32 +4370,29 @@
         <v>190</v>
       </c>
       <c r="D29" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E29" s="3">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="F29" s="3">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G29" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
       </c>
@@ -4423,26 +4414,26 @@
       <c r="V29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="1" t="s">
-        <v>36</v>
+      <c r="W29" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y29" s="1" t="s">
-        <v>36</v>
+      <c r="Y29" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC29" s="2" t="s">
-        <v>35</v>
+      <c r="AA29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD29" s="2" t="s">
         <v>35</v>
@@ -4465,76 +4456,79 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D30" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E30" s="3">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F30" s="3">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G30" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K30" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>36</v>
+      <c r="R30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y30" s="2" t="s">
-        <v>35</v>
+      <c r="W30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB30" s="1" t="s">
-        <v>36</v>
+      <c r="AA30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>35</v>
@@ -4551,8 +4545,8 @@
       <c r="AG30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH30" s="1" t="s">
-        <v>36</v>
+      <c r="AH30" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI30" s="2" t="s">
         <v>35</v>
@@ -4560,13 +4554,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="3">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3">
         <v>0.3</v>
@@ -4575,28 +4569,28 @@
         <v>-32</v>
       </c>
       <c r="F31" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G31" s="3">
         <v>30</v>
       </c>
       <c r="J31" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>36</v>
+      <c r="P31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>36</v>
@@ -4610,8 +4604,8 @@
       <c r="U31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="V31" s="1" t="s">
-        <v>36</v>
+      <c r="V31" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>35</v>
@@ -4640,8 +4634,8 @@
       <c r="AE31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF31" s="1" t="s">
-        <v>36</v>
+      <c r="AF31" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>35</v>
@@ -4655,130 +4649,133 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="3">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D32" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F32" s="3">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="G32" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI32" s="1" t="s">
-        <v>36</v>
+      <c r="P32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI32" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="3">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D33" s="3">
         <v>0.25</v>
       </c>
       <c r="E33" s="3">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="G33" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="P33" s="2" t="s">
         <v>35</v>
       </c>
@@ -4809,8 +4806,8 @@
       <c r="Y33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z33" s="2" t="s">
-        <v>35</v>
+      <c r="Z33" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA33" s="1" t="s">
         <v>36</v>
@@ -4818,51 +4815,57 @@
       <c r="AB33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE33" s="2" t="s">
-        <v>35</v>
+      <c r="AC33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG33" s="2" t="s">
-        <v>35</v>
+      <c r="AG33" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI33" s="2" t="s">
-        <v>35</v>
+      <c r="AI33" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C34" s="3">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D34" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E34" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F34" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G34" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>181</v>
       </c>
       <c r="P34" s="2" t="s">
@@ -4871,38 +4874,38 @@
       <c r="Q34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>36</v>
+      <c r="R34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y34" s="2" t="s">
-        <v>35</v>
+      <c r="W34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB34" s="1" t="s">
-        <v>36</v>
+      <c r="AA34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC34" s="2" t="s">
         <v>35</v>
@@ -4919,8 +4922,8 @@
       <c r="AG34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH34" s="1" t="s">
-        <v>36</v>
+      <c r="AH34" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI34" s="2" t="s">
         <v>35</v>
@@ -4934,70 +4937,61 @@
         <v>31</v>
       </c>
       <c r="C35" s="3">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="D35" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="3">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="F35" s="3">
+        <v>90</v>
+      </c>
+      <c r="G35" s="3">
         <v>30</v>
       </c>
-      <c r="G35" s="3">
-        <v>26</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>36</v>
+        <v>90</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB35" s="2" t="s">
-        <v>35</v>
+      <c r="AA35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC35" s="2" t="s">
         <v>35</v>
@@ -5008,14 +5002,14 @@
       <c r="AE35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF35" s="1" t="s">
-        <v>36</v>
+      <c r="AF35" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH35" s="2" t="s">
-        <v>35</v>
+      <c r="AH35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI35" s="2" t="s">
         <v>35</v>
@@ -5023,40 +5017,43 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E36" s="3">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F36" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G36" s="3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>35</v>
+        <v>186</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>35</v>
@@ -5070,23 +5067,23 @@
       <c r="U36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>35</v>
+      <c r="V36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA36" s="2" t="s">
-        <v>35</v>
+      <c r="Y36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>35</v>
@@ -5097,17 +5094,17 @@
       <c r="AD36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH36" s="1" t="s">
-        <v>36</v>
+      <c r="AE36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI36" s="2" t="s">
         <v>35</v>
@@ -5115,16 +5112,16 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D37" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E37" s="3">
         <v>-32</v>
@@ -5136,13 +5133,13 @@
         <v>40</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>35</v>
@@ -5174,11 +5171,11 @@
       <c r="Y37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA37" s="1" t="s">
-        <v>36</v>
+      <c r="Z37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>35</v>
@@ -5189,17 +5186,17 @@
       <c r="AD37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE37" s="2" t="s">
-        <v>35</v>
+      <c r="AE37" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH37" s="2" t="s">
-        <v>35</v>
+      <c r="AG37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI37" s="2" t="s">
         <v>35</v>
@@ -5207,40 +5204,34 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D38" s="3">
         <v>0.4</v>
       </c>
       <c r="E38" s="3">
-        <v>30</v>
+        <v>-32</v>
       </c>
       <c r="F38" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G38" s="3">
         <v>40</v>
       </c>
-      <c r="H38" s="3">
-        <v>4</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>35</v>
@@ -5254,8 +5245,8 @@
       <c r="S38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T38" s="1" t="s">
-        <v>36</v>
+      <c r="T38" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>35</v>
@@ -5275,11 +5266,11 @@
       <c r="Z38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB38" s="1" t="s">
-        <v>36</v>
+      <c r="AA38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>35</v>
@@ -5296,8 +5287,8 @@
       <c r="AG38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH38" s="1" t="s">
-        <v>36</v>
+      <c r="AH38" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>35</v>
@@ -5305,37 +5296,40 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C39" s="3">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E39" s="3">
-        <v>-32</v>
+        <v>30</v>
       </c>
       <c r="F39" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G39" s="3">
         <v>40</v>
       </c>
+      <c r="H39" s="3">
+        <v>4</v>
+      </c>
       <c r="J39" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>35</v>
@@ -5349,8 +5343,8 @@
       <c r="S39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T39" s="2" t="s">
-        <v>35</v>
+      <c r="T39" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>35</v>
@@ -5358,76 +5352,79 @@
       <c r="V39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W39" s="1" t="s">
-        <v>36</v>
+      <c r="W39" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE39" s="1" t="s">
-        <v>36</v>
+      <c r="Y39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE39" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI39" s="1" t="s">
-        <v>36</v>
+      <c r="AG39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI39" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="3">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E40" s="3">
         <v>-32</v>
       </c>
       <c r="F40" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G40" s="3">
         <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>35</v>
@@ -5450,14 +5447,14 @@
       <c r="V40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W40" s="2" t="s">
-        <v>35</v>
+      <c r="W40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y40" s="2" t="s">
-        <v>35</v>
+      <c r="Y40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z40" s="1" t="s">
         <v>36</v>
@@ -5468,37 +5465,37 @@
       <c r="AB40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE40" s="2" t="s">
-        <v>35</v>
+      <c r="AC40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG40" s="2" t="s">
-        <v>35</v>
+      <c r="AG40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI40" s="2" t="s">
-        <v>35</v>
+      <c r="AI40" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3">
         <v>0.4</v>
@@ -5513,19 +5510,19 @@
         <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>36</v>
+        <v>209</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>35</v>
@@ -5539,8 +5536,8 @@
       <c r="U41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V41" s="1" t="s">
-        <v>36</v>
+      <c r="V41" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>35</v>
@@ -5554,76 +5551,70 @@
       <c r="Z41" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA41" s="2" t="s">
-        <v>35</v>
+      <c r="AA41" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG41" s="1" t="s">
-        <v>36</v>
+      <c r="AC41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG41" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI41" s="1" t="s">
-        <v>36</v>
+      <c r="AI41" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="3">
+        <v>170</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="3">
+        <v>-32</v>
+      </c>
+      <c r="F42" s="3">
+        <v>75</v>
+      </c>
+      <c r="G42" s="3">
+        <v>40</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="3">
-        <v>180</v>
-      </c>
-      <c r="D42" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="E42" s="3">
-        <v>20</v>
-      </c>
-      <c r="F42" s="3">
-        <v>60</v>
-      </c>
-      <c r="G42" s="3">
-        <v>35</v>
-      </c>
-      <c r="H42" s="3">
-        <v>6</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>35</v>
+      <c r="P42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>35</v>
@@ -5637,23 +5628,23 @@
       <c r="U42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W42" s="1" t="s">
-        <v>36</v>
+      <c r="V42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y42" s="1" t="s">
-        <v>36</v>
+      <c r="Y42" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Z42" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA42" s="1" t="s">
-        <v>36</v>
+      <c r="AA42" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>35</v>
@@ -5667,8 +5658,8 @@
       <c r="AE42" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF42" s="2" t="s">
-        <v>35</v>
+      <c r="AF42" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AG42" s="1" t="s">
         <v>36</v>
@@ -5682,40 +5673,46 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="3">
+        <v>180</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="E43" s="3">
+        <v>20</v>
+      </c>
+      <c r="F43" s="3">
+        <v>60</v>
+      </c>
+      <c r="G43" s="3">
+        <v>35</v>
+      </c>
+      <c r="H43" s="3">
+        <v>6</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="3">
-        <v>165</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>210</v>
-      </c>
-      <c r="G43" s="3">
-        <v>45</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>36</v>
+      <c r="P43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R43" s="2" t="s">
         <v>35</v>
@@ -5729,216 +5726,216 @@
       <c r="U43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>35</v>
+      <c r="V43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA43" s="2" t="s">
-        <v>35</v>
+      <c r="Y43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA43" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG43" s="2" t="s">
-        <v>35</v>
+      <c r="AC43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG43" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AH43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI43" s="2" t="s">
-        <v>35</v>
+      <c r="AI43" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="3">
+        <v>165</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>210</v>
+      </c>
+      <c r="G44" s="3">
+        <v>45</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="3">
-        <v>140</v>
-      </c>
-      <c r="D44" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="E44" s="3">
-        <v>20</v>
-      </c>
-      <c r="F44" s="3">
-        <v>120</v>
-      </c>
-      <c r="H44" s="3">
-        <v>60</v>
-      </c>
-      <c r="I44" s="3">
-        <v>10</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="P44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>36</v>
+      <c r="R44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>36</v>
+      <c r="W44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE44" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI44" s="1" t="s">
-        <v>36</v>
+      <c r="AG44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI44" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="3">
+        <v>140</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E45" s="3">
+        <v>20</v>
+      </c>
+      <c r="F45" s="3">
+        <v>120</v>
+      </c>
+      <c r="H45" s="3">
+        <v>60</v>
+      </c>
+      <c r="I45" s="3">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="3">
-        <v>170</v>
-      </c>
-      <c r="D45" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E45" s="3">
-        <v>-32</v>
-      </c>
-      <c r="F45" s="3">
-        <v>75</v>
-      </c>
-      <c r="G45" s="3">
-        <v>40</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="L45" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y45" s="2" t="s">
-        <v>35</v>
+        <v>141</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB45" s="2" t="s">
-        <v>35</v>
+      <c r="AA45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC45" s="1" t="s">
         <v>36</v>
@@ -5949,14 +5946,14 @@
       <c r="AE45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF45" s="2" t="s">
-        <v>35</v>
+      <c r="AF45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AG45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AH45" s="2" t="s">
-        <v>35</v>
+      <c r="AH45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI45" s="1" t="s">
         <v>36</v>
@@ -5964,37 +5961,34 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D46" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E46" s="3">
-        <v>60</v>
+        <v>-32</v>
       </c>
       <c r="F46" s="3">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G46" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>35</v>
@@ -6002,70 +5996,70 @@
       <c r="Q46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>36</v>
+      <c r="R46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE46" s="2" t="s">
-        <v>35</v>
+      <c r="W46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI46" s="2" t="s">
-        <v>35</v>
+      <c r="AG46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI46" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="3">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D47" s="3">
         <v>0.25</v>
@@ -6080,13 +6074,16 @@
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>111</v>
+        <v>232</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>35</v>
@@ -6094,17 +6091,17 @@
       <c r="Q47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>35</v>
+      <c r="R47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>35</v>
@@ -6112,8 +6109,8 @@
       <c r="W47" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X47" s="2" t="s">
-        <v>35</v>
+      <c r="X47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y47" s="1" t="s">
         <v>36</v>
@@ -6124,8 +6121,8 @@
       <c r="AA47" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB47" s="2" t="s">
-        <v>35</v>
+      <c r="AB47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC47" s="2" t="s">
         <v>35</v>
@@ -6142,8 +6139,8 @@
       <c r="AG47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH47" s="2" t="s">
-        <v>35</v>
+      <c r="AH47" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AI47" s="2" t="s">
         <v>35</v>
@@ -6151,43 +6148,40 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="3">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="D48" s="3">
         <v>0.25</v>
       </c>
       <c r="E48" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F48" s="3">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G48" s="3">
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>36</v>
+        <v>113</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>35</v>
@@ -6201,23 +6195,23 @@
       <c r="U48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W48" s="2" t="s">
-        <v>35</v>
+      <c r="V48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y48" s="2" t="s">
-        <v>35</v>
+      <c r="Y48" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA48" s="2" t="s">
-        <v>35</v>
+      <c r="AA48" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>35</v>
@@ -6231,8 +6225,8 @@
       <c r="AE48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF48" s="1" t="s">
-        <v>36</v>
+      <c r="AF48" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>35</v>
@@ -6246,34 +6240,37 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="3">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="D49" s="3">
         <v>0.25</v>
       </c>
       <c r="E49" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F49" s="3">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G49" s="3">
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>36</v>
@@ -6305,8 +6302,8 @@
       <c r="Y49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z49" s="1" t="s">
-        <v>36</v>
+      <c r="Z49" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA49" s="2" t="s">
         <v>35</v>
@@ -6314,37 +6311,37 @@
       <c r="AB49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE49" s="1" t="s">
-        <v>36</v>
+      <c r="AC49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE49" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF49" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG49" s="1" t="s">
-        <v>36</v>
+      <c r="AG49" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI49" s="1" t="s">
-        <v>36</v>
+      <c r="AI49" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="3">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D50" s="3">
         <v>0.25</v>
@@ -6359,72 +6356,164 @@
         <v>50</v>
       </c>
       <c r="J50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI50" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="3">
+        <v>140</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>60</v>
+      </c>
+      <c r="F51" s="3">
+        <v>210</v>
+      </c>
+      <c r="G51" s="3">
+        <v>50</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI50" s="1" t="s">
+      <c r="K51" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI51" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6554,10 +6643,10 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>26</v>
@@ -6566,12 +6655,12 @@
         <v>28</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6592,13 +6681,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6654,7 +6743,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6678,7 +6767,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6737,7 +6826,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6761,13 +6850,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6823,7 +6912,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6850,7 +6939,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -6859,7 +6948,7 @@
         <v>79</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -6915,7 +7004,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -6936,16 +7025,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -7001,10 +7090,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3">
         <v>350</v>
@@ -7025,13 +7114,13 @@
         <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -7087,7 +7176,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -7108,10 +7197,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7167,7 +7256,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7188,16 +7277,16 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -7253,7 +7342,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7274,16 +7363,16 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -7339,7 +7428,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7360,16 +7449,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -7425,10 +7514,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3">
         <v>220</v>
@@ -7449,16 +7538,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -7514,7 +7603,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -7535,13 +7624,13 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>55</v>
@@ -7600,7 +7689,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -7621,16 +7710,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -7686,7 +7775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7707,22 +7796,22 @@
         <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -7778,7 +7867,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7799,16 +7888,16 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -7864,7 +7953,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -7885,16 +7974,16 @@
         <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7950,7 +8039,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7971,13 +8060,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -8033,7 +8122,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -8054,16 +8143,16 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
@@ -8119,7 +8208,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>38</v>
@@ -8143,16 +8232,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>35</v>
@@ -8208,7 +8297,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8229,16 +8318,16 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -8294,7 +8383,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8315,16 +8404,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8380,7 +8469,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8401,16 +8490,16 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -8466,7 +8555,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8490,13 +8579,13 @@
         <v>81</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>83</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8552,7 +8641,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8573,16 +8662,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8638,7 +8727,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8659,13 +8748,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8721,7 +8810,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8742,16 +8831,16 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>55</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8807,7 +8896,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8828,19 +8917,19 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8896,7 +8985,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -8917,16 +9006,16 @@
         <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -9085,16 +9174,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -9102,7 +9191,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -9123,16 +9212,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -9167,7 +9256,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -9188,13 +9277,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9229,10 +9318,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3">
         <v>260</v>
@@ -9253,19 +9342,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -9300,7 +9389,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9321,16 +9410,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9365,7 +9454,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9389,13 +9478,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9430,7 +9519,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9451,16 +9540,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9495,7 +9584,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9519,16 +9608,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9563,7 +9652,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9584,19 +9673,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>35</v>
@@ -9631,7 +9720,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9655,16 +9744,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -9699,10 +9788,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C11" s="3">
         <v>260</v>
@@ -9723,13 +9812,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9764,7 +9853,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9788,19 +9877,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9835,7 +9924,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9856,19 +9945,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>35</v>
@@ -9903,7 +9992,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9924,13 +10013,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9971,7 +10060,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9992,16 +10081,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
@@ -10036,7 +10125,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -10057,19 +10146,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -10104,7 +10193,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -10134,7 +10223,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -10169,7 +10258,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -10190,16 +10279,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10234,7 +10323,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10255,16 +10344,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10299,7 +10388,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10320,16 +10409,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10364,7 +10453,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10385,16 +10474,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10429,7 +10518,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10450,16 +10539,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10494,7 +10583,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10521,7 +10610,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10530,7 +10619,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10565,7 +10654,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10586,13 +10675,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10627,7 +10716,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10648,16 +10737,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10692,7 +10781,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10713,13 +10802,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10754,7 +10843,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10775,16 +10864,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10819,7 +10908,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10978,16 +11067,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -11004,7 +11093,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -11028,7 +11117,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -11060,7 +11149,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -11081,13 +11170,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -11119,7 +11208,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -11143,16 +11232,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>36</v>
@@ -11184,13 +11273,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C5" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D5" s="3">
         <v>0.45</v>
@@ -11208,16 +11297,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>36</v>
@@ -11249,7 +11338,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11270,13 +11359,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -11308,7 +11397,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11338,7 +11427,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11370,7 +11459,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11391,16 +11480,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11432,7 +11521,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11456,16 +11545,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11497,7 +11586,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11518,16 +11607,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>35</v>
@@ -11559,7 +11648,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11580,19 +11669,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -11624,7 +11713,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11645,10 +11734,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11686,7 +11775,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11748,10 +11837,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3">
         <v>120</v>
@@ -11772,13 +11861,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11810,7 +11899,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11834,16 +11923,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11875,7 +11964,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11902,7 +11991,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11940,7 +12029,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11961,16 +12050,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -12002,7 +12091,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -12023,19 +12112,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -12067,7 +12156,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -12088,16 +12177,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -12132,7 +12221,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -12153,16 +12242,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -12194,7 +12283,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -12215,13 +12304,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12253,7 +12342,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12280,10 +12369,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12315,7 +12404,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12336,13 +12425,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12374,7 +12463,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12395,7 +12484,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12427,7 +12516,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12448,16 +12537,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>36</v>
@@ -12489,7 +12578,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12548,7 +12637,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12569,13 +12658,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12607,7 +12696,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12628,13 +12717,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12666,7 +12755,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12687,16 +12776,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -12728,7 +12817,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12758,10 +12847,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12793,7 +12882,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12814,13 +12903,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12852,7 +12941,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12873,13 +12962,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12911,7 +13000,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12932,13 +13021,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12970,7 +13059,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12991,13 +13080,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -13029,7 +13118,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -13050,13 +13139,13 @@
         <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -13088,7 +13177,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>38</v>
@@ -13250,18 +13339,18 @@
         <v>16</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -13285,16 +13374,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13317,7 +13406,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -13338,13 +13427,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -6524,7 +6524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AF29"/>
+  <dimension ref="A1:AG29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.277278900146484" customWidth="1" style="3"/>
@@ -6555,11 +6555,11 @@
     <col min="26" max="26" width="9.140625" customWidth="1" style="3"/>
     <col min="27" max="27" width="10.328712463378906" customWidth="1" style="3"/>
     <col min="28" max="28" width="11.9512939453125" customWidth="1" style="3"/>
-    <col min="29" max="29" width="11.877633094787598" customWidth="1" style="3"/>
-    <col min="30" max="30" width="9.140625" customWidth="1" style="3"/>
+    <col min="29" max="29" width="9.530721664428711" customWidth="1" style="3"/>
+    <col min="30" max="30" width="11.877633094787598" customWidth="1" style="3"/>
     <col min="31" max="31" width="9.140625" customWidth="1" style="3"/>
-    <col min="32" max="32" width="12.787137985229492" customWidth="1" style="3"/>
-    <col min="33" max="33" width="9.140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="9.140625" customWidth="1" style="3"/>
+    <col min="33" max="33" width="12.787137985229492" customWidth="1" style="3"/>
     <col min="34" max="34" width="9.140625" customWidth="1" style="3"/>
     <col min="35" max="35" width="9.140625" customWidth="1" style="3"/>
     <col min="36" max="36" width="9.140625" customWidth="1" style="3"/>
@@ -6646,15 +6646,18 @@
         <v>248</v>
       </c>
       <c r="AC1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>250</v>
       </c>
     </row>
@@ -6672,7 +6675,7 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -6692,52 +6695,55 @@
       <c r="P2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>36</v>
+      <c r="Q2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>35</v>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>36</v>
+      <c r="Y2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>36</v>
+      <c r="AD2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6755,7 +6761,7 @@
         <v>0.3</v>
       </c>
       <c r="E3" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -6784,14 +6790,14 @@
       <c r="S3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>36</v>
+      <c r="T3" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>36</v>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>36</v>
@@ -6802,26 +6808,29 @@
       <c r="Y3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="2" t="s">
-        <v>35</v>
+      <c r="Z3" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>36</v>
+      <c r="AB3" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>36</v>
+      <c r="AD3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -6838,7 +6847,7 @@
         <v>0.3</v>
       </c>
       <c r="E4" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -6861,23 +6870,23 @@
       <c r="P4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>36</v>
+      <c r="Q4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>36</v>
+      <c r="U4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>36</v>
@@ -6885,29 +6894,32 @@
       <c r="X4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>35</v>
+      <c r="Y4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>35</v>
+      <c r="AB4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AE4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF4" s="1" t="s">
-        <v>36</v>
+      <c r="AF4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -6989,16 +7001,19 @@
       <c r="AB5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>36</v>
+      <c r="AC5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7075,16 +7090,19 @@
       <c r="AB6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>36</v>
+      <c r="AC6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7164,13 +7182,16 @@
       <c r="AC7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AD7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>35</v>
+      <c r="AD7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG7" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7241,16 +7262,19 @@
       <c r="AB8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>35</v>
+      <c r="AC8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AE8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AF8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7327,16 +7351,19 @@
       <c r="AB9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>35</v>
+      <c r="AC9" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>36</v>
+      <c r="AE9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7413,16 +7440,19 @@
       <c r="AB10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7505,10 +7535,13 @@
       <c r="AD11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF11" s="2" t="s">
+      <c r="AE11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7588,16 +7621,19 @@
       <c r="AB12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>35</v>
+      <c r="AC12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AE12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF12" s="1" t="s">
+      <c r="AF12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG12" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7677,13 +7713,16 @@
       <c r="AC13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD13" s="2" t="s">
-        <v>35</v>
+      <c r="AD13" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AE13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AF13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7766,10 +7805,13 @@
       <c r="AD14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF14" s="2" t="s">
+      <c r="AE14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7855,13 +7897,16 @@
       <c r="AC15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF15" s="2" t="s">
+      <c r="AD15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG15" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7938,8 +7983,8 @@
       <c r="AB16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC16" s="2" t="s">
-        <v>35</v>
+      <c r="AC16" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>35</v>
@@ -7947,7 +7992,10 @@
       <c r="AE16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AF16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG16" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8027,13 +8075,16 @@
       <c r="AC17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF17" s="2" t="s">
+      <c r="AD17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG17" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8110,13 +8161,16 @@
       <c r="AC18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>36</v>
+      <c r="AD18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8196,13 +8250,16 @@
       <c r="AC19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE19" s="1" t="s">
-        <v>36</v>
+      <c r="AD19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG19" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8285,13 +8342,16 @@
       <c r="AC20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD20" s="2" t="s">
-        <v>35</v>
+      <c r="AD20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AE20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF20" s="1" t="s">
+      <c r="AF20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG20" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8371,13 +8431,16 @@
       <c r="AC21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>36</v>
+      <c r="AD21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG21" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8463,7 +8526,10 @@
       <c r="AE22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AF22" s="1" t="s">
+      <c r="AF22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG22" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8540,16 +8606,19 @@
       <c r="AB23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>36</v>
+      <c r="AC23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG23" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8626,16 +8695,19 @@
       <c r="AB24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF24" s="2" t="s">
+      <c r="AC24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG24" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8715,13 +8787,16 @@
       <c r="AC25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>36</v>
+      <c r="AD25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG25" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8798,13 +8873,16 @@
       <c r="AC26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE26" s="1" t="s">
-        <v>36</v>
+      <c r="AD26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE26" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG26" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8884,13 +8962,16 @@
       <c r="AC27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>36</v>
+      <c r="AD27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG27" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8973,13 +9054,16 @@
       <c r="AC28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>36</v>
+      <c r="AD28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG28" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -9059,13 +9143,16 @@
       <c r="AC29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE29" s="1" t="s">
-        <v>36</v>
+      <c r="AD29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG29" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1558,6 +1558,12 @@
   </si>
   <si>
     <t>nether_topaz</t>
+  </si>
+  <si>
+    <t>flavolite</t>
+  </si>
+  <si>
+    <t>sandy_jadestone</t>
   </si>
   <si>
     <t>venus_manual_salt</t>
@@ -1707,8 +1713,7 @@
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
-    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -6577,8 +6582,7 @@
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
-    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -9219,8 +9223,7 @@
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
-    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -11127,8 +11130,7 @@
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
-    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -13346,7 +13348,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.293367385864258" customWidth="1" style="3"/>
@@ -13369,9 +13371,9 @@
     <col min="18" max="18" width="9.140625" customWidth="1" style="3"/>
     <col min="19" max="19" width="10.040207862854004" customWidth="1" style="3"/>
     <col min="20" max="20" width="9.140625" customWidth="1" style="3"/>
-    <col min="21" max="21" width="12.787137985229492" customWidth="1" style="3"/>
-    <col min="22" max="22" width="9.140625" customWidth="1" style="3"/>
-    <col min="23" max="23" width="9.140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="9.140625" customWidth="1" style="3"/>
+    <col min="22" max="22" width="16.62772560119629" customWidth="1" style="3"/>
+    <col min="23" max="23" width="12.787137985229492" customWidth="1" style="3"/>
     <col min="24" max="24" width="9.140625" customWidth="1" style="3"/>
     <col min="25" max="25" width="9.140625" customWidth="1" style="3"/>
     <col min="26" max="26" width="9.140625" customWidth="1" style="3"/>
@@ -13396,8 +13398,7 @@
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
-    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -13444,15 +13445,21 @@
         <v>409</v>
       </c>
       <c r="T1" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -13476,16 +13483,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13503,12 +13510,18 @@
         <v>36</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -13529,13 +13542,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>
@@ -13553,6 +13566,12 @@
         <v>36</v>
       </c>
       <c r="U3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -6481,7 +6481,7 @@
         <v>82</v>
       </c>
       <c r="C2" s="3">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="D2" s="3">
         <v>0.2</v>
@@ -6769,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="3">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="D5" s="3">
         <v>0.12</v>
@@ -6781,7 +6781,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>330</v>
@@ -6810,20 +6810,20 @@
       <c r="V5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="2" t="s">
-        <v>25</v>
+      <c r="W5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="2" t="s">
-        <v>25</v>
+      <c r="Y5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA5" s="2" t="s">
-        <v>25</v>
+      <c r="AA5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>26</v>
@@ -6861,7 +6861,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D6" s="3">
         <v>0.22</v>
@@ -6873,7 +6873,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>333</v>
@@ -6905,20 +6905,20 @@
       <c r="V6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>25</v>
+      <c r="W6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>25</v>
+      <c r="Y6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>25</v>
+      <c r="AA6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>25</v>
@@ -6956,7 +6956,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="3">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="D7" s="3">
         <v>0.14</v>
@@ -6968,7 +6968,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>337</v>
@@ -7324,7 +7324,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="3">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3">
         <v>0.2</v>
@@ -7336,7 +7336,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>349</v>
@@ -7968,7 +7968,7 @@
         <v>82</v>
       </c>
       <c r="C18" s="3">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="D18" s="3">
         <v>0.15</v>
@@ -8377,17 +8377,17 @@
       <c r="Q22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>25</v>
+      <c r="R22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>25</v>
@@ -8395,8 +8395,8 @@
       <c r="W22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X22" s="2" t="s">
-        <v>25</v>
+      <c r="X22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>25</v>
@@ -8407,8 +8407,8 @@
       <c r="AA22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB22" s="2" t="s">
-        <v>25</v>
+      <c r="AB22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>26</v>
@@ -8425,14 +8425,14 @@
       <c r="AG22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH22" s="2" t="s">
-        <v>25</v>
+      <c r="AH22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ22" s="2" t="s">
-        <v>25</v>
+      <c r="AJ22" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -8443,7 +8443,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="3">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="D23" s="3">
         <v>0.2</v>
@@ -8455,7 +8455,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>387</v>
@@ -8490,20 +8490,20 @@
       <c r="V23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W23" s="2" t="s">
-        <v>25</v>
+      <c r="W23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y23" s="2" t="s">
-        <v>25</v>
+      <c r="Y23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA23" s="2" t="s">
-        <v>25</v>
+      <c r="AA23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB23" s="1" t="s">
         <v>26</v>
@@ -8567,17 +8567,17 @@
       <c r="Q24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>25</v>
+      <c r="R24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V24" s="2" t="s">
         <v>25</v>
@@ -8585,8 +8585,8 @@
       <c r="W24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X24" s="2" t="s">
-        <v>25</v>
+      <c r="X24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>25</v>
@@ -8597,8 +8597,8 @@
       <c r="AA24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB24" s="2" t="s">
-        <v>25</v>
+      <c r="AB24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>26</v>
@@ -8615,14 +8615,14 @@
       <c r="AG24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH24" s="2" t="s">
-        <v>25</v>
+      <c r="AH24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ24" s="2" t="s">
-        <v>25</v>
+      <c r="AJ24" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -8639,10 +8639,10 @@
         <v>0.18</v>
       </c>
       <c r="E25" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3">
         <v>20</v>
@@ -8731,7 +8731,7 @@
         <v>20</v>
       </c>
       <c r="C26" s="3">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="D26" s="3">
         <v>0.15</v>
@@ -8743,7 +8743,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>398</v>
@@ -9194,7 +9194,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="D31" s="3">
         <v>0.2</v>
@@ -9206,7 +9206,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H31" s="3">
         <v>5</v>
@@ -9292,7 +9292,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="3">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="D32" s="3">
         <v>0.18</v>
@@ -9304,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>415</v>
@@ -9339,20 +9339,20 @@
       <c r="V32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W32" s="2" t="s">
-        <v>25</v>
+      <c r="W32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y32" s="2" t="s">
-        <v>25</v>
+      <c r="Y32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA32" s="2" t="s">
-        <v>25</v>
+      <c r="AA32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>25</v>
@@ -9413,11 +9413,11 @@
       <c r="K33" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>25</v>
+      <c r="P33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>25</v>
@@ -9431,8 +9431,8 @@
       <c r="U33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V33" s="2" t="s">
-        <v>25</v>
+      <c r="V33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W33" s="2" t="s">
         <v>25</v>
@@ -9461,8 +9461,8 @@
       <c r="AE33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF33" s="2" t="s">
-        <v>25</v>
+      <c r="AF33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG33" s="1" t="s">
         <v>26</v>
@@ -9574,7 +9574,7 @@
         <v>20</v>
       </c>
       <c r="C35" s="3">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="D35" s="3">
         <v>0.23</v>
@@ -9586,7 +9586,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>424</v>
@@ -9761,7 +9761,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="3">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="D37" s="3">
         <v>0.15</v>
@@ -9773,7 +9773,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>430</v>
@@ -9817,8 +9817,8 @@
       <c r="Y37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z37" s="2" t="s">
-        <v>25</v>
+      <c r="Z37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA37" s="2" t="s">
         <v>25</v>
@@ -9826,26 +9826,26 @@
       <c r="AB37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE37" s="2" t="s">
-        <v>25</v>
+      <c r="AC37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG37" s="2" t="s">
-        <v>25</v>
+      <c r="AG37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI37" s="2" t="s">
-        <v>25</v>
+      <c r="AI37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ37" s="1" t="s">
         <v>26</v>
@@ -9859,7 +9859,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="3">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D38" s="3">
         <v>0.15</v>
@@ -9871,7 +9871,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>435</v>
@@ -9957,7 +9957,7 @@
         <v>34</v>
       </c>
       <c r="C39" s="3">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="D39" s="3">
         <v>0.25</v>
@@ -9969,7 +9969,7 @@
         <v>20</v>
       </c>
       <c r="G39" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H39" s="3">
         <v>5</v>
@@ -10167,11 +10167,11 @@
       <c r="J41" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>25</v>
+      <c r="P41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>25</v>
@@ -10185,8 +10185,8 @@
       <c r="U41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V41" s="2" t="s">
-        <v>25</v>
+      <c r="V41" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>25</v>
@@ -10215,8 +10215,8 @@
       <c r="AE41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF41" s="2" t="s">
-        <v>25</v>
+      <c r="AF41" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG41" s="1" t="s">
         <v>26</v>
@@ -10239,7 +10239,7 @@
         <v>20</v>
       </c>
       <c r="C42" s="3">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="D42" s="3">
         <v>0.2</v>
@@ -10251,7 +10251,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>450</v>
@@ -10788,7 +10788,7 @@
         <v>20</v>
       </c>
       <c r="C48" s="3">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="D48" s="3">
         <v>0.1</v>
@@ -10800,7 +10800,7 @@
         <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>467</v>
@@ -10978,7 +10978,7 @@
         <v>82</v>
       </c>
       <c r="C50" s="3">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="D50" s="3">
         <v>0.2</v>
@@ -11079,7 +11079,7 @@
         <v>20</v>
       </c>
       <c r="C51" s="3">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3">
         <v>0.2</v>
@@ -11091,7 +11091,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>480</v>
@@ -11135,8 +11135,8 @@
       <c r="Y51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z51" s="2" t="s">
-        <v>25</v>
+      <c r="Z51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA51" s="2" t="s">
         <v>25</v>
@@ -11144,26 +11144,26 @@
       <c r="AB51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE51" s="2" t="s">
-        <v>25</v>
+      <c r="AC51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG51" s="2" t="s">
-        <v>25</v>
+      <c r="AG51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI51" s="2" t="s">
-        <v>25</v>
+      <c r="AI51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ51" s="2" t="s">
         <v>25</v>
@@ -11177,7 +11177,7 @@
         <v>20</v>
       </c>
       <c r="C52" s="3">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="D52" s="3">
         <v>0.15</v>
@@ -11189,7 +11189,7 @@
         <v>20</v>
       </c>
       <c r="G52" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>484</v>
@@ -11221,20 +11221,20 @@
       <c r="V52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W52" s="2" t="s">
-        <v>25</v>
+      <c r="W52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y52" s="2" t="s">
-        <v>25</v>
+      <c r="Y52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA52" s="2" t="s">
-        <v>25</v>
+      <c r="AA52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB52" s="1" t="s">
         <v>26</v>
@@ -11367,7 +11367,7 @@
         <v>20</v>
       </c>
       <c r="C54" s="3">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="D54" s="3">
         <v>0.2</v>
@@ -11379,7 +11379,7 @@
         <v>20</v>
       </c>
       <c r="G54" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>492</v>
@@ -11580,11 +11580,11 @@
       <c r="L56" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>25</v>
+      <c r="P56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>25</v>
@@ -11598,8 +11598,8 @@
       <c r="U56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V56" s="2" t="s">
-        <v>25</v>
+      <c r="V56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>26</v>
@@ -11628,8 +11628,8 @@
       <c r="AE56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF56" s="2" t="s">
-        <v>25</v>
+      <c r="AF56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>25</v>
@@ -11741,7 +11741,7 @@
         <v>20</v>
       </c>
       <c r="C58" s="3">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="D58" s="3">
         <v>0.2</v>
@@ -11753,7 +11753,7 @@
         <v>20</v>
       </c>
       <c r="G58" s="3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>502</v>
@@ -11794,8 +11794,8 @@
       <c r="Y58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z58" s="2" t="s">
-        <v>25</v>
+      <c r="Z58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA58" s="2" t="s">
         <v>25</v>
@@ -11803,26 +11803,26 @@
       <c r="AB58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE58" s="2" t="s">
-        <v>25</v>
+      <c r="AC58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG58" s="2" t="s">
-        <v>25</v>
+      <c r="AG58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI58" s="2" t="s">
-        <v>25</v>
+      <c r="AI58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ58" s="1" t="s">
         <v>26</v>
@@ -12106,7 +12106,7 @@
         <v>20</v>
       </c>
       <c r="C62" s="3">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3">
         <v>0.15</v>
@@ -12118,7 +12118,7 @@
         <v>20</v>
       </c>
       <c r="G62" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>512</v>
@@ -12239,20 +12239,20 @@
       <c r="V63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W63" s="2" t="s">
-        <v>25</v>
+      <c r="W63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y63" s="2" t="s">
-        <v>25</v>
+      <c r="Y63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA63" s="2" t="s">
-        <v>25</v>
+      <c r="AA63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB63" s="2" t="s">
         <v>25</v>
@@ -12290,7 +12290,7 @@
         <v>20</v>
       </c>
       <c r="C64" s="3">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D64" s="3">
         <v>0.2</v>
@@ -12302,7 +12302,7 @@
         <v>20</v>
       </c>
       <c r="G64" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>518</v>
@@ -12346,8 +12346,8 @@
       <c r="Y64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z64" s="2" t="s">
-        <v>25</v>
+      <c r="Z64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA64" s="2" t="s">
         <v>25</v>
@@ -12355,26 +12355,26 @@
       <c r="AB64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE64" s="2" t="s">
-        <v>25</v>
+      <c r="AC64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG64" s="2" t="s">
-        <v>25</v>
+      <c r="AG64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI64" s="2" t="s">
-        <v>25</v>
+      <c r="AI64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ64" s="1" t="s">
         <v>26</v>
@@ -12388,7 +12388,7 @@
         <v>20</v>
       </c>
       <c r="C65" s="3">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D65" s="3">
         <v>0.25</v>
@@ -12400,7 +12400,7 @@
         <v>20</v>
       </c>
       <c r="G65" s="3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>521</v>
@@ -12441,8 +12441,8 @@
       <c r="Y65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z65" s="2" t="s">
-        <v>25</v>
+      <c r="Z65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA65" s="2" t="s">
         <v>25</v>
@@ -12450,26 +12450,26 @@
       <c r="AB65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE65" s="2" t="s">
-        <v>25</v>
+      <c r="AC65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG65" s="2" t="s">
-        <v>25</v>
+      <c r="AG65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI65" s="2" t="s">
-        <v>25</v>
+      <c r="AI65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ65" s="2" t="s">
         <v>25</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
   <si>
     <t>Vein ID</t>
   </si>
@@ -447,7 +447,13 @@
     <t>deep_sulfur</t>
   </si>
   <si>
-    <t>sulfur: 10 [1]</t>
+    <t>sulfur: 90 [1]</t>
+  </si>
+  <si>
+    <t>bornite: 5</t>
+  </si>
+  <si>
+    <t>chalcocite: 5</t>
   </si>
   <si>
     <t>deep_tantalite</t>
@@ -510,10 +516,7 @@
     <t>high_coal</t>
   </si>
   <si>
-    <t>coal: 9</t>
-  </si>
-  <si>
-    <t>diamond: 1</t>
+    <t>coal: 100</t>
   </si>
   <si>
     <t>high_gypsum</t>
@@ -4840,7 +4843,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="3">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="3">
         <v>-60</v>
@@ -4856,6 +4859,12 @@
       </c>
       <c r="J25" s="3" t="s">
         <v>143</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -4944,7 +4953,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -4965,16 +4974,16 @@
         <v>28</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -5063,7 +5072,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -5084,16 +5093,16 @@
         <v>28</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>43</v>
@@ -5182,7 +5191,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -5203,10 +5212,10 @@
         <v>30</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -5295,7 +5304,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -5316,16 +5325,16 @@
         <v>24</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -5414,7 +5423,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -5435,7 +5444,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>44</v>
@@ -5524,7 +5533,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -5545,10 +5554,7 @@
         <v>30</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>44</v>
@@ -5637,7 +5643,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -5658,7 +5664,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>44</v>
@@ -5747,7 +5753,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -5768,10 +5774,10 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>44</v>
@@ -5860,7 +5866,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>46</v>
@@ -5884,13 +5890,13 @@
         <v>5</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>44</v>
@@ -5979,7 +5985,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -6000,7 +6006,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>44</v>
@@ -6089,7 +6095,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -6110,13 +6116,13 @@
         <v>25</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>44</v>
@@ -6205,7 +6211,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -6226,10 +6232,10 @@
         <v>15</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>44</v>
@@ -6318,7 +6324,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -6339,10 +6345,10 @@
         <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>43</v>
@@ -6431,7 +6437,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -6452,10 +6458,10 @@
         <v>16</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>43</v>
@@ -6544,7 +6550,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -6565,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>43</v>
@@ -6654,7 +6660,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -6675,13 +6681,13 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>44</v>
@@ -6770,7 +6776,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -6791,10 +6797,10 @@
         <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>43</v>
@@ -6883,7 +6889,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -6904,13 +6910,13 @@
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>43</v>
@@ -6999,7 +7005,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -7020,10 +7026,10 @@
         <v>15</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>44</v>
@@ -7112,7 +7118,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -7133,10 +7139,10 @@
         <v>15</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>43</v>
@@ -7225,7 +7231,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -7246,10 +7252,10 @@
         <v>10</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>43</v>
@@ -7338,7 +7344,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>46</v>
@@ -7362,10 +7368,10 @@
         <v>4</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>43</v>
@@ -7454,7 +7460,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>62</v>
@@ -7478,10 +7484,10 @@
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>43</v>
@@ -7570,7 +7576,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>46</v>
@@ -7594,13 +7600,13 @@
         <v>10</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>43</v>
@@ -7689,7 +7695,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>46</v>
@@ -7713,10 +7719,10 @@
         <v>8</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>44</v>
@@ -7805,7 +7811,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>62</v>
@@ -7829,13 +7835,13 @@
         <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>44</v>
@@ -7924,7 +7930,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -7954,7 +7960,7 @@
         <v>108</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>43</v>
@@ -8043,7 +8049,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -8064,7 +8070,7 @@
         <v>15</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>43</v>
@@ -8153,7 +8159,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -8174,7 +8180,7 @@
         <v>5</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>44</v>
@@ -8263,7 +8269,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -8284,7 +8290,7 @@
         <v>10</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>44</v>
@@ -8373,7 +8379,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -8394,7 +8400,7 @@
         <v>15</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>44</v>
@@ -8483,7 +8489,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -8504,7 +8510,7 @@
         <v>15</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>43</v>
@@ -8593,7 +8599,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -8614,7 +8620,7 @@
         <v>15</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>43</v>
@@ -8703,7 +8709,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -8724,7 +8730,7 @@
         <v>15</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>43</v>
@@ -8813,7 +8819,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -8834,7 +8840,7 @@
         <v>5</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>44</v>
@@ -8923,7 +8929,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -8944,7 +8950,7 @@
         <v>15</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>44</v>
@@ -9033,7 +9039,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -9054,7 +9060,7 @@
         <v>15</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>43</v>
@@ -9143,7 +9149,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -9164,7 +9170,7 @@
         <v>5</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>44</v>
@@ -9253,7 +9259,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -9274,7 +9280,7 @@
         <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>44</v>
@@ -9363,7 +9369,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -9384,10 +9390,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>43</v>
@@ -9476,7 +9482,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -9497,7 +9503,7 @@
         <v>10</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>43</v>
@@ -9586,7 +9592,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -9607,7 +9613,7 @@
         <v>10</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -9830,13 +9836,13 @@
         <v>25</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>31</v>
@@ -9845,12 +9851,12 @@
         <v>33</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -9871,13 +9877,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -9936,7 +9942,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -9957,13 +9963,13 @@
         <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -10022,7 +10028,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -10043,16 +10049,16 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -10111,7 +10117,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>46</v>
@@ -10135,16 +10141,16 @@
         <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>81</v>
@@ -10206,7 +10212,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -10227,13 +10233,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>81</v>
@@ -10295,7 +10301,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>62</v>
@@ -10319,13 +10325,13 @@
         <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -10384,7 +10390,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -10405,10 +10411,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>43</v>
@@ -10467,7 +10473,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -10488,13 +10494,13 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>81</v>
@@ -10556,7 +10562,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -10577,13 +10583,13 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>81</v>
@@ -10645,7 +10651,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -10666,16 +10672,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -10734,7 +10740,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>62</v>
@@ -10758,16 +10764,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>43</v>
@@ -10826,7 +10832,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -10847,13 +10853,13 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>95</v>
@@ -10915,7 +10921,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -10936,16 +10942,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -11004,7 +11010,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -11025,19 +11031,19 @@
         <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>81</v>
@@ -11099,7 +11105,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -11120,13 +11126,13 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>81</v>
@@ -11188,7 +11194,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -11209,13 +11215,13 @@
         <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>81</v>
@@ -11277,7 +11283,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -11298,13 +11304,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -11363,7 +11369,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -11384,13 +11390,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>81</v>
@@ -11452,7 +11458,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -11476,16 +11482,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>43</v>
@@ -11544,7 +11550,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -11565,13 +11571,13 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>81</v>
@@ -11633,7 +11639,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -11654,16 +11660,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -11722,7 +11728,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -11743,16 +11749,16 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -11811,7 +11817,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -11832,13 +11838,13 @@
         <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>81</v>
@@ -11900,7 +11906,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -11921,16 +11927,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -11989,7 +11995,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -12010,13 +12016,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -12075,7 +12081,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -12096,16 +12102,16 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>95</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>43</v>
@@ -12164,7 +12170,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -12185,19 +12191,19 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -12256,7 +12262,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -12277,16 +12283,16 @@
         <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -12458,16 +12464,16 @@
         <v>21</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>31</v>
@@ -12475,7 +12481,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -12496,16 +12502,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -12540,7 +12546,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -12561,13 +12567,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -12602,7 +12608,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>62</v>
@@ -12626,19 +12632,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -12673,7 +12679,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -12694,16 +12700,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>43</v>
@@ -12738,7 +12744,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -12759,16 +12765,16 @@
         <v>30</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>44</v>
@@ -12803,7 +12809,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -12824,16 +12830,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -12868,7 +12874,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>46</v>
@@ -12892,16 +12898,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -12936,7 +12942,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -12957,19 +12963,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>43</v>
@@ -13004,7 +13010,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>46</v>
@@ -13028,16 +13034,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -13072,7 +13078,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>62</v>
@@ -13096,13 +13102,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -13137,7 +13143,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
@@ -13161,19 +13167,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>43</v>
@@ -13208,7 +13214,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -13229,19 +13235,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -13276,7 +13282,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -13297,19 +13303,19 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -13344,7 +13350,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -13365,16 +13371,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>44</v>
@@ -13409,7 +13415,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -13430,19 +13436,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -13477,7 +13483,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -13498,16 +13504,16 @@
         <v>35</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -13542,7 +13548,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -13563,16 +13569,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>44</v>
@@ -13607,7 +13613,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -13628,16 +13634,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -13672,7 +13678,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -13693,16 +13699,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -13737,7 +13743,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -13758,16 +13764,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>44</v>
@@ -13802,7 +13808,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -13823,16 +13829,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>44</v>
@@ -13867,7 +13873,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>46</v>
@@ -13891,16 +13897,16 @@
         <v>8</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>99</v>
@@ -13938,7 +13944,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -13959,13 +13965,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -14000,7 +14006,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -14021,16 +14027,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -14065,7 +14071,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -14086,13 +14092,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>44</v>
@@ -14127,7 +14133,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -14148,16 +14154,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -14192,7 +14198,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
@@ -14216,16 +14222,16 @@
         <v>16</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>44</v>
@@ -14361,16 +14367,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>21</v>
@@ -14387,7 +14393,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -14411,7 +14417,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -14443,7 +14449,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -14464,13 +14470,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -14502,7 +14508,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>46</v>
@@ -14526,16 +14532,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>44</v>
@@ -14567,7 +14573,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>62</v>
@@ -14591,16 +14597,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>44</v>
@@ -14632,7 +14638,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -14653,13 +14659,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>43</v>
@@ -14691,7 +14697,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -14712,16 +14718,16 @@
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -14753,7 +14759,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -14774,16 +14780,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -14815,7 +14821,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -14839,16 +14845,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>44</v>
@@ -14880,7 +14886,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -14901,16 +14907,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -14942,7 +14948,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -14963,19 +14969,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -15007,7 +15013,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -15028,16 +15034,16 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>44</v>
@@ -15069,7 +15075,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -15096,10 +15102,10 @@
         <v>52</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -15131,7 +15137,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>62</v>
@@ -15155,13 +15161,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -15193,7 +15199,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -15217,16 +15223,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -15258,7 +15264,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -15279,19 +15285,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>95</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>44</v>
@@ -15323,7 +15329,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -15344,16 +15350,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -15385,7 +15391,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -15406,19 +15412,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -15450,7 +15456,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -15471,19 +15477,19 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -15515,7 +15521,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -15536,16 +15542,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -15577,7 +15583,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -15598,13 +15604,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -15636,7 +15642,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -15657,16 +15663,16 @@
         <v>31</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -15698,7 +15704,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -15719,13 +15725,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -15757,7 +15763,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -15778,7 +15784,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>44</v>
@@ -15810,7 +15816,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -15831,16 +15837,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>44</v>
@@ -15872,7 +15878,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -15893,13 +15899,13 @@
         <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -15931,7 +15937,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -15952,13 +15958,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -15990,7 +15996,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -16011,13 +16017,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -16049,7 +16055,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -16070,16 +16076,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -16111,7 +16117,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>46</v>
@@ -16135,16 +16141,16 @@
         <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>43</v>
@@ -16176,7 +16182,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -16197,13 +16203,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>43</v>
@@ -16235,7 +16241,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -16256,13 +16262,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>43</v>
@@ -16294,7 +16300,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -16315,13 +16321,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>44</v>
@@ -16353,7 +16359,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -16374,13 +16380,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>44</v>
@@ -16412,7 +16418,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -16433,13 +16439,13 @@
         <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>43</v>
@@ -16471,7 +16477,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>46</v>
@@ -16495,16 +16501,16 @@
         <v>7</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>44</v>
@@ -16643,24 +16649,24 @@
         <v>18</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -16684,16 +16690,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>44</v>
@@ -16722,7 +16728,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -16743,13 +16749,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>44</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -7613,7 +7613,7 @@
         <v>-5</v>
       </c>
       <c r="G11" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>356</v>
@@ -8291,7 +8291,7 @@
         <v>-5</v>
       </c>
       <c r="G17" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>373</v>
@@ -9210,7 +9210,7 @@
         <v>-5</v>
       </c>
       <c r="G25" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>399</v>
@@ -11414,7 +11414,7 @@
         <v>-5</v>
       </c>
       <c r="G44" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>461</v>
@@ -13394,20 +13394,20 @@
       <c r="X61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y61" s="1" t="s">
-        <v>26</v>
+      <c r="Y61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC61" s="1" t="s">
-        <v>26</v>
+      <c r="AA61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD61" s="2" t="s">
         <v>25</v>
@@ -13415,17 +13415,17 @@
       <c r="AE61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG61" s="1" t="s">
-        <v>26</v>
+      <c r="AF61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI61" s="1" t="s">
-        <v>26</v>
+      <c r="AI61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ61" s="2" t="s">
         <v>25</v>
@@ -13433,14 +13433,14 @@
       <c r="AK61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL61" s="1" t="s">
-        <v>26</v>
+      <c r="AL61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN61" s="1" t="s">
-        <v>26</v>
+      <c r="AN61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO61" s="1" t="s">
         <v>26</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="639">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1113,7 +1113,7 @@
     <t>surface_mica</t>
   </si>
   <si>
-    <t>mica: 10 [1]</t>
+    <t>mica: 20 [1]</t>
   </si>
   <si>
     <t>deep_nickel</t>
@@ -1221,9 +1221,6 @@
     <t>surface_native_copper</t>
   </si>
   <si>
-    <t>copper: 10 [1]</t>
-  </si>
-  <si>
     <t>normal_galena</t>
   </si>
   <si>
@@ -1299,385 +1296,379 @@
     <t>bornite: 9 [1]</t>
   </si>
   <si>
+    <t>deep_copper_sulfide</t>
+  </si>
+  <si>
+    <t>sulfur: 8 [1]</t>
+  </si>
+  <si>
+    <t>bornite: 1</t>
+  </si>
+  <si>
+    <t>chalcocite: 1</t>
+  </si>
+  <si>
+    <t>high_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 1</t>
+  </si>
+  <si>
+    <t>normal_quartz_borax</t>
+  </si>
+  <si>
+    <t>quartzite: 6</t>
+  </si>
+  <si>
+    <t>sand_mineral_sand</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 5</t>
+  </si>
+  <si>
+    <t>deep_graphite_volcanic</t>
+  </si>
+  <si>
+    <t>surface_limonite</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 20 [1]</t>
+  </si>
+  <si>
+    <t>deep_asbestos</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 5 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 3</t>
+  </si>
+  <si>
+    <t>diatomite: 1</t>
+  </si>
+  <si>
+    <t>deep_copper_iron</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 6 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 3</t>
+  </si>
+  <si>
+    <t>copper: 2</t>
+  </si>
+  <si>
+    <t>normal_spodumene</t>
+  </si>
+  <si>
+    <t>spodumene: 15 [1]</t>
+  </si>
+  <si>
+    <t>rock_salt: 5</t>
+  </si>
+  <si>
+    <t>high_gypsum</t>
+  </si>
+  <si>
+    <t>gypsum: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 8</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 6</t>
+  </si>
+  <si>
+    <t>pyrochlore: 2</t>
+  </si>
+  <si>
+    <t>deep_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 12 [1]</t>
+  </si>
+  <si>
+    <t>diatomite: 5</t>
+  </si>
+  <si>
+    <t>electrotine: 4</t>
+  </si>
+  <si>
+    <t>alunite: 4</t>
+  </si>
+  <si>
+    <t>deep_molybdenum</t>
+  </si>
+  <si>
+    <t>wulfenite: 4</t>
+  </si>
+  <si>
+    <t>molybdenite: 8 [1]</t>
+  </si>
+  <si>
+    <t>molybdenum: 1</t>
+  </si>
+  <si>
+    <t>powellite: 1</t>
+  </si>
+  <si>
+    <t>deep_big_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 10</t>
+  </si>
+  <si>
+    <t>ruby: 6</t>
+  </si>
+  <si>
+    <t>cinnabar: 4</t>
+  </si>
+  <si>
+    <t>deep_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 4 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 2</t>
+  </si>
+  <si>
+    <t>cinnabar: 1</t>
+  </si>
+  <si>
+    <t>surface_cobaltite</t>
+  </si>
+  <si>
+    <t>deep_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 6</t>
+  </si>
+  <si>
+    <t>tungstate: 6</t>
+  </si>
+  <si>
+    <t>lithium: 2 [1]</t>
+  </si>
+  <si>
+    <t>normal_iron</t>
+  </si>
+  <si>
+    <t>hematite: 4</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 7 [1]</t>
+  </si>
+  <si>
+    <t>normal_gold</t>
+  </si>
+  <si>
+    <t>gold: 4</t>
+  </si>
+  <si>
+    <t>magnetite: 3</t>
+  </si>
+  <si>
+    <t>normal_asbestos</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 6</t>
+  </si>
+  <si>
+    <t>asbestos: 1</t>
+  </si>
+  <si>
+    <t>surface_hematite</t>
+  </si>
+  <si>
+    <t>surface_malachite</t>
+  </si>
+  <si>
+    <t>malachite: 1</t>
+  </si>
+  <si>
+    <t>deep_topaz</t>
+  </si>
+  <si>
+    <t>blue_topaz: 7 [1]</t>
+  </si>
+  <si>
+    <t>topaz: 5</t>
+  </si>
+  <si>
+    <t>chalcocite: 3</t>
+  </si>
+  <si>
+    <t>normal_mica</t>
+  </si>
+  <si>
+    <t>mica: 7</t>
+  </si>
+  <si>
+    <t>kyanite: 5</t>
+  </si>
+  <si>
+    <t>deep_bismuth</t>
+  </si>
+  <si>
+    <t>bismuth: 9</t>
+  </si>
+  <si>
+    <t>silver: 8</t>
+  </si>
+  <si>
+    <t>gold: 8</t>
+  </si>
+  <si>
+    <t>electrotine: 4 [1]</t>
+  </si>
+  <si>
+    <t>deep_magnetite_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 9 [1]</t>
+  </si>
+  <si>
+    <t>magnesite: 4</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 12</t>
+  </si>
+  <si>
+    <t>surface_coal</t>
+  </si>
+  <si>
+    <t>coal: 1</t>
+  </si>
+  <si>
+    <t>deep_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 9</t>
+  </si>
+  <si>
+    <t>pyrolusite: 8</t>
+  </si>
+  <si>
+    <t>tantalite: 4 [1]</t>
+  </si>
+  <si>
+    <t>normal_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite: 12</t>
+  </si>
+  <si>
+    <t>nickel: 4 [1]</t>
+  </si>
+  <si>
+    <t>cobaltite: 7</t>
+  </si>
+  <si>
+    <t>deep_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 12 [1]</t>
+  </si>
+  <si>
+    <t>spessartine: 10</t>
+  </si>
+  <si>
+    <t>tantalite: 6</t>
+  </si>
+  <si>
+    <t>surface_tricalcium_phosphate</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 1</t>
+  </si>
+  <si>
+    <t>normal_tarkianite</t>
+  </si>
+  <si>
+    <t>tarkianite: 35 [1]</t>
+  </si>
+  <si>
+    <t>deep_banded_iron</t>
+  </si>
+  <si>
+    <t>goethite: 6 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 3</t>
+  </si>
+  <si>
+    <t>normal_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 8 [1]</t>
+  </si>
+  <si>
+    <t>tin: 2</t>
+  </si>
+  <si>
+    <t>surface_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 20 [1]</t>
+  </si>
+  <si>
+    <t>surface_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 1</t>
+  </si>
+  <si>
+    <t>deep_kyanite</t>
+  </si>
+  <si>
+    <t>kyanite: 12 [1]</t>
+  </si>
+  <si>
+    <t>mica: 8</t>
+  </si>
+  <si>
+    <t>pollucite: 5</t>
+  </si>
+  <si>
+    <t>surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 1</t>
+  </si>
+  <si>
+    <t>deep_iron</t>
+  </si>
+  <si>
+    <t>goethite: 7 [1]</t>
+  </si>
+  <si>
+    <t>malachite: 5</t>
+  </si>
+  <si>
+    <t>deep_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 12 [1]</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 7</t>
+  </si>
+  <si>
+    <t>deep_sphalerite</t>
+  </si>
+  <si>
     <t>sphalerite: 7</t>
-  </si>
-  <si>
-    <t>deep_copper_sulfide</t>
-  </si>
-  <si>
-    <t>sulfur: 8 [1]</t>
-  </si>
-  <si>
-    <t>bornite: 1</t>
-  </si>
-  <si>
-    <t>chalcocite: 1</t>
-  </si>
-  <si>
-    <t>high_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 1</t>
-  </si>
-  <si>
-    <t>normal_quartz_borax</t>
-  </si>
-  <si>
-    <t>quartzite: 6</t>
-  </si>
-  <si>
-    <t>sand_mineral_sand</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 5</t>
-  </si>
-  <si>
-    <t>deep_graphite_volcanic</t>
-  </si>
-  <si>
-    <t>surface_limonite</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_asbestos</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 5 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 3</t>
-  </si>
-  <si>
-    <t>diatomite: 1</t>
-  </si>
-  <si>
-    <t>deep_copper_iron</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 6 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 3</t>
-  </si>
-  <si>
-    <t>copper: 2</t>
-  </si>
-  <si>
-    <t>normal_spodumene</t>
-  </si>
-  <si>
-    <t>spodumene: 15 [1]</t>
-  </si>
-  <si>
-    <t>rock_salt: 5</t>
-  </si>
-  <si>
-    <t>high_gypsum</t>
-  </si>
-  <si>
-    <t>gypsum: 10 [1]</t>
-  </si>
-  <si>
-    <t>deep_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 8</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 6</t>
-  </si>
-  <si>
-    <t>pyrochlore: 2</t>
-  </si>
-  <si>
-    <t>deep_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 10 [1]</t>
-  </si>
-  <si>
-    <t>deep_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 12 [1]</t>
-  </si>
-  <si>
-    <t>diatomite: 5</t>
-  </si>
-  <si>
-    <t>electrotine: 4</t>
-  </si>
-  <si>
-    <t>alunite: 4</t>
-  </si>
-  <si>
-    <t>deep_molybdenum</t>
-  </si>
-  <si>
-    <t>wulfenite: 4</t>
-  </si>
-  <si>
-    <t>molybdenite: 8 [1]</t>
-  </si>
-  <si>
-    <t>molybdenum: 1</t>
-  </si>
-  <si>
-    <t>powellite: 1</t>
-  </si>
-  <si>
-    <t>deep_big_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 10</t>
-  </si>
-  <si>
-    <t>ruby: 6</t>
-  </si>
-  <si>
-    <t>cinnabar: 4</t>
-  </si>
-  <si>
-    <t>deep_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 4 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 2</t>
-  </si>
-  <si>
-    <t>cinnabar: 1</t>
-  </si>
-  <si>
-    <t>surface_cobaltite</t>
-  </si>
-  <si>
-    <t>cobaltite: 10 [1]</t>
-  </si>
-  <si>
-    <t>deep_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 6</t>
-  </si>
-  <si>
-    <t>tungstate: 6</t>
-  </si>
-  <si>
-    <t>lithium: 2 [1]</t>
-  </si>
-  <si>
-    <t>normal_iron</t>
-  </si>
-  <si>
-    <t>hematite: 4</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 7 [1]</t>
-  </si>
-  <si>
-    <t>normal_gold</t>
-  </si>
-  <si>
-    <t>gold: 4</t>
-  </si>
-  <si>
-    <t>magnetite: 3</t>
-  </si>
-  <si>
-    <t>normal_asbestos</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 6</t>
-  </si>
-  <si>
-    <t>asbestos: 1</t>
-  </si>
-  <si>
-    <t>surface_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 10 [1]</t>
-  </si>
-  <si>
-    <t>surface_malachite</t>
-  </si>
-  <si>
-    <t>malachite: 1</t>
-  </si>
-  <si>
-    <t>deep_topaz</t>
-  </si>
-  <si>
-    <t>blue_topaz: 7 [1]</t>
-  </si>
-  <si>
-    <t>topaz: 5</t>
-  </si>
-  <si>
-    <t>chalcocite: 3</t>
-  </si>
-  <si>
-    <t>normal_mica</t>
-  </si>
-  <si>
-    <t>mica: 7</t>
-  </si>
-  <si>
-    <t>kyanite: 5</t>
-  </si>
-  <si>
-    <t>deep_bismuth</t>
-  </si>
-  <si>
-    <t>bismuth: 9</t>
-  </si>
-  <si>
-    <t>silver: 8</t>
-  </si>
-  <si>
-    <t>gold: 8</t>
-  </si>
-  <si>
-    <t>electrotine: 4 [1]</t>
-  </si>
-  <si>
-    <t>deep_magnetite_olivine</t>
-  </si>
-  <si>
-    <t>bentonite: 9 [1]</t>
-  </si>
-  <si>
-    <t>magnesite: 4</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 12</t>
-  </si>
-  <si>
-    <t>surface_coal</t>
-  </si>
-  <si>
-    <t>coal: 1</t>
-  </si>
-  <si>
-    <t>deep_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 9</t>
-  </si>
-  <si>
-    <t>pyrolusite: 8</t>
-  </si>
-  <si>
-    <t>tantalite: 4 [1]</t>
-  </si>
-  <si>
-    <t>normal_garnierite</t>
-  </si>
-  <si>
-    <t>garnierite: 12</t>
-  </si>
-  <si>
-    <t>nickel: 4 [1]</t>
-  </si>
-  <si>
-    <t>cobaltite: 7</t>
-  </si>
-  <si>
-    <t>deep_tantalite</t>
-  </si>
-  <si>
-    <t>grossular: 12 [1]</t>
-  </si>
-  <si>
-    <t>spessartine: 10</t>
-  </si>
-  <si>
-    <t>tantalite: 6</t>
-  </si>
-  <si>
-    <t>surface_tricalcium_phosphate</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 1</t>
-  </si>
-  <si>
-    <t>normal_tarkianite</t>
-  </si>
-  <si>
-    <t>tarkianite: 35 [1]</t>
-  </si>
-  <si>
-    <t>deep_banded_iron</t>
-  </si>
-  <si>
-    <t>goethite: 6 [1]</t>
-  </si>
-  <si>
-    <t>hematite: 3</t>
-  </si>
-  <si>
-    <t>normal_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 8 [1]</t>
-  </si>
-  <si>
-    <t>tin: 2</t>
-  </si>
-  <si>
-    <t>surface_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 20 [1]</t>
-  </si>
-  <si>
-    <t>surface_nickel</t>
-  </si>
-  <si>
-    <t>garnierite: 1</t>
-  </si>
-  <si>
-    <t>deep_kyanite</t>
-  </si>
-  <si>
-    <t>kyanite: 12 [1]</t>
-  </si>
-  <si>
-    <t>mica: 8</t>
-  </si>
-  <si>
-    <t>pollucite: 5</t>
-  </si>
-  <si>
-    <t>surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 1</t>
-  </si>
-  <si>
-    <t>deep_iron</t>
-  </si>
-  <si>
-    <t>goethite: 7 [1]</t>
-  </si>
-  <si>
-    <t>malachite: 5</t>
-  </si>
-  <si>
-    <t>deep_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 12 [1]</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 7</t>
-  </si>
-  <si>
-    <t>deep_sphalerite</t>
   </si>
   <si>
     <t>surface_bismuth</t>
@@ -6870,7 +6861,7 @@
         <v>82</v>
       </c>
       <c r="C4" s="3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D4" s="3">
         <v>0.28</v>
@@ -7004,7 +6995,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>339</v>
@@ -7117,7 +7108,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>342</v>
@@ -7233,7 +7224,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>346</v>
@@ -7346,7 +7337,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>349</v>
@@ -7462,7 +7453,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>353</v>
@@ -7679,7 +7670,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="D11" s="3">
         <v>0.28</v>
@@ -7691,7 +7682,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
@@ -8027,7 +8018,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>367</v>
@@ -8134,7 +8125,7 @@
         <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3">
         <v>0.25</v>
@@ -8250,7 +8241,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D16" s="3">
         <v>0.25</v>
@@ -8360,7 +8351,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D17" s="3">
         <v>0.25</v>
@@ -8583,7 +8574,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D19" s="3">
         <v>0.3</v>
@@ -8925,7 +8916,7 @@
         <v>34</v>
       </c>
       <c r="C22" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D22" s="3">
         <v>0.33</v>
@@ -8937,7 +8928,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H22" s="3">
         <v>10</v>
@@ -9273,7 +9264,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="3">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3">
         <v>0.2</v>
@@ -9288,7 +9279,7 @@
         <v>15</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>401</v>
+        <v>121</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>26</v>
@@ -9377,13 +9368,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="3">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3">
         <v>0.18</v>
@@ -9395,16 +9386,16 @@
         <v>70</v>
       </c>
       <c r="G26" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3">
         <v>10</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>404</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>26</v>
@@ -9493,7 +9484,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -9511,19 +9502,19 @@
         <v>20</v>
       </c>
       <c r="G27" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>25</v>
@@ -9612,13 +9603,13 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D28" s="3">
         <v>0.15</v>
@@ -9633,10 +9624,10 @@
         <v>15</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>25</v>
@@ -9725,13 +9716,13 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3">
         <v>0.26</v>
@@ -9743,19 +9734,19 @@
         <v>70</v>
       </c>
       <c r="G29" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H29" s="3">
         <v>10</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K29" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>26</v>
@@ -9844,7 +9835,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>20</v>
@@ -9862,16 +9853,16 @@
         <v>20</v>
       </c>
       <c r="G30" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>25</v>
@@ -9960,13 +9951,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D31" s="3">
         <v>0.23</v>
@@ -9978,16 +9969,16 @@
         <v>70</v>
       </c>
       <c r="G31" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3">
         <v>10</v>
       </c>
       <c r="J31" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>422</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>25</v>
@@ -10076,13 +10067,13 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3">
         <v>0.29</v>
@@ -10094,22 +10085,19 @@
         <v>70</v>
       </c>
       <c r="G32" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H32" s="3">
         <v>10</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>26</v>
@@ -10198,7 +10186,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>34</v>
@@ -10216,19 +10204,19 @@
         <v>-45</v>
       </c>
       <c r="G33" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H33" s="3">
         <v>6</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>25</v>
@@ -10317,7 +10305,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>20</v>
@@ -10338,7 +10326,7 @@
         <v>15</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>26</v>
@@ -10427,13 +10415,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D35" s="3">
         <v>0.28</v>
@@ -10451,10 +10439,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>26</v>
@@ -10543,7 +10531,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>20</v>
@@ -10564,16 +10552,16 @@
         <v>34</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="M36" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>25</v>
@@ -10662,7 +10650,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>82</v>
@@ -10778,7 +10766,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>20</v>
@@ -10799,7 +10787,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>25</v>
@@ -10888,7 +10876,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>34</v>
@@ -10906,19 +10894,19 @@
         <v>20</v>
       </c>
       <c r="G39" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H39" s="3">
         <v>5</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>25</v>
@@ -11007,7 +10995,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>20</v>
@@ -11025,19 +11013,19 @@
         <v>20</v>
       </c>
       <c r="G40" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>26</v>
@@ -11126,13 +11114,13 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C41" s="3">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D41" s="3">
         <v>0.23</v>
@@ -11144,16 +11132,16 @@
         <v>70</v>
       </c>
       <c r="G41" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H41" s="3">
         <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>25</v>
@@ -11242,7 +11230,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
@@ -11263,7 +11251,7 @@
         <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>26</v>
@@ -11352,7 +11340,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>20</v>
@@ -11370,16 +11358,16 @@
         <v>20</v>
       </c>
       <c r="G43" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J43" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>25</v>
@@ -11468,7 +11456,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>34</v>
@@ -11486,13 +11474,13 @@
         <v>-45</v>
       </c>
       <c r="G44" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H44" s="3">
         <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>25</v>
@@ -11581,7 +11569,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
@@ -11599,19 +11587,19 @@
         <v>20</v>
       </c>
       <c r="G45" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>25</v>
@@ -11700,7 +11688,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>20</v>
@@ -11718,19 +11706,19 @@
         <v>20</v>
       </c>
       <c r="G46" s="3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>25</v>
@@ -11819,7 +11807,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>34</v>
@@ -11837,19 +11825,19 @@
         <v>20</v>
       </c>
       <c r="G47" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H47" s="3">
         <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>25</v>
@@ -11938,7 +11926,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>20</v>
@@ -11956,16 +11944,16 @@
         <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J48" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>477</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>25</v>
@@ -12054,7 +12042,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
@@ -12075,7 +12063,7 @@
         <v>15</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>479</v>
+        <v>100</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>26</v>
@@ -12164,7 +12152,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>20</v>
@@ -12182,16 +12170,16 @@
         <v>20</v>
       </c>
       <c r="G50" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>25</v>
@@ -12280,13 +12268,13 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C51" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D51" s="3">
         <v>0.28</v>
@@ -12298,16 +12286,16 @@
         <v>70</v>
       </c>
       <c r="G51" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H51" s="3">
         <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>26</v>
@@ -12396,13 +12384,13 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C52" s="3">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D52" s="3">
         <v>0.33</v>
@@ -12414,16 +12402,16 @@
         <v>70</v>
       </c>
       <c r="G52" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H52" s="3">
         <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>26</v>
@@ -12512,13 +12500,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C53" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D53" s="3">
         <v>0.28</v>
@@ -12530,16 +12518,16 @@
         <v>70</v>
       </c>
       <c r="G53" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H53" s="3">
         <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>25</v>
@@ -12628,7 +12616,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>20</v>
@@ -12649,7 +12637,7 @@
         <v>15</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>494</v>
+        <v>23</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>26</v>
@@ -12738,13 +12726,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C55" s="3">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D55" s="3">
         <v>0.2</v>
@@ -12759,7 +12747,7 @@
         <v>15</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>25</v>
@@ -12848,7 +12836,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>20</v>
@@ -12866,19 +12854,19 @@
         <v>20</v>
       </c>
       <c r="G56" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>25</v>
@@ -12967,13 +12955,13 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C57" s="3">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D57" s="3">
         <v>0.28</v>
@@ -12985,16 +12973,16 @@
         <v>70</v>
       </c>
       <c r="G57" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H57" s="3">
         <v>10</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>26</v>
@@ -13083,7 +13071,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>82</v>
@@ -13107,16 +13095,16 @@
         <v>10</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>25</v>
@@ -13205,7 +13193,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>20</v>
@@ -13223,19 +13211,19 @@
         <v>20</v>
       </c>
       <c r="G59" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>288</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>26</v>
@@ -13324,7 +13312,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
@@ -13345,7 +13333,7 @@
         <v>15</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>26</v>
@@ -13434,7 +13422,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>20</v>
@@ -13452,16 +13440,16 @@
         <v>20</v>
       </c>
       <c r="G61" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>25</v>
@@ -13550,13 +13538,13 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C62" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D62" s="3">
         <v>0.28</v>
@@ -13568,19 +13556,19 @@
         <v>70</v>
       </c>
       <c r="G62" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H62" s="3">
         <v>10</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>25</v>
@@ -13669,7 +13657,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>20</v>
@@ -13687,19 +13675,19 @@
         <v>20</v>
       </c>
       <c r="G63" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>25</v>
@@ -13788,7 +13776,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
@@ -13809,7 +13797,7 @@
         <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>25</v>
@@ -13898,13 +13886,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C65" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D65" s="3">
         <v>0.28</v>
@@ -13922,7 +13910,7 @@
         <v>10</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>295</v>
@@ -14017,7 +14005,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>20</v>
@@ -14035,16 +14023,16 @@
         <v>20</v>
       </c>
       <c r="G66" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>25</v>
@@ -14133,13 +14121,13 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C67" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D67" s="3">
         <v>0.33</v>
@@ -14151,16 +14139,16 @@
         <v>70</v>
       </c>
       <c r="G67" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H67" s="3">
         <v>10</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>25</v>
@@ -14249,7 +14237,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>20</v>
@@ -14270,7 +14258,7 @@
         <v>15</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>25</v>
@@ -14359,7 +14347,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>20</v>
@@ -14380,7 +14368,7 @@
         <v>15</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>25</v>
@@ -14469,7 +14457,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>20</v>
@@ -14487,16 +14475,16 @@
         <v>20</v>
       </c>
       <c r="G70" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>25</v>
@@ -14585,13 +14573,13 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="3">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D71" s="3">
         <v>0.2</v>
@@ -14606,7 +14594,7 @@
         <v>15</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>25</v>
@@ -14695,7 +14683,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>20</v>
@@ -14713,10 +14701,10 @@
         <v>20</v>
       </c>
       <c r="G72" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>22</v>
@@ -14725,7 +14713,7 @@
         <v>45</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>25</v>
@@ -14814,7 +14802,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>20</v>
@@ -14832,13 +14820,13 @@
         <v>20</v>
       </c>
       <c r="G73" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>96</v>
@@ -14930,7 +14918,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>20</v>
@@ -14948,16 +14936,16 @@
         <v>20</v>
       </c>
       <c r="G74" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>427</v>
+        <v>550</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>25</v>
@@ -15046,13 +15034,13 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D75" s="3">
         <v>0.25</v>
@@ -15290,13 +15278,13 @@
         <v>314</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>318</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>185</v>
@@ -15310,7 +15298,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -15331,13 +15319,13 @@
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -15396,7 +15384,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -15417,13 +15405,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>45</v>
@@ -15485,7 +15473,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -15506,10 +15494,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -15568,7 +15556,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -15589,10 +15577,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>167</v>
@@ -15654,7 +15642,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
@@ -15749,7 +15737,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -15770,7 +15758,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>76</v>
@@ -15779,10 +15767,10 @@
         <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -15841,7 +15829,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>82</v>
@@ -15865,13 +15853,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>26</v>
@@ -15930,7 +15918,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -16019,7 +16007,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -16040,16 +16028,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -16108,7 +16096,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -16132,16 +16120,16 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
@@ -16200,7 +16188,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -16221,19 +16209,19 @@
         <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>45</v>
@@ -16295,7 +16283,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -16316,7 +16304,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>299</v>
@@ -16384,7 +16372,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -16405,10 +16393,10 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>122</v>
@@ -16473,7 +16461,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -16562,7 +16550,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>82</v>
@@ -16589,13 +16577,13 @@
         <v>104</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>25</v>
@@ -16654,7 +16642,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -16675,16 +16663,16 @@
         <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -16743,7 +16731,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -16764,13 +16752,13 @@
         <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>131</v>
@@ -16832,7 +16820,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -16853,13 +16841,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>45</v>
@@ -16921,7 +16909,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -16945,7 +16933,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>256</v>
@@ -17010,7 +16998,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -17031,16 +17019,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>25</v>
@@ -17099,7 +17087,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -17120,16 +17108,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -17188,7 +17176,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -17212,7 +17200,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>54</v>
@@ -17274,7 +17262,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
@@ -17301,7 +17289,7 @@
         <v>207</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>209</v>
@@ -17363,7 +17351,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -17390,7 +17378,7 @@
         <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -17449,7 +17437,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -17470,16 +17458,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -17538,7 +17526,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -17559,13 +17547,13 @@
         <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>45</v>
@@ -17627,7 +17615,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
@@ -17648,13 +17636,13 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>96</v>
@@ -17716,7 +17704,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
   <si>
     <t>Vein ID</t>
   </si>
@@ -138,13 +138,13 @@
     <t>tfc:cluster_vein</t>
   </si>
   <si>
-    <t>apatite: 80 [1]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 60</t>
-  </si>
-  <si>
-    <t>pyrochlore: 20</t>
+    <t>apatite: 16 [1]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 12</t>
+  </si>
+  <si>
+    <t>pyrochlore: 4</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -159,1780 +159,1798 @@
     <t>tfc:disc_vein</t>
   </si>
   <si>
-    <t>cassiterite: 50 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 30</t>
+    <t>cassiterite: 10 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 6</t>
+  </si>
+  <si>
+    <t>diatomite: 2</t>
+  </si>
+  <si>
+    <t>deep_banded_iron</t>
+  </si>
+  <si>
+    <t>goethite: 12 [1]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 10</t>
+  </si>
+  <si>
+    <t>hematite: 6</t>
+  </si>
+  <si>
+    <t>deep_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 6</t>
+  </si>
+  <si>
+    <t>ilmenite: 14 [1]</t>
+  </si>
+  <si>
+    <t>deep_big_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 20 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 12</t>
+  </si>
+  <si>
+    <t>cinnabar: 8</t>
+  </si>
+  <si>
+    <t>deep_bismuth</t>
+  </si>
+  <si>
+    <t>tfc:pipe_vein</t>
+  </si>
+  <si>
+    <t>bismuth: 18</t>
+  </si>
+  <si>
+    <t>silver: 16</t>
+  </si>
+  <si>
+    <t>gold: 16</t>
+  </si>
+  <si>
+    <t>electrotine: 8 [1]</t>
+  </si>
+  <si>
+    <t>deep_copper_iron</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 12 [1]</t>
+  </si>
+  <si>
+    <t>goethite: 10</t>
+  </si>
+  <si>
+    <t>pyrite: 6</t>
+  </si>
+  <si>
+    <t>copper: 4</t>
+  </si>
+  <si>
+    <t>deep_copper_sulfide</t>
+  </si>
+  <si>
+    <t>sulfur: 16 [1]</t>
+  </si>
+  <si>
+    <t>bornite: 2</t>
+  </si>
+  <si>
+    <t>chalcocite: 2</t>
+  </si>
+  <si>
+    <t>deep_copper_tin</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 7</t>
+  </si>
+  <si>
+    <t>zeolite: 3</t>
+  </si>
+  <si>
+    <t>cassiterite: 3</t>
+  </si>
+  <si>
+    <t>deep_galena</t>
+  </si>
+  <si>
+    <t>galena: 12 [1]</t>
+  </si>
+  <si>
+    <t>silver: 6</t>
+  </si>
+  <si>
+    <t>lead: 5</t>
+  </si>
+  <si>
+    <t>deep_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 14 [1]</t>
+  </si>
+  <si>
+    <t>coal: 4</t>
+  </si>
+  <si>
+    <t>diamond: 2</t>
+  </si>
+  <si>
+    <t>deep_graphite_volcanic</t>
+  </si>
+  <si>
+    <t>graphite: 12 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 4</t>
+  </si>
+  <si>
+    <t>deep_iron</t>
+  </si>
+  <si>
+    <t>goethite: 14 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 10</t>
+  </si>
+  <si>
+    <t>malachite: 10</t>
+  </si>
+  <si>
+    <t>deep_kyanite</t>
+  </si>
+  <si>
+    <t>kyanite: 24 [1]</t>
+  </si>
+  <si>
+    <t>mica: 16</t>
+  </si>
+  <si>
+    <t>pollucite: 10</t>
+  </si>
+  <si>
+    <t>deep_lazurite_calcite</t>
+  </si>
+  <si>
+    <t>lazurite: 10 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 8</t>
+  </si>
+  <si>
+    <t>lapis: 6</t>
+  </si>
+  <si>
+    <t>calcite: 6</t>
+  </si>
+  <si>
+    <t>deep_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 24 [1]</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 14</t>
+  </si>
+  <si>
+    <t>gold: 10</t>
+  </si>
+  <si>
+    <t>deep_magnetite_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 18 [1]</t>
+  </si>
+  <si>
+    <t>magnesite: 8</t>
+  </si>
+  <si>
+    <t>olivine: 4</t>
+  </si>
+  <si>
+    <t>fullers_earth: 24</t>
+  </si>
+  <si>
+    <t>deep_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 18</t>
+  </si>
+  <si>
+    <t>pyrolusite: 16</t>
+  </si>
+  <si>
+    <t>tantalite: 8 [1]</t>
+  </si>
+  <si>
+    <t>deep_molybdenum</t>
+  </si>
+  <si>
+    <t>wulfenite: 8</t>
+  </si>
+  <si>
+    <t>molybdenite: 16 [1]</t>
+  </si>
+  <si>
+    <t>molybdenum: 2</t>
+  </si>
+  <si>
+    <t>powellite: 2</t>
+  </si>
+  <si>
+    <t>deep_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 12 [1]</t>
+  </si>
+  <si>
+    <t>monazite: 6</t>
+  </si>
+  <si>
+    <t>neodymium: 2</t>
+  </si>
+  <si>
+    <t>deep_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 14 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 8</t>
+  </si>
+  <si>
+    <t>cobaltite: 10</t>
+  </si>
+  <si>
+    <t>pentlandite: 6</t>
+  </si>
+  <si>
+    <t>deep_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 8 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 4</t>
+  </si>
+  <si>
+    <t>cinnabar: 2</t>
+  </si>
+  <si>
+    <t>deep_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 24 [1]</t>
   </si>
   <si>
     <t>diatomite: 10</t>
   </si>
   <si>
-    <t>deep_banded_iron</t>
-  </si>
-  <si>
-    <t>goethite: 60 [1]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 50</t>
+    <t>electrotine: 8</t>
+  </si>
+  <si>
+    <t>alunite: 8</t>
+  </si>
+  <si>
+    <t>deep_sapphire</t>
+  </si>
+  <si>
+    <t>almandine: 8 [1]</t>
+  </si>
+  <si>
+    <t>pyrope: 12</t>
+  </si>
+  <si>
+    <t>sapphire: 16</t>
+  </si>
+  <si>
+    <t>green_sapphire: 13</t>
+  </si>
+  <si>
+    <t>deep_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 12</t>
+  </si>
+  <si>
+    <t>tungstate: 12</t>
+  </si>
+  <si>
+    <t>lithium: 4 [1]</t>
+  </si>
+  <si>
+    <t>deep_sphalerite</t>
+  </si>
+  <si>
+    <t>sulfur: 1</t>
+  </si>
+  <si>
+    <t>pyrite: 3</t>
+  </si>
+  <si>
+    <t>sphalerite: 7</t>
+  </si>
+  <si>
+    <t>deep_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 20 [1]</t>
+  </si>
+  <si>
+    <t>deep_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 24 [1]</t>
+  </si>
+  <si>
+    <t>spessartine: 20</t>
+  </si>
+  <si>
+    <t>tantalite: 12</t>
+  </si>
+  <si>
+    <t>deep_thorianite</t>
+  </si>
+  <si>
+    <t>thorium: 8</t>
+  </si>
+  <si>
+    <t>uraninite: 4</t>
+  </si>
+  <si>
+    <t>emerald: 2</t>
+  </si>
+  <si>
+    <t>beryllium: 4 [1]</t>
+  </si>
+  <si>
+    <t>deep_tin</t>
+  </si>
+  <si>
+    <t>cassiterite: 14 [1]</t>
+  </si>
+  <si>
+    <t>tin: 2</t>
+  </si>
+  <si>
+    <t>deep_topaz</t>
+  </si>
+  <si>
+    <t>blue_topaz: 14 [1]</t>
+  </si>
+  <si>
+    <t>topaz: 10</t>
+  </si>
+  <si>
+    <t>chalcocite: 6</t>
+  </si>
+  <si>
+    <t>high_bismuth_mountain</t>
+  </si>
+  <si>
+    <t>bismuth: 1</t>
+  </si>
+  <si>
+    <t>high_coal</t>
+  </si>
+  <si>
+    <t>coal: 50 [1]</t>
+  </si>
+  <si>
+    <t>high_gypsum</t>
+  </si>
+  <si>
+    <t>gypsum: 100 [1]</t>
+  </si>
+  <si>
+    <t>high_lead</t>
+  </si>
+  <si>
+    <t>lead: 6</t>
+  </si>
+  <si>
+    <t>silver: 4</t>
+  </si>
+  <si>
+    <t>high_realgar</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 20</t>
+  </si>
+  <si>
+    <t>realgar: 10</t>
+  </si>
+  <si>
+    <t>high_sulfur</t>
+  </si>
+  <si>
+    <t>high_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 50 [1]</t>
+  </si>
+  <si>
+    <t>copper: 30</t>
+  </si>
+  <si>
+    <t>stibnite: 20</t>
+  </si>
+  <si>
+    <t>high_tin</t>
+  </si>
+  <si>
+    <t>tin: 4</t>
+  </si>
+  <si>
+    <t>cassiterite: 6</t>
+  </si>
+  <si>
+    <t>normal_asbestos_dry</t>
+  </si>
+  <si>
+    <t>asbestos: 1</t>
+  </si>
+  <si>
+    <t>normal_coal</t>
+  </si>
+  <si>
+    <t>coal: 100 [1]</t>
+  </si>
+  <si>
+    <t>normal_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 35 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 20</t>
+  </si>
+  <si>
+    <t>copper: 10</t>
+  </si>
+  <si>
+    <t>normal_copper_gypsum</t>
+  </si>
+  <si>
+    <t>chalcocite: 48 [1]</t>
+  </si>
+  <si>
+    <t>gypsum: 12</t>
+  </si>
+  <si>
+    <t>cobalt: 20</t>
+  </si>
+  <si>
+    <t>sulfur: 8</t>
+  </si>
+  <si>
+    <t>normal_galena</t>
+  </si>
+  <si>
+    <t>galena: 70 [1]</t>
+  </si>
+  <si>
+    <t>silver: 20</t>
+  </si>
+  <si>
+    <t>normal_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite: 60 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 20</t>
+  </si>
+  <si>
+    <t>cobaltite: 35</t>
+  </si>
+  <si>
+    <t>normal_gold</t>
+  </si>
+  <si>
+    <t>gold: 4</t>
+  </si>
+  <si>
+    <t>magnetite: 3</t>
+  </si>
+  <si>
+    <t>normal_iron</t>
+  </si>
+  <si>
+    <t>hematite: 40</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 70 [1]</t>
+  </si>
+  <si>
+    <t>normal_mica</t>
+  </si>
+  <si>
+    <t>mica: 7</t>
+  </si>
+  <si>
+    <t>kyanite: 5</t>
+  </si>
+  <si>
+    <t>normal_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 90 [1]</t>
+  </si>
+  <si>
+    <t>barite: 30</t>
+  </si>
+  <si>
+    <t>normal_quartz_borax</t>
+  </si>
+  <si>
+    <t>quartzite: 6</t>
+  </si>
+  <si>
+    <t>borax: 1</t>
+  </si>
+  <si>
+    <t>normal_salt</t>
+  </si>
+  <si>
+    <t>salt: 60 [1]</t>
+  </si>
+  <si>
+    <t>rock_salt: 30</t>
+  </si>
+  <si>
+    <t>borax: 10</t>
+  </si>
+  <si>
+    <t>normal_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite: 10</t>
+  </si>
+  <si>
+    <t>galena: 3</t>
+  </si>
+  <si>
+    <t>normal_spodumene</t>
+  </si>
+  <si>
+    <t>spodumene: 75 [1]</t>
+  </si>
+  <si>
+    <t>rock_salt: 25</t>
+  </si>
+  <si>
+    <t>normal_sulfide</t>
+  </si>
+  <si>
+    <t>sulfur: 20</t>
+  </si>
+  <si>
+    <t>stibnite: 15</t>
+  </si>
+  <si>
+    <t>bornite: 45 [1]</t>
+  </si>
+  <si>
+    <t>normal_tarkianite</t>
+  </si>
+  <si>
+    <t>tarkianite: 35 [1]</t>
+  </si>
+  <si>
+    <t>borax: 20</t>
+  </si>
+  <si>
+    <t>trona: 10</t>
+  </si>
+  <si>
+    <t>sand_basaltic</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 8</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 5</t>
+  </si>
+  <si>
+    <t>garnet_sand: 1</t>
+  </si>
+  <si>
+    <t>sand_granitic</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 8</t>
+  </si>
+  <si>
+    <t>fullers_earth: 4</t>
+  </si>
+  <si>
+    <t>sand_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 1</t>
+  </si>
+  <si>
+    <t>surface_bismuth</t>
+  </si>
+  <si>
+    <t>surface_coal</t>
+  </si>
+  <si>
+    <t>lignite: 100</t>
+  </si>
+  <si>
+    <t>surface_cobaltite</t>
+  </si>
+  <si>
+    <t>cobaltite: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_gold</t>
+  </si>
+  <si>
+    <t>gold: 1</t>
+  </si>
+  <si>
+    <t>surface_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_limonite</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_malachite</t>
+  </si>
+  <si>
+    <t>malachite: 1</t>
+  </si>
+  <si>
+    <t>surface_mica</t>
+  </si>
+  <si>
+    <t>mica: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_native_copper</t>
+  </si>
+  <si>
+    <t>copper: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 1</t>
+  </si>
+  <si>
+    <t>surface_salpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 100 [1]</t>
+  </si>
+  <si>
+    <t>surface_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite: 1</t>
+  </si>
+  <si>
+    <t>surface_sylvite_salt</t>
+  </si>
+  <si>
+    <t>salt: 6</t>
+  </si>
+  <si>
+    <t>rock_salt: 4</t>
+  </si>
+  <si>
+    <t>surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 1</t>
+  </si>
+  <si>
+    <t>surface_tricalcium_phosphate</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 1</t>
+  </si>
+  <si>
+    <t>mars_stone</t>
+  </si>
+  <si>
+    <t>red_granite</t>
+  </si>
+  <si>
+    <t>venus_stone</t>
+  </si>
+  <si>
+    <t>deep_mars_chromite</t>
+  </si>
+  <si>
+    <t>redstone: 45 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 35</t>
+  </si>
+  <si>
+    <t>chromite: 20</t>
+  </si>
+  <si>
+    <t>deep_mars_pitchblende</t>
+  </si>
+  <si>
+    <t>pitchblende: 50 [1]</t>
+  </si>
+  <si>
+    <t>thorium: 25</t>
+  </si>
+  <si>
+    <t>uraninite: 20</t>
+  </si>
+  <si>
+    <t>deep_mars_sheldonite</t>
+  </si>
+  <si>
+    <t>bornite: 35 [1]</t>
+  </si>
+  <si>
+    <t>cooperite: 25</t>
+  </si>
+  <si>
+    <t>nickel: 25</t>
+  </si>
+  <si>
+    <t>platinum: 15</t>
+  </si>
+  <si>
+    <t>mars_almandine</t>
+  </si>
+  <si>
+    <t>almandine: 35 [1]</t>
+  </si>
+  <si>
+    <t>pyrope: 25</t>
+  </si>
+  <si>
+    <t>sapphire: 15</t>
+  </si>
+  <si>
+    <t>green_sapphire: 15</t>
+  </si>
+  <si>
+    <t>hematite: 5</t>
+  </si>
+  <si>
+    <t>mars_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 50 [1]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 35</t>
+  </si>
+  <si>
+    <t>pyrochlore: 15</t>
+  </si>
+  <si>
+    <t>mars_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium: 35</t>
+  </si>
+  <si>
+    <t>emerald: 50</t>
+  </si>
+  <si>
+    <t>realgar: 15</t>
+  </si>
+  <si>
+    <t>mars_coal</t>
+  </si>
+  <si>
+    <t>coal: 70 [1]</t>
   </si>
   <si>
     <t>hematite: 30</t>
   </si>
   <si>
-    <t>deep_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 30</t>
-  </si>
-  <si>
-    <t>ilmenite: 70 [1]</t>
-  </si>
-  <si>
-    <t>deep_big_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 50 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 30</t>
+    <t>mars_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 65 [1]</t>
+  </si>
+  <si>
+    <t>copper: 20</t>
+  </si>
+  <si>
+    <t>pyrite: 10</t>
+  </si>
+  <si>
+    <t>mars_galena</t>
+  </si>
+  <si>
+    <t>galena: 30 [1]</t>
+  </si>
+  <si>
+    <t>silver: 15</t>
+  </si>
+  <si>
+    <t>lead: 25</t>
+  </si>
+  <si>
+    <t>mars_gold</t>
+  </si>
+  <si>
+    <t>green_sapphire: 5</t>
+  </si>
+  <si>
+    <t>bauxite: 20</t>
+  </si>
+  <si>
+    <t>electrotine: 20</t>
+  </si>
+  <si>
+    <t>gold: 55 [1]</t>
+  </si>
+  <si>
+    <t>mars_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 45 [1]</t>
+  </si>
+  <si>
+    <t>coal: 25</t>
+  </si>
+  <si>
+    <t>diamond: 20</t>
+  </si>
+  <si>
+    <t>mars_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 50 [1]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 30</t>
+  </si>
+  <si>
+    <t>goethite: 15</t>
+  </si>
+  <si>
+    <t>gold: 5</t>
+  </si>
+  <si>
+    <t>mars_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35</t>
+  </si>
+  <si>
+    <t>sodalite: 25</t>
+  </si>
+  <si>
+    <t>lapis: 25</t>
+  </si>
+  <si>
+    <t>calcite: 15</t>
+  </si>
+  <si>
+    <t>mars_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 15</t>
+  </si>
+  <si>
+    <t>talc: 15</t>
+  </si>
+  <si>
+    <t>trona: 25</t>
+  </si>
+  <si>
+    <t>pentlandite: 5</t>
+  </si>
+  <si>
+    <t>mars_neodynium</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [1]</t>
+  </si>
+  <si>
+    <t>monazite: 25</t>
+  </si>
+  <si>
+    <t>neodymium: 5</t>
+  </si>
+  <si>
+    <t>mars_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 25 [1]</t>
+  </si>
+  <si>
+    <t>cobaltite: 20</t>
+  </si>
+  <si>
+    <t>mars_pitchblende</t>
+  </si>
+  <si>
+    <t>pitchblende: 35 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 25</t>
+  </si>
+  <si>
+    <t>mars_quartzite</t>
+  </si>
+  <si>
+    <t>quartzite: 35 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 15</t>
+  </si>
+  <si>
+    <t>mars_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 20 [1]</t>
+  </si>
+  <si>
+    <t>salt: 30</t>
+  </si>
+  <si>
+    <t>lepidolite: 15</t>
+  </si>
+  <si>
+    <t>spodumene: 35</t>
+  </si>
+  <si>
+    <t>mars_stibnite</t>
+  </si>
+  <si>
+    <t>mars_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 15</t>
+  </si>
+  <si>
+    <t>pyrite: 45</t>
+  </si>
+  <si>
+    <t>sphalerite: 25</t>
+  </si>
+  <si>
+    <t>hematite: 20</t>
+  </si>
+  <si>
+    <t>mars_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 10</t>
+  </si>
+  <si>
+    <t>spessartine: 10</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tantalite: 35 [1]</t>
+  </si>
+  <si>
+    <t>mars_tungsten</t>
+  </si>
+  <si>
+    <t>scheelite: 45 [1]</t>
+  </si>
+  <si>
+    <t>tungstate: 35</t>
+  </si>
+  <si>
+    <t>lithium: 20</t>
+  </si>
+  <si>
+    <t>mars_surface_bismuthinite</t>
+  </si>
+  <si>
+    <t>bismuth: 20 [1]</t>
+  </si>
+  <si>
+    <t>sulfur: 10</t>
+  </si>
+  <si>
+    <t>gypsum: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 55 [1]</t>
+  </si>
+  <si>
+    <t>tin: 35</t>
+  </si>
+  <si>
+    <t>saltpeter: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_hematite</t>
+  </si>
+  <si>
+    <t>calcite: 5</t>
+  </si>
+  <si>
+    <t>mars_surface_nickel_galena</t>
+  </si>
+  <si>
+    <t>sphalerite: 15</t>
+  </si>
+  <si>
+    <t>galena: 30</t>
+  </si>
+  <si>
+    <t>silver: 10</t>
+  </si>
+  <si>
+    <t>mars_surface_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 60 [1]</t>
+  </si>
+  <si>
+    <t>redstone: 5</t>
+  </si>
+  <si>
+    <t>glacio_stone</t>
+  </si>
+  <si>
+    <t>moon_deepslate</t>
+  </si>
+  <si>
+    <t>moon_stone</t>
+  </si>
+  <si>
+    <t>moon_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 25</t>
+  </si>
+  <si>
+    <t>pyrochlore: 40 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 5</t>
+  </si>
+  <si>
+    <t>moon_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 35 [1]</t>
+  </si>
+  <si>
+    <t>ilmenite: 40 [1]</t>
+  </si>
+  <si>
+    <t>armalcolite: 20</t>
+  </si>
+  <si>
+    <t>moon_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium: 35 [1]</t>
+  </si>
+  <si>
+    <t>emerald: 50 [2]</t>
+  </si>
+  <si>
+    <t>thorium: 1</t>
+  </si>
+  <si>
+    <t>rock_salt: 20</t>
+  </si>
+  <si>
+    <t>moon_cassiterite</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 30 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 5</t>
+  </si>
+  <si>
+    <t>cassiterite: 35 [1]</t>
+  </si>
+  <si>
+    <t>tin: 15</t>
+  </si>
+  <si>
+    <t>moon_sheldonite</t>
+  </si>
+  <si>
+    <t>moon_desh</t>
+  </si>
+  <si>
+    <t>desh: 25</t>
+  </si>
+  <si>
+    <t>ilmenite: 30 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 25</t>
+  </si>
+  <si>
+    <t>moon_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10</t>
+  </si>
+  <si>
+    <t>yellow_garnet: 15</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [1]</t>
+  </si>
+  <si>
+    <t>opal: 40 [1]</t>
+  </si>
+  <si>
+    <t>moon_garnierite</t>
+  </si>
+  <si>
+    <t>pentlandite: 25 [1]</t>
+  </si>
+  <si>
+    <t>cobalt: 15</t>
+  </si>
+  <si>
+    <t>moon_gold</t>
+  </si>
+  <si>
+    <t>magnetite: 20</t>
+  </si>
+  <si>
+    <t>moon_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 50 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 35</t>
+  </si>
+  <si>
+    <t>olivine: 10</t>
+  </si>
+  <si>
+    <t>moon_gypsum</t>
+  </si>
+  <si>
+    <t>calcite: 25</t>
+  </si>
+  <si>
+    <t>alunite: 15</t>
+  </si>
+  <si>
+    <t>gypsum: 35 [1]</t>
+  </si>
+  <si>
+    <t>moon_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30</t>
+  </si>
+  <si>
+    <t>talc: 20</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 25</t>
+  </si>
+  <si>
+    <t>pentlandite: 15</t>
+  </si>
+  <si>
+    <t>moon_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 25</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 15</t>
+  </si>
+  <si>
+    <t>chromite: 40 [2]</t>
+  </si>
+  <si>
+    <t>gold: 15</t>
+  </si>
+  <si>
+    <t>sapphire: 5</t>
+  </si>
+  <si>
+    <t>moon_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 30</t>
+  </si>
+  <si>
+    <t>pyrolusite: 20</t>
+  </si>
+  <si>
+    <t>tantalite: 10</t>
+  </si>
+  <si>
+    <t>moon_mica</t>
+  </si>
+  <si>
+    <t>kyanite: 35 [1]</t>
+  </si>
+  <si>
+    <t>mica: 25</t>
+  </si>
+  <si>
+    <t>bauxite: 25</t>
+  </si>
+  <si>
+    <t>aluminium: 15</t>
+  </si>
+  <si>
+    <t>moon_molybdenum</t>
+  </si>
+  <si>
+    <t>wulfenite: 40 [1]</t>
+  </si>
+  <si>
+    <t>molybdenite: 30 [1]</t>
+  </si>
+  <si>
+    <t>powellite: 15</t>
+  </si>
+  <si>
+    <t>moon_monazite</t>
+  </si>
+  <si>
+    <t>olivine: 1</t>
+  </si>
+  <si>
+    <t>moon_pyrolusite</t>
+  </si>
+  <si>
+    <t>pyrolusite: 40 [2]</t>
+  </si>
+  <si>
+    <t>cobaltite: 25</t>
+  </si>
+  <si>
+    <t>cobalt: 25</t>
+  </si>
+  <si>
+    <t>tantalite: 15</t>
+  </si>
+  <si>
+    <t>moon_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 20</t>
+  </si>
+  <si>
+    <t>certus_quartz: 45 [2]</t>
+  </si>
+  <si>
+    <t>nether_quartz: 30 [1]</t>
+  </si>
+  <si>
+    <t>barite: 5</t>
+  </si>
+  <si>
+    <t>moon_redstone</t>
   </si>
   <si>
     <t>cinnabar: 20</t>
   </si>
   <si>
-    <t>deep_bismuth</t>
-  </si>
-  <si>
-    <t>tfc:pipe_vein</t>
-  </si>
-  <si>
-    <t>bismuth: 45</t>
-  </si>
-  <si>
-    <t>silver: 40</t>
-  </si>
-  <si>
-    <t>gold: 40</t>
-  </si>
-  <si>
-    <t>electrotine: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_copper_iron</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 30 [1]</t>
-  </si>
-  <si>
-    <t>goethite: 25</t>
+    <t>moon_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35 [1]</t>
+  </si>
+  <si>
+    <t>soapstone: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 45</t>
+  </si>
+  <si>
+    <t>moon_sapphire</t>
+  </si>
+  <si>
+    <t>olivine: 2</t>
+  </si>
+  <si>
+    <t>moon_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tungstate: 50 [2]</t>
+  </si>
+  <si>
+    <t>lithium: 10</t>
+  </si>
+  <si>
+    <t>moon_silver</t>
+  </si>
+  <si>
+    <t>silver: 45 [1]</t>
+  </si>
+  <si>
+    <t>moon_sphalerite</t>
+  </si>
+  <si>
+    <t>desh: 10</t>
+  </si>
+  <si>
+    <t>sphalerite: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 40</t>
+  </si>
+  <si>
+    <t>moon_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>copper: 15</t>
+  </si>
+  <si>
+    <t>chalcocite: 25</t>
+  </si>
+  <si>
+    <t>moon_topaz</t>
+  </si>
+  <si>
+    <t>blue_topaz: 35 [1]</t>
+  </si>
+  <si>
+    <t>topaz: 25 [1]</t>
+  </si>
+  <si>
+    <t>chalcocite: 25 [1]</t>
+  </si>
+  <si>
+    <t>bornite: 15</t>
+  </si>
+  <si>
+    <t>blackstone</t>
+  </si>
+  <si>
+    <t>deepslate</t>
+  </si>
+  <si>
+    <t>dripstone</t>
+  </si>
+  <si>
+    <t>nether_anthracite</t>
+  </si>
+  <si>
+    <t>anthracite: 100</t>
+  </si>
+  <si>
+    <t>nether_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 50 [2]</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 35 [1]</t>
+  </si>
+  <si>
+    <t>nether_basaltic_sands</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>fullers_earth: 25 [1]</t>
+  </si>
+  <si>
+    <t>gypsum: 15</t>
+  </si>
+  <si>
+    <t>nether_beryllium</t>
+  </si>
+  <si>
+    <t>nether_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 40 [2]</t>
+  </si>
+  <si>
+    <t>tin: 60 [2]</t>
+  </si>
+  <si>
+    <t>nether_sheldonite</t>
+  </si>
+  <si>
+    <t>cooperite: 25 [1]</t>
+  </si>
+  <si>
+    <t>platinum: 5 [1]</t>
+  </si>
+  <si>
+    <t>nether_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 10 [1]</t>
+  </si>
+  <si>
+    <t>copper: 65 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10 [1]</t>
+  </si>
+  <si>
+    <t>yellow_garnet: 15 [1]</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [2]</t>
+  </si>
+  <si>
+    <t>opal: 40 [2]</t>
+  </si>
+  <si>
+    <t>nether_garnet_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 35 [1]</t>
+  </si>
+  <si>
+    <t>garnet_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 25 [1]</t>
+  </si>
+  <si>
+    <t>diatomite: 15</t>
+  </si>
+  <si>
+    <t>nether_garnierite</t>
+  </si>
+  <si>
+    <t>cobaltite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_goethite</t>
+  </si>
+  <si>
+    <t>goethite: 50 [3]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 15 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 15 [1]</t>
+  </si>
+  <si>
+    <t>malachite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_gold</t>
+  </si>
+  <si>
+    <t>goethite: 5</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 5</t>
+  </si>
+  <si>
+    <t>gold: 75 [2]</t>
+  </si>
+  <si>
+    <t>nether_graphite</t>
+  </si>
+  <si>
+    <t>diamond: 40 [1]</t>
+  </si>
+  <si>
+    <t>coal: 15</t>
+  </si>
+  <si>
+    <t>nether_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20 [1]</t>
+  </si>
+  <si>
+    <t>calcite: 30 [1]</t>
+  </si>
+  <si>
+    <t>fullers_earth: 15</t>
+  </si>
+  <si>
+    <t>nether_hematite</t>
+  </si>
+  <si>
+    <t>goethite: 25 [1]</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 15</t>
+  </si>
+  <si>
+    <t>hematite: 35 [3]</t>
+  </si>
+  <si>
+    <t>ruby: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 25 [1]</t>
+  </si>
+  <si>
+    <t>lapis: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30 [1]</t>
+  </si>
+  <si>
+    <t>talc: 20 [1]</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 25 [1]</t>
+  </si>
+  <si>
+    <t>pentlandite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 10</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 15 [1]</t>
+  </si>
+  <si>
+    <t>chromite: 5</t>
+  </si>
+  <si>
+    <t>gold: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 30 [1]</t>
+  </si>
+  <si>
+    <t>spessartine: 20 [1]</t>
+  </si>
+  <si>
+    <t>pyrolusite: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_mica</t>
+  </si>
+  <si>
+    <t>mica: 25 [1]</t>
+  </si>
+  <si>
+    <t>pollucite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_molybdenum</t>
+  </si>
+  <si>
+    <t>powellite: 10</t>
+  </si>
+  <si>
+    <t>nickel: 15</t>
+  </si>
+  <si>
+    <t>nether_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 50 [2]</t>
+  </si>
+  <si>
+    <t>monazite: 25 [1]</t>
+  </si>
+  <si>
+    <t>neodymium: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_naquadah</t>
+  </si>
+  <si>
+    <t>naquadah: 75 [2]</t>
+  </si>
+  <si>
+    <t>nether_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 35 [1]</t>
+  </si>
+  <si>
+    <t>magnesite: 25 [1]</t>
+  </si>
+  <si>
+    <t>olivine: 25 [1]</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 15</t>
+  </si>
+  <si>
+    <t>nether_pitchblende</t>
+  </si>
+  <si>
+    <t>wulfenite: 10</t>
+  </si>
+  <si>
+    <t>nether_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 30 [1]</t>
+  </si>
+  <si>
+    <t>nether_quartz: 65 [2]</t>
+  </si>
+  <si>
+    <t>barite: 25</t>
+  </si>
+  <si>
+    <t>nether_redstone</t>
+  </si>
+  <si>
+    <t>ruby: 35 [1]</t>
+  </si>
+  <si>
+    <t>cinnabar: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_saltpeter</t>
+  </si>
+  <si>
+    <t>diatomite: 25 [1]</t>
+  </si>
+  <si>
+    <t>electrotine: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_sapphire</t>
+  </si>
+  <si>
+    <t>pyrope: 25 [1]</t>
+  </si>
+  <si>
+    <t>sapphire: 15 [1]</t>
+  </si>
+  <si>
+    <t>green_sapphire: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 45 [2]</t>
+  </si>
+  <si>
+    <t>tungstate: 35 [1]</t>
+  </si>
+  <si>
+    <t>lithium: 20 [1]</t>
+  </si>
+  <si>
+    <t>nether_silver</t>
+  </si>
+  <si>
+    <t>silver: 35 [1]</t>
+  </si>
+  <si>
+    <t>lead: 35 [1]</t>
+  </si>
+  <si>
+    <t>nether_sphalerite</t>
+  </si>
+  <si>
+    <t>sulfur: 35 [1]</t>
+  </si>
+  <si>
+    <t>sphalerite: 40 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 25 [1]</t>
+  </si>
+  <si>
+    <t>nether_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 50 [2]</t>
+  </si>
+  <si>
+    <t>pyrite: 35 [1]</t>
+  </si>
+  <si>
+    <t>sphalerite: 15 [1]</t>
+  </si>
+  <si>
+    <t>nether_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 50 [2]</t>
+  </si>
+  <si>
+    <t>copper: 30 [1]</t>
+  </si>
+  <si>
+    <t>nether_topaz</t>
+  </si>
+  <si>
+    <t>flavolite</t>
+  </si>
+  <si>
+    <t>sandy_jadestone</t>
+  </si>
+  <si>
+    <t>venus_manual_salt</t>
+  </si>
+  <si>
+    <t>salt: 80</t>
+  </si>
+  <si>
+    <t>rock_salt: 10</t>
+  </si>
+  <si>
+    <t>lepidolite: 5</t>
+  </si>
+  <si>
+    <t>spodumene: 5</t>
+  </si>
+  <si>
+    <t>venus_manual_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 80</t>
   </si>
   <si>
     <t>pyrite: 15</t>
-  </si>
-  <si>
-    <t>copper: 10</t>
-  </si>
-  <si>
-    <t>deep_copper_sulfide</t>
-  </si>
-  <si>
-    <t>sulfur: 40 [1]</t>
-  </si>
-  <si>
-    <t>bornite: 5</t>
-  </si>
-  <si>
-    <t>chalcocite: 5</t>
-  </si>
-  <si>
-    <t>deep_copper_tin</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 7</t>
-  </si>
-  <si>
-    <t>zeolite: 3</t>
-  </si>
-  <si>
-    <t>cassiterite: 3</t>
-  </si>
-  <si>
-    <t>deep_galena</t>
-  </si>
-  <si>
-    <t>galena: 60 [1]</t>
-  </si>
-  <si>
-    <t>silver: 30</t>
-  </si>
-  <si>
-    <t>lead: 25</t>
-  </si>
-  <si>
-    <t>deep_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 70 [1]</t>
-  </si>
-  <si>
-    <t>coal: 20 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 10</t>
-  </si>
-  <si>
-    <t>deep_graphite_volcanic</t>
-  </si>
-  <si>
-    <t>graphite: 60</t>
-  </si>
-  <si>
-    <t>coal: 20</t>
-  </si>
-  <si>
-    <t>diamond: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_iron</t>
-  </si>
-  <si>
-    <t>goethite: 35 [1]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 25</t>
-  </si>
-  <si>
-    <t>hematite: 25</t>
-  </si>
-  <si>
-    <t>malachite: 25</t>
-  </si>
-  <si>
-    <t>deep_kyanite</t>
-  </si>
-  <si>
-    <t>kyanite: 60 [1]</t>
-  </si>
-  <si>
-    <t>mica: 40</t>
-  </si>
-  <si>
-    <t>pollucite: 25</t>
-  </si>
-  <si>
-    <t>deep_lazurite_calcite</t>
-  </si>
-  <si>
-    <t>lazurite: 50 [1]</t>
-  </si>
-  <si>
-    <t>sodalite: 40</t>
-  </si>
-  <si>
-    <t>lapis: 30</t>
-  </si>
-  <si>
-    <t>calcite: 30</t>
-  </si>
-  <si>
-    <t>deep_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 60 [1]</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 35</t>
-  </si>
-  <si>
-    <t>gold: 25</t>
-  </si>
-  <si>
-    <t>deep_magnetite_olivine</t>
-  </si>
-  <si>
-    <t>bentonite: 45 [1]</t>
-  </si>
-  <si>
-    <t>magnesite: 20</t>
-  </si>
-  <si>
-    <t>olivine: 10</t>
-  </si>
-  <si>
-    <t>fullers_earth: 60</t>
-  </si>
-  <si>
-    <t>deep_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 45</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40</t>
-  </si>
-  <si>
-    <t>tantalite: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_molybdenum</t>
-  </si>
-  <si>
-    <t>wulfenite: 40</t>
-  </si>
-  <si>
-    <t>molybdenite: 80 [1]</t>
-  </si>
-  <si>
-    <t>molybdenum: 10</t>
-  </si>
-  <si>
-    <t>powellite: 10</t>
-  </si>
-  <si>
-    <t>deep_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite: 60 [1]</t>
-  </si>
-  <si>
-    <t>monazite: 30</t>
-  </si>
-  <si>
-    <t>neodymium: 10</t>
-  </si>
-  <si>
-    <t>deep_nickel</t>
-  </si>
-  <si>
-    <t>garnierite: 70 [1]</t>
-  </si>
-  <si>
-    <t>nickel: 40</t>
-  </si>
-  <si>
-    <t>cobaltite: 50</t>
-  </si>
-  <si>
-    <t>pentlandite: 30</t>
-  </si>
-  <si>
-    <t>deep_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 40 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 20</t>
-  </si>
-  <si>
-    <t>cinnabar: 10</t>
-  </si>
-  <si>
-    <t>deep_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 60 [1]</t>
-  </si>
-  <si>
-    <t>diatomite: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 20</t>
-  </si>
-  <si>
-    <t>alunite: 20</t>
-  </si>
-  <si>
-    <t>deep_sapphire</t>
-  </si>
-  <si>
-    <t>almandine: 24 [1]</t>
-  </si>
-  <si>
-    <t>pyrope: 36</t>
-  </si>
-  <si>
-    <t>sapphire: 48</t>
-  </si>
-  <si>
-    <t>green_sapphire: 39</t>
-  </si>
-  <si>
-    <t>deep_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 60</t>
-  </si>
-  <si>
-    <t>tungstate: 60</t>
-  </si>
-  <si>
-    <t>lithium: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_sphalerite</t>
-  </si>
-  <si>
-    <t>sulfur: 1</t>
-  </si>
-  <si>
-    <t>pyrite: 3</t>
-  </si>
-  <si>
-    <t>sphalerite: 7</t>
-  </si>
-  <si>
-    <t>deep_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 50 [1]</t>
-  </si>
-  <si>
-    <t>deep_tantalite</t>
-  </si>
-  <si>
-    <t>grossular: 60 [1]</t>
-  </si>
-  <si>
-    <t>spessartine: 50</t>
-  </si>
-  <si>
-    <t>tantalite: 30</t>
-  </si>
-  <si>
-    <t>deep_thorianite</t>
-  </si>
-  <si>
-    <t>thorium: 40</t>
-  </si>
-  <si>
-    <t>uraninite: 20</t>
-  </si>
-  <si>
-    <t>emerald: 10</t>
-  </si>
-  <si>
-    <t>beryllium: 20 [1]</t>
-  </si>
-  <si>
-    <t>deep_tin</t>
-  </si>
-  <si>
-    <t>cassiterite: 70 [1]</t>
-  </si>
-  <si>
-    <t>tin: 10</t>
-  </si>
-  <si>
-    <t>deep_topaz</t>
-  </si>
-  <si>
-    <t>blue_topaz: 70 [1]</t>
-  </si>
-  <si>
-    <t>topaz: 50</t>
-  </si>
-  <si>
-    <t>chalcocite: 30</t>
-  </si>
-  <si>
-    <t>bornite: 10</t>
-  </si>
-  <si>
-    <t>high_bismuth_mountain</t>
-  </si>
-  <si>
-    <t>bismuth: 1</t>
-  </si>
-  <si>
-    <t>high_coal</t>
-  </si>
-  <si>
-    <t>coal: 100 [2]</t>
-  </si>
-  <si>
-    <t>high_gypsum</t>
-  </si>
-  <si>
-    <t>gypsum: 100 [1]</t>
-  </si>
-  <si>
-    <t>high_lead</t>
-  </si>
-  <si>
-    <t>lead: 6</t>
-  </si>
-  <si>
-    <t>silver: 4</t>
-  </si>
-  <si>
-    <t>high_realgar</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 40 [1]</t>
-  </si>
-  <si>
-    <t>zeolite: 20</t>
-  </si>
-  <si>
-    <t>realgar: 10</t>
-  </si>
-  <si>
-    <t>high_sulfur</t>
-  </si>
-  <si>
-    <t>high_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 50 [1]</t>
-  </si>
-  <si>
-    <t>copper: 30</t>
-  </si>
-  <si>
-    <t>stibnite: 20</t>
-  </si>
-  <si>
-    <t>high_tin</t>
-  </si>
-  <si>
-    <t>tin: 4</t>
-  </si>
-  <si>
-    <t>cassiterite: 6</t>
-  </si>
-  <si>
-    <t>normal_asbestos_dry</t>
-  </si>
-  <si>
-    <t>asbestos: 1</t>
-  </si>
-  <si>
-    <t>normal_coal</t>
-  </si>
-  <si>
-    <t>coal: 100 [1]</t>
-  </si>
-  <si>
-    <t>normal_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 35 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 20</t>
-  </si>
-  <si>
-    <t>normal_copper_gypsum</t>
-  </si>
-  <si>
-    <t>chalcocite: 48 [1]</t>
-  </si>
-  <si>
-    <t>gypsum: 12</t>
-  </si>
-  <si>
-    <t>cobalt: 20</t>
-  </si>
-  <si>
-    <t>sulfur: 8</t>
-  </si>
-  <si>
-    <t>normal_galena</t>
-  </si>
-  <si>
-    <t>galena: 70 [1]</t>
-  </si>
-  <si>
-    <t>silver: 20</t>
-  </si>
-  <si>
-    <t>normal_garnierite</t>
-  </si>
-  <si>
-    <t>garnierite: 60 [1]</t>
-  </si>
-  <si>
-    <t>nickel: 20</t>
-  </si>
-  <si>
-    <t>cobaltite: 35</t>
-  </si>
-  <si>
-    <t>normal_gold</t>
-  </si>
-  <si>
-    <t>gold: 4</t>
-  </si>
-  <si>
-    <t>magnetite: 3</t>
-  </si>
-  <si>
-    <t>normal_iron</t>
-  </si>
-  <si>
-    <t>hematite: 40</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 70 [1]</t>
-  </si>
-  <si>
-    <t>normal_mica</t>
-  </si>
-  <si>
-    <t>mica: 7</t>
-  </si>
-  <si>
-    <t>kyanite: 5</t>
-  </si>
-  <si>
-    <t>normal_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 90 [1]</t>
-  </si>
-  <si>
-    <t>barite: 30</t>
-  </si>
-  <si>
-    <t>normal_quartz_borax</t>
-  </si>
-  <si>
-    <t>quartzite: 6</t>
-  </si>
-  <si>
-    <t>borax: 1</t>
-  </si>
-  <si>
-    <t>normal_salt</t>
-  </si>
-  <si>
-    <t>salt: 60 [1]</t>
-  </si>
-  <si>
-    <t>rock_salt: 30</t>
-  </si>
-  <si>
-    <t>borax: 10</t>
-  </si>
-  <si>
-    <t>normal_sphalerite</t>
-  </si>
-  <si>
-    <t>sphalerite: 10</t>
-  </si>
-  <si>
-    <t>galena: 3</t>
-  </si>
-  <si>
-    <t>normal_spodumene</t>
-  </si>
-  <si>
-    <t>spodumene: 75 [1]</t>
-  </si>
-  <si>
-    <t>rock_salt: 25</t>
-  </si>
-  <si>
-    <t>normal_sulfide</t>
-  </si>
-  <si>
-    <t>sulfur: 20</t>
-  </si>
-  <si>
-    <t>stibnite: 15</t>
-  </si>
-  <si>
-    <t>bornite: 45 [1]</t>
-  </si>
-  <si>
-    <t>normal_tarkianite</t>
-  </si>
-  <si>
-    <t>tarkianite: 35 [1]</t>
-  </si>
-  <si>
-    <t>borax: 20</t>
-  </si>
-  <si>
-    <t>trona: 10</t>
-  </si>
-  <si>
-    <t>sand_basaltic</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand: 8</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 5</t>
-  </si>
-  <si>
-    <t>garnet_sand: 1</t>
-  </si>
-  <si>
-    <t>sand_granitic</t>
-  </si>
-  <si>
-    <t>granitic_mineral_sand: 8</t>
-  </si>
-  <si>
-    <t>fullers_earth: 4</t>
-  </si>
-  <si>
-    <t>sand_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 1</t>
-  </si>
-  <si>
-    <t>surface_bismuth</t>
-  </si>
-  <si>
-    <t>surface_coal</t>
-  </si>
-  <si>
-    <t>lignite: 100</t>
-  </si>
-  <si>
-    <t>surface_cobaltite</t>
-  </si>
-  <si>
-    <t>cobaltite: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_gold</t>
-  </si>
-  <si>
-    <t>gold: 1</t>
-  </si>
-  <si>
-    <t>surface_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_limonite</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_malachite</t>
-  </si>
-  <si>
-    <t>malachite: 1</t>
-  </si>
-  <si>
-    <t>surface_mica</t>
-  </si>
-  <si>
-    <t>mica: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_native_copper</t>
-  </si>
-  <si>
-    <t>copper: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_nickel</t>
-  </si>
-  <si>
-    <t>garnierite: 1</t>
-  </si>
-  <si>
-    <t>surface_salpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_sphalerite</t>
-  </si>
-  <si>
-    <t>sphalerite: 1</t>
-  </si>
-  <si>
-    <t>surface_sylvite_salt</t>
-  </si>
-  <si>
-    <t>salt: 6</t>
-  </si>
-  <si>
-    <t>rock_salt: 4</t>
-  </si>
-  <si>
-    <t>surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 1</t>
-  </si>
-  <si>
-    <t>surface_tricalcium_phosphate</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 1</t>
-  </si>
-  <si>
-    <t>mars_stone</t>
-  </si>
-  <si>
-    <t>red_granite</t>
-  </si>
-  <si>
-    <t>venus_stone</t>
-  </si>
-  <si>
-    <t>deep_mars_chromite</t>
-  </si>
-  <si>
-    <t>redstone: 45 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 35</t>
-  </si>
-  <si>
-    <t>chromite: 20</t>
-  </si>
-  <si>
-    <t>deep_mars_pitchblende</t>
-  </si>
-  <si>
-    <t>pitchblende: 50 [1]</t>
-  </si>
-  <si>
-    <t>thorium: 25</t>
-  </si>
-  <si>
-    <t>deep_mars_sheldonite</t>
-  </si>
-  <si>
-    <t>bornite: 35 [1]</t>
-  </si>
-  <si>
-    <t>cooperite: 25</t>
-  </si>
-  <si>
-    <t>nickel: 25</t>
-  </si>
-  <si>
-    <t>platinum: 15</t>
-  </si>
-  <si>
-    <t>mars_almandine</t>
-  </si>
-  <si>
-    <t>almandine: 35 [1]</t>
-  </si>
-  <si>
-    <t>pyrope: 25</t>
-  </si>
-  <si>
-    <t>sapphire: 15</t>
-  </si>
-  <si>
-    <t>green_sapphire: 15</t>
-  </si>
-  <si>
-    <t>hematite: 5</t>
-  </si>
-  <si>
-    <t>mars_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 50 [1]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 35</t>
-  </si>
-  <si>
-    <t>pyrochlore: 15</t>
-  </si>
-  <si>
-    <t>mars_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium: 35</t>
-  </si>
-  <si>
-    <t>emerald: 50</t>
-  </si>
-  <si>
-    <t>realgar: 15</t>
-  </si>
-  <si>
-    <t>mars_coal</t>
-  </si>
-  <si>
-    <t>coal: 70 [1]</t>
-  </si>
-  <si>
-    <t>mars_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 65 [1]</t>
-  </si>
-  <si>
-    <t>copper: 20</t>
-  </si>
-  <si>
-    <t>pyrite: 10</t>
-  </si>
-  <si>
-    <t>mars_galena</t>
-  </si>
-  <si>
-    <t>galena: 30 [1]</t>
-  </si>
-  <si>
-    <t>silver: 15</t>
-  </si>
-  <si>
-    <t>mars_gold</t>
-  </si>
-  <si>
-    <t>green_sapphire: 5</t>
-  </si>
-  <si>
-    <t>bauxite: 20</t>
-  </si>
-  <si>
-    <t>gold: 55 [1]</t>
-  </si>
-  <si>
-    <t>mars_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 45 [1]</t>
-  </si>
-  <si>
-    <t>coal: 25</t>
-  </si>
-  <si>
-    <t>diamond: 20</t>
-  </si>
-  <si>
-    <t>hematite: 10</t>
-  </si>
-  <si>
-    <t>mars_hematite</t>
-  </si>
-  <si>
-    <t>hematite: 50 [1]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 30</t>
-  </si>
-  <si>
-    <t>goethite: 15</t>
-  </si>
-  <si>
-    <t>gold: 5</t>
-  </si>
-  <si>
-    <t>mars_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35</t>
-  </si>
-  <si>
-    <t>sodalite: 25</t>
-  </si>
-  <si>
-    <t>lapis: 25</t>
-  </si>
-  <si>
-    <t>calcite: 15</t>
-  </si>
-  <si>
-    <t>mars_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 15</t>
-  </si>
-  <si>
-    <t>talc: 15</t>
-  </si>
-  <si>
-    <t>trona: 25</t>
-  </si>
-  <si>
-    <t>pentlandite: 5</t>
-  </si>
-  <si>
-    <t>mars_neodynium</t>
-  </si>
-  <si>
-    <t>bastnasite: 50 [1]</t>
-  </si>
-  <si>
-    <t>monazite: 25</t>
-  </si>
-  <si>
-    <t>neodymium: 5</t>
-  </si>
-  <si>
-    <t>mars_nickel</t>
-  </si>
-  <si>
-    <t>garnierite: 25 [1]</t>
-  </si>
-  <si>
-    <t>cobaltite: 20</t>
-  </si>
-  <si>
-    <t>mars_pitchblende</t>
-  </si>
-  <si>
-    <t>pitchblende: 35 [1]</t>
-  </si>
-  <si>
-    <t>mars_quartzite</t>
-  </si>
-  <si>
-    <t>quartzite: 35 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 15</t>
-  </si>
-  <si>
-    <t>mars_salt</t>
-  </si>
-  <si>
-    <t>rock_salt: 20 [1]</t>
-  </si>
-  <si>
-    <t>salt: 30</t>
-  </si>
-  <si>
-    <t>lepidolite: 15</t>
-  </si>
-  <si>
-    <t>spodumene: 35</t>
-  </si>
-  <si>
-    <t>mars_stibnite</t>
-  </si>
-  <si>
-    <t>mars_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 15</t>
-  </si>
-  <si>
-    <t>pyrite: 45</t>
-  </si>
-  <si>
-    <t>sphalerite: 25</t>
-  </si>
-  <si>
-    <t>hematite: 20</t>
-  </si>
-  <si>
-    <t>mars_tantalite</t>
-  </si>
-  <si>
-    <t>grossular: 10</t>
-  </si>
-  <si>
-    <t>spessartine: 10</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tantalite: 35 [1]</t>
-  </si>
-  <si>
-    <t>mars_tungsten</t>
-  </si>
-  <si>
-    <t>scheelite: 45 [1]</t>
-  </si>
-  <si>
-    <t>tungstate: 35</t>
-  </si>
-  <si>
-    <t>lithium: 20</t>
-  </si>
-  <si>
-    <t>mars_surface_bismuthinite</t>
-  </si>
-  <si>
-    <t>bismuth: 20 [1]</t>
-  </si>
-  <si>
-    <t>sulfur: 10</t>
-  </si>
-  <si>
-    <t>gypsum: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 55 [1]</t>
-  </si>
-  <si>
-    <t>tin: 35</t>
-  </si>
-  <si>
-    <t>saltpeter: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_hematite</t>
-  </si>
-  <si>
-    <t>calcite: 5</t>
-  </si>
-  <si>
-    <t>mars_surface_nickel_galena</t>
-  </si>
-  <si>
-    <t>sphalerite: 15</t>
-  </si>
-  <si>
-    <t>galena: 30</t>
-  </si>
-  <si>
-    <t>silver: 10</t>
-  </si>
-  <si>
-    <t>cobaltite: 10</t>
-  </si>
-  <si>
-    <t>mars_surface_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 60 [1]</t>
-  </si>
-  <si>
-    <t>redstone: 5</t>
-  </si>
-  <si>
-    <t>glacio_stone</t>
-  </si>
-  <si>
-    <t>moon_deepslate</t>
-  </si>
-  <si>
-    <t>moon_stone</t>
-  </si>
-  <si>
-    <t>moon_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 25</t>
-  </si>
-  <si>
-    <t>pyrochlore: 40 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 5</t>
-  </si>
-  <si>
-    <t>moon_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite: 35 [1]</t>
-  </si>
-  <si>
-    <t>ilmenite: 40 [1]</t>
-  </si>
-  <si>
-    <t>armalcolite: 20</t>
-  </si>
-  <si>
-    <t>moon_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium: 35 [1]</t>
-  </si>
-  <si>
-    <t>emerald: 50 [2]</t>
-  </si>
-  <si>
-    <t>thorium: 1</t>
-  </si>
-  <si>
-    <t>rock_salt: 20</t>
-  </si>
-  <si>
-    <t>moon_cassiterite</t>
-  </si>
-  <si>
-    <t>zeolite: 5</t>
-  </si>
-  <si>
-    <t>cassiterite: 35 [1]</t>
-  </si>
-  <si>
-    <t>tin: 15</t>
-  </si>
-  <si>
-    <t>moon_sheldonite</t>
-  </si>
-  <si>
-    <t>moon_desh</t>
-  </si>
-  <si>
-    <t>desh: 25</t>
-  </si>
-  <si>
-    <t>ilmenite: 30 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 25</t>
-  </si>
-  <si>
-    <t>moon_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10</t>
-  </si>
-  <si>
-    <t>yellow_garnet: 15</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [1]</t>
-  </si>
-  <si>
-    <t>opal: 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_garnierite</t>
-  </si>
-  <si>
-    <t>pentlandite: 25 [1]</t>
-  </si>
-  <si>
-    <t>cobalt: 15</t>
-  </si>
-  <si>
-    <t>moon_gold</t>
-  </si>
-  <si>
-    <t>magnetite: 20</t>
-  </si>
-  <si>
-    <t>moon_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 50 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 35</t>
-  </si>
-  <si>
-    <t>moon_gypsum</t>
-  </si>
-  <si>
-    <t>calcite: 25</t>
-  </si>
-  <si>
-    <t>alunite: 15</t>
-  </si>
-  <si>
-    <t>gypsum: 35 [1]</t>
-  </si>
-  <si>
-    <t>moon_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30</t>
-  </si>
-  <si>
-    <t>talc: 20</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 25</t>
-  </si>
-  <si>
-    <t>pentlandite: 15</t>
-  </si>
-  <si>
-    <t>moon_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 25</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 15</t>
-  </si>
-  <si>
-    <t>chromite: 40 [2]</t>
-  </si>
-  <si>
-    <t>gold: 15</t>
-  </si>
-  <si>
-    <t>sapphire: 5</t>
-  </si>
-  <si>
-    <t>moon_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 30</t>
-  </si>
-  <si>
-    <t>spessartine: 20</t>
-  </si>
-  <si>
-    <t>pyrolusite: 20</t>
-  </si>
-  <si>
-    <t>tantalite: 10</t>
-  </si>
-  <si>
-    <t>moon_mica</t>
-  </si>
-  <si>
-    <t>kyanite: 35 [1]</t>
-  </si>
-  <si>
-    <t>mica: 25</t>
-  </si>
-  <si>
-    <t>bauxite: 25</t>
-  </si>
-  <si>
-    <t>aluminium: 15</t>
-  </si>
-  <si>
-    <t>moon_molybdenum</t>
-  </si>
-  <si>
-    <t>wulfenite: 40 [1]</t>
-  </si>
-  <si>
-    <t>molybdenite: 30 [1]</t>
-  </si>
-  <si>
-    <t>powellite: 15</t>
-  </si>
-  <si>
-    <t>moon_monazite</t>
-  </si>
-  <si>
-    <t>olivine: 1</t>
-  </si>
-  <si>
-    <t>moon_pyrolusite</t>
-  </si>
-  <si>
-    <t>pyrolusite: 40 [2]</t>
-  </si>
-  <si>
-    <t>cobaltite: 25</t>
-  </si>
-  <si>
-    <t>cobalt: 25</t>
-  </si>
-  <si>
-    <t>tantalite: 15</t>
-  </si>
-  <si>
-    <t>moon_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 20</t>
-  </si>
-  <si>
-    <t>certus_quartz: 45 [2]</t>
-  </si>
-  <si>
-    <t>nether_quartz: 30 [1]</t>
-  </si>
-  <si>
-    <t>barite: 5</t>
-  </si>
-  <si>
-    <t>moon_redstone</t>
-  </si>
-  <si>
-    <t>moon_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35 [1]</t>
-  </si>
-  <si>
-    <t>soapstone: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 45</t>
-  </si>
-  <si>
-    <t>moon_sapphire</t>
-  </si>
-  <si>
-    <t>olivine: 2</t>
-  </si>
-  <si>
-    <t>moon_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tungstate: 50 [2]</t>
-  </si>
-  <si>
-    <t>lithium: 10</t>
-  </si>
-  <si>
-    <t>moon_silver</t>
-  </si>
-  <si>
-    <t>silver: 45 [1]</t>
-  </si>
-  <si>
-    <t>moon_sphalerite</t>
-  </si>
-  <si>
-    <t>desh: 10</t>
-  </si>
-  <si>
-    <t>sphalerite: 50 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 40</t>
-  </si>
-  <si>
-    <t>moon_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 40 [1]</t>
-  </si>
-  <si>
-    <t>copper: 15</t>
-  </si>
-  <si>
-    <t>chalcocite: 25</t>
-  </si>
-  <si>
-    <t>moon_topaz</t>
-  </si>
-  <si>
-    <t>blue_topaz: 35 [1]</t>
-  </si>
-  <si>
-    <t>topaz: 25 [1]</t>
-  </si>
-  <si>
-    <t>chalcocite: 25 [1]</t>
-  </si>
-  <si>
-    <t>bornite: 15</t>
-  </si>
-  <si>
-    <t>blackstone</t>
-  </si>
-  <si>
-    <t>deepslate</t>
-  </si>
-  <si>
-    <t>dripstone</t>
-  </si>
-  <si>
-    <t>nether_anthracite</t>
-  </si>
-  <si>
-    <t>anthracite: 100</t>
-  </si>
-  <si>
-    <t>nether_apatite</t>
-  </si>
-  <si>
-    <t>apatite: 50 [2]</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_basaltic_sands</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>granitic_mineral_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>fullers_earth: 25 [1]</t>
-  </si>
-  <si>
-    <t>gypsum: 15</t>
-  </si>
-  <si>
-    <t>nether_beryllium</t>
-  </si>
-  <si>
-    <t>nether_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 40 [2]</t>
-  </si>
-  <si>
-    <t>tin: 60 [2]</t>
-  </si>
-  <si>
-    <t>nether_sheldonite</t>
-  </si>
-  <si>
-    <t>cooperite: 25 [1]</t>
-  </si>
-  <si>
-    <t>platinum: 5 [1]</t>
-  </si>
-  <si>
-    <t>nether_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 10 [1]</t>
-  </si>
-  <si>
-    <t>copper: 65 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet: 10 [1]</t>
-  </si>
-  <si>
-    <t>yellow_garnet: 15 [1]</t>
-  </si>
-  <si>
-    <t>amethyst: 40 [2]</t>
-  </si>
-  <si>
-    <t>opal: 40 [2]</t>
-  </si>
-  <si>
-    <t>nether_garnet_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 35 [1]</t>
-  </si>
-  <si>
-    <t>garnet_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>asbestos: 25 [1]</t>
-  </si>
-  <si>
-    <t>diatomite: 15</t>
-  </si>
-  <si>
-    <t>nether_garnierite</t>
-  </si>
-  <si>
-    <t>cobaltite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_goethite</t>
-  </si>
-  <si>
-    <t>goethite: 50 [3]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 15 [1]</t>
-  </si>
-  <si>
-    <t>hematite: 15 [1]</t>
-  </si>
-  <si>
-    <t>malachite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_gold</t>
-  </si>
-  <si>
-    <t>goethite: 5</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 5</t>
-  </si>
-  <si>
-    <t>gold: 75 [2]</t>
-  </si>
-  <si>
-    <t>nether_graphite</t>
-  </si>
-  <si>
-    <t>diamond: 40 [1]</t>
-  </si>
-  <si>
-    <t>coal: 15</t>
-  </si>
-  <si>
-    <t>nether_gypsum</t>
-  </si>
-  <si>
-    <t>borax: 20 [1]</t>
-  </si>
-  <si>
-    <t>calcite: 30 [1]</t>
-  </si>
-  <si>
-    <t>fullers_earth: 15</t>
-  </si>
-  <si>
-    <t>nether_hematite</t>
-  </si>
-  <si>
-    <t>goethite: 25 [1]</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 15</t>
-  </si>
-  <si>
-    <t>hematite: 35 [3]</t>
-  </si>
-  <si>
-    <t>ruby: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sodalite: 25 [1]</t>
-  </si>
-  <si>
-    <t>lapis: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30 [1]</t>
-  </si>
-  <si>
-    <t>talc: 20 [1]</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 25 [1]</t>
-  </si>
-  <si>
-    <t>pentlandite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 10</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 15 [1]</t>
-  </si>
-  <si>
-    <t>chromite: 5</t>
-  </si>
-  <si>
-    <t>gold: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 30 [1]</t>
-  </si>
-  <si>
-    <t>spessartine: 20 [1]</t>
-  </si>
-  <si>
-    <t>pyrolusite: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_mica</t>
-  </si>
-  <si>
-    <t>mica: 25 [1]</t>
-  </si>
-  <si>
-    <t>pollucite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_molybdenum</t>
-  </si>
-  <si>
-    <t>nickel: 15</t>
-  </si>
-  <si>
-    <t>nether_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite: 50 [2]</t>
-  </si>
-  <si>
-    <t>monazite: 25 [1]</t>
-  </si>
-  <si>
-    <t>neodymium: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_naquadah</t>
-  </si>
-  <si>
-    <t>naquadah: 75 [2]</t>
-  </si>
-  <si>
-    <t>nether_olivine</t>
-  </si>
-  <si>
-    <t>bentonite: 35 [1]</t>
-  </si>
-  <si>
-    <t>magnesite: 25 [1]</t>
-  </si>
-  <si>
-    <t>olivine: 25 [1]</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 15</t>
-  </si>
-  <si>
-    <t>nether_pitchblende</t>
-  </si>
-  <si>
-    <t>wulfenite: 10</t>
-  </si>
-  <si>
-    <t>nether_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 30 [1]</t>
-  </si>
-  <si>
-    <t>nether_quartz: 65 [2]</t>
-  </si>
-  <si>
-    <t>barite: 25</t>
-  </si>
-  <si>
-    <t>nether_redstone</t>
-  </si>
-  <si>
-    <t>ruby: 35 [1]</t>
-  </si>
-  <si>
-    <t>cinnabar: 20 [1]</t>
-  </si>
-  <si>
-    <t>nether_saltpeter</t>
-  </si>
-  <si>
-    <t>diatomite: 25 [1]</t>
-  </si>
-  <si>
-    <t>electrotine: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_sapphire</t>
-  </si>
-  <si>
-    <t>pyrope: 25 [1]</t>
-  </si>
-  <si>
-    <t>sapphire: 15 [1]</t>
-  </si>
-  <si>
-    <t>green_sapphire: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite: 45 [2]</t>
-  </si>
-  <si>
-    <t>tungstate: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_silver</t>
-  </si>
-  <si>
-    <t>silver: 35 [1]</t>
-  </si>
-  <si>
-    <t>lead: 35 [1]</t>
-  </si>
-  <si>
-    <t>nether_sphalerite</t>
-  </si>
-  <si>
-    <t>sulfur: 35 [1]</t>
-  </si>
-  <si>
-    <t>sphalerite: 40 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 25 [1]</t>
-  </si>
-  <si>
-    <t>nether_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 50 [2]</t>
-  </si>
-  <si>
-    <t>pyrite: 35 [1]</t>
-  </si>
-  <si>
-    <t>sphalerite: 15 [1]</t>
-  </si>
-  <si>
-    <t>nether_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 50 [2]</t>
-  </si>
-  <si>
-    <t>copper: 30 [1]</t>
-  </si>
-  <si>
-    <t>nether_topaz</t>
-  </si>
-  <si>
-    <t>flavolite</t>
-  </si>
-  <si>
-    <t>sandy_jadestone</t>
-  </si>
-  <si>
-    <t>venus_manual_salt</t>
-  </si>
-  <si>
-    <t>salt: 80</t>
-  </si>
-  <si>
-    <t>rock_salt: 10</t>
-  </si>
-  <si>
-    <t>lepidolite: 5</t>
-  </si>
-  <si>
-    <t>spodumene: 5</t>
-  </si>
-  <si>
-    <t>venus_manual_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 80</t>
   </si>
   <si>
     <t>sphalerite: 5</t>
@@ -2022,7 +2040,7 @@
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
     <col min="10" max="10" width="23.243886947631836" customWidth="1" style="3"/>
     <col min="11" max="11" width="23.763607025146484" customWidth="1" style="3"/>
-    <col min="12" max="12" width="16.331035614013672" customWidth="1" style="3"/>
+    <col min="12" max="12" width="15.237380027770996" customWidth="1" style="3"/>
     <col min="13" max="13" width="18.38944435119629" customWidth="1" style="3"/>
     <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
     <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
@@ -3508,10 +3526,10 @@
         <v>89</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -3600,7 +3618,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -3621,16 +3639,16 @@
         <v>37</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -3719,7 +3737,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -3740,13 +3758,13 @@
         <v>35</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -3835,7 +3853,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>62</v>
@@ -3859,16 +3877,16 @@
         <v>10</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -3957,7 +3975,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -3978,13 +3996,13 @@
         <v>41</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>44</v>
@@ -4073,7 +4091,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -4094,16 +4112,16 @@
         <v>37</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>44</v>
@@ -4192,7 +4210,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -4213,13 +4231,13 @@
         <v>37</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>43</v>
@@ -4308,7 +4326,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -4329,16 +4347,16 @@
         <v>38</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>43</v>
@@ -4427,7 +4445,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -4448,13 +4466,13 @@
         <v>27</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -4543,7 +4561,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -4564,16 +4582,16 @@
         <v>39</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -4662,7 +4680,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -4683,13 +4701,13 @@
         <v>28</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -4778,7 +4796,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -4799,16 +4817,16 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -4897,7 +4915,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>62</v>
@@ -4921,16 +4939,16 @@
         <v>10</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -5019,7 +5037,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -5040,13 +5058,13 @@
         <v>25</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -5135,7 +5153,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -5156,13 +5174,13 @@
         <v>29</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>43</v>
@@ -5251,7 +5269,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
@@ -5275,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>44</v>
@@ -5364,7 +5382,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -5385,16 +5403,16 @@
         <v>31</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -5483,7 +5501,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -5504,16 +5522,16 @@
         <v>31</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>43</v>
@@ -5602,7 +5620,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -5623,10 +5641,10 @@
         <v>33</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>43</v>
@@ -5715,7 +5733,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -5736,16 +5754,16 @@
         <v>27</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="M32" s="3" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>43</v>
@@ -5834,7 +5852,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -5855,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>44</v>
@@ -5944,7 +5962,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -5965,7 +5983,7 @@
         <v>30</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>44</v>
@@ -6054,7 +6072,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -6075,7 +6093,7 @@
         <v>15</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>44</v>
@@ -6164,7 +6182,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -6185,10 +6203,10 @@
         <v>25</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>44</v>
@@ -6277,7 +6295,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>46</v>
@@ -6301,13 +6319,13 @@
         <v>12</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>44</v>
@@ -6396,7 +6414,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -6417,7 +6435,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>44</v>
@@ -6506,7 +6524,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -6527,13 +6545,13 @@
         <v>25</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>44</v>
@@ -6622,7 +6640,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -6643,10 +6661,10 @@
         <v>35</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>44</v>
@@ -6735,7 +6753,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>46</v>
@@ -6759,10 +6777,10 @@
         <v>10</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>43</v>
@@ -6851,7 +6869,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>46</v>
@@ -6875,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>43</v>
@@ -6964,7 +6982,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>46</v>
@@ -6988,13 +7006,13 @@
         <v>10</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>71</v>
+        <v>199</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>43</v>
@@ -7083,7 +7101,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>62</v>
@@ -7107,16 +7125,16 @@
         <v>16</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>44</v>
@@ -7205,7 +7223,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>46</v>
@@ -7229,10 +7247,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>44</v>
@@ -7321,7 +7339,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>46</v>
@@ -7345,13 +7363,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>43</v>
@@ -7440,7 +7458,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>46</v>
@@ -7464,10 +7482,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>44</v>
@@ -7556,7 +7574,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>46</v>
@@ -7580,10 +7598,10 @@
         <v>10</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>44</v>
@@ -7672,7 +7690,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>46</v>
@@ -7696,10 +7714,10 @@
         <v>10</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>44</v>
@@ -7788,7 +7806,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>46</v>
@@ -7812,10 +7830,10 @@
         <v>10</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>43</v>
@@ -7904,7 +7922,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>62</v>
@@ -7928,10 +7946,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>44</v>
@@ -8020,7 +8038,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>46</v>
@@ -8044,13 +8062,13 @@
         <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>44</v>
@@ -8139,7 +8157,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>46</v>
@@ -8163,10 +8181,10 @@
         <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>43</v>
@@ -8255,7 +8273,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>46</v>
@@ -8279,10 +8297,10 @@
         <v>8</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>43</v>
@@ -8371,7 +8389,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>46</v>
@@ -8395,13 +8413,13 @@
         <v>10</v>
       </c>
       <c r="J55" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>44</v>
@@ -8490,7 +8508,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>62</v>
@@ -8514,13 +8532,13 @@
         <v>10</v>
       </c>
       <c r="J56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L56" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>44</v>
@@ -8609,7 +8627,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -8630,13 +8648,13 @@
         <v>34</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>43</v>
@@ -8725,7 +8743,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -8746,13 +8764,13 @@
         <v>34</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>43</v>
@@ -8841,7 +8859,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -8862,7 +8880,7 @@
         <v>15</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>43</v>
@@ -8951,7 +8969,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -8972,7 +8990,7 @@
         <v>15</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>44</v>
@@ -9061,7 +9079,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -9082,7 +9100,7 @@
         <v>15</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>43</v>
@@ -9171,7 +9189,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -9192,7 +9210,7 @@
         <v>15</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>44</v>
@@ -9281,7 +9299,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -9302,7 +9320,7 @@
         <v>15</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>44</v>
@@ -9391,7 +9409,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -9412,7 +9430,7 @@
         <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>44</v>
@@ -9501,7 +9519,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -9522,7 +9540,7 @@
         <v>15</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>43</v>
@@ -9611,7 +9629,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -9632,7 +9650,7 @@
         <v>15</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>43</v>
@@ -9721,7 +9739,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -9742,7 +9760,7 @@
         <v>15</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -9831,7 +9849,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -9852,7 +9870,7 @@
         <v>10</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>44</v>
@@ -9941,7 +9959,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -9962,7 +9980,7 @@
         <v>15</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>44</v>
@@ -10051,7 +10069,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -10072,7 +10090,7 @@
         <v>15</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>43</v>
@@ -10161,7 +10179,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -10182,7 +10200,7 @@
         <v>20</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>44</v>
@@ -10271,7 +10289,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -10292,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>44</v>
@@ -10381,7 +10399,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -10402,10 +10420,10 @@
         <v>15</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>43</v>
@@ -10494,7 +10512,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -10515,7 +10533,7 @@
         <v>15</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>43</v>
@@ -10604,7 +10622,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -10625,7 +10643,7 @@
         <v>15</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>43</v>
@@ -10848,13 +10866,13 @@
         <v>25</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>31</v>
@@ -10863,12 +10881,12 @@
         <v>33</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -10889,13 +10907,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -10954,7 +10972,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -10975,13 +10993,13 @@
         <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -11040,7 +11058,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -11061,16 +11079,16 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -11129,7 +11147,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>46</v>
@@ -11153,19 +11171,19 @@
         <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>43</v>
@@ -11224,7 +11242,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -11245,16 +11263,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>43</v>
@@ -11313,7 +11331,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>62</v>
@@ -11337,13 +11355,13 @@
         <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -11402,7 +11420,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -11423,10 +11441,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>43</v>
@@ -11515,7 +11533,7 @@
         <v>322</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>43</v>
@@ -11601,10 +11619,10 @@
         <v>325</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -11663,7 +11681,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -11684,16 +11702,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>140</v>
+        <v>330</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -11752,7 +11770,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>62</v>
@@ -11776,16 +11794,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>43</v>
@@ -11844,7 +11862,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -11865,16 +11883,16 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -11933,7 +11951,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -11954,16 +11972,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -12022,7 +12040,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -12043,22 +12061,22 @@
         <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -12117,7 +12135,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -12138,16 +12156,16 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -12206,7 +12224,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -12227,16 +12245,16 @@
         <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -12295,7 +12313,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -12316,13 +12334,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>95</v>
+        <v>360</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -12381,7 +12399,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -12402,16 +12420,16 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>43</v>
@@ -12470,7 +12488,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -12494,16 +12512,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>43</v>
@@ -12562,7 +12580,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -12583,16 +12601,16 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -12651,7 +12669,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -12672,16 +12690,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -12740,7 +12758,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -12761,16 +12779,16 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -12829,7 +12847,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -12850,16 +12868,16 @@
         <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -12918,7 +12936,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -12939,16 +12957,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -13007,7 +13025,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -13028,13 +13046,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -13093,7 +13111,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -13114,16 +13132,16 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>43</v>
@@ -13182,7 +13200,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -13203,19 +13221,19 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>396</v>
+        <v>129</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -13274,7 +13292,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -13295,16 +13313,16 @@
         <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>321</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -13476,16 +13494,16 @@
         <v>21</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>31</v>
@@ -13493,7 +13511,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -13514,16 +13532,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -13558,7 +13576,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -13579,13 +13597,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -13620,7 +13638,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>62</v>
@@ -13644,19 +13662,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -13691,7 +13709,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -13712,16 +13730,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>68</v>
+        <v>418</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>43</v>
@@ -13756,7 +13774,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -13777,16 +13795,16 @@
         <v>30</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>44</v>
@@ -13821,7 +13839,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -13842,16 +13860,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -13886,7 +13904,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>46</v>
@@ -13910,16 +13928,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -13954,7 +13972,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -13975,19 +13993,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>43</v>
@@ -14022,7 +14040,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>46</v>
@@ -14046,16 +14064,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -14090,7 +14108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>62</v>
@@ -14114,13 +14132,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>113</v>
+        <v>440</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -14155,7 +14173,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
@@ -14179,19 +14197,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>43</v>
@@ -14226,7 +14244,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -14247,19 +14265,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -14294,7 +14312,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -14315,19 +14333,19 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -14362,7 +14380,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -14383,16 +14401,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>455</v>
+        <v>157</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>44</v>
@@ -14427,7 +14445,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -14448,19 +14466,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -14495,7 +14513,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -14516,16 +14534,16 @@
         <v>35</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -14560,7 +14578,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -14581,16 +14599,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>44</v>
@@ -14625,7 +14643,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -14646,16 +14664,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -14690,7 +14708,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -14711,16 +14729,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -14755,7 +14773,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -14776,16 +14794,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>60</v>
+        <v>482</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>44</v>
@@ -14820,7 +14838,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -14841,16 +14859,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>44</v>
@@ -14885,7 +14903,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>46</v>
@@ -14909,19 +14927,19 @@
         <v>8</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="N23" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -14956,7 +14974,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -14977,13 +14995,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -15018,7 +15036,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -15039,16 +15057,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -15083,7 +15101,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -15104,13 +15122,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>44</v>
@@ -15145,7 +15163,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -15166,16 +15184,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -15210,7 +15228,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
@@ -15234,16 +15252,16 @@
         <v>16</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>44</v>
@@ -15379,16 +15397,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>21</v>
@@ -15405,7 +15423,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -15429,7 +15447,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -15461,7 +15479,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -15482,13 +15500,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -15520,7 +15538,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>46</v>
@@ -15544,16 +15562,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>44</v>
@@ -15585,7 +15603,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>62</v>
@@ -15609,16 +15627,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>44</v>
@@ -15650,7 +15668,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -15671,13 +15689,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>43</v>
@@ -15709,7 +15727,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -15730,16 +15748,16 @@
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -15771,7 +15789,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -15792,16 +15810,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -15833,7 +15851,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -15857,16 +15875,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>44</v>
@@ -15898,7 +15916,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -15919,16 +15937,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -15960,7 +15978,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -15981,19 +15999,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -16025,7 +16043,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -16046,16 +16064,16 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>44</v>
@@ -16087,7 +16105,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -16108,16 +16126,16 @@
         <v>37</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="M13" s="3" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -16149,7 +16167,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>62</v>
@@ -16173,13 +16191,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -16211,7 +16229,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -16235,16 +16253,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -16276,7 +16294,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -16297,19 +16315,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>44</v>
@@ -16341,7 +16359,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -16362,16 +16380,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -16403,7 +16421,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -16424,19 +16442,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -16468,7 +16486,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -16489,19 +16507,19 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -16533,7 +16551,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -16554,16 +16572,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -16595,7 +16613,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -16616,13 +16634,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -16654,7 +16672,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -16675,16 +16693,16 @@
         <v>31</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>123</v>
+        <v>587</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -16716,7 +16734,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -16737,13 +16755,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -16775,7 +16793,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -16796,7 +16814,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>44</v>
@@ -16828,7 +16846,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -16849,16 +16867,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>44</v>
@@ -16890,7 +16908,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -16911,13 +16929,13 @@
         <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -16949,7 +16967,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -16970,13 +16988,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -17008,7 +17026,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -17029,13 +17047,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -17067,7 +17085,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -17088,16 +17106,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -17129,7 +17147,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>46</v>
@@ -17153,16 +17171,16 @@
         <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>43</v>
@@ -17194,7 +17212,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -17215,13 +17233,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>150</v>
+        <v>619</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>43</v>
@@ -17253,7 +17271,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -17277,10 +17295,10 @@
         <v>324</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>43</v>
@@ -17312,7 +17330,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -17333,13 +17351,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>44</v>
@@ -17371,7 +17389,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -17392,13 +17410,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>44</v>
@@ -17430,7 +17448,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -17451,13 +17469,13 @@
         <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>43</v>
@@ -17489,7 +17507,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>46</v>
@@ -17513,16 +17531,16 @@
         <v>7</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>44</v>
@@ -17661,24 +17679,24 @@
         <v>18</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -17702,16 +17720,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>44</v>
@@ -17740,7 +17758,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -17761,13 +17779,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>70</v>
+        <v>644</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>44</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -603,7 +603,7 @@
     <t>normal_coal</t>
   </si>
   <si>
-    <t>coal: 100 [1]</t>
+    <t>lignite: 100 [1]</t>
   </si>
   <si>
     <t>normal_copper</t>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="647">
   <si>
     <t>Vein ID</t>
   </si>
@@ -603,7 +603,10 @@
     <t>normal_coal</t>
   </si>
   <si>
-    <t>lignite: 100 [1]</t>
+    <t>lignite: 70 [1]</t>
+  </si>
+  <si>
+    <t>coal: 30</t>
   </si>
   <si>
     <t>normal_copper</t>
@@ -6895,6 +6898,9 @@
       <c r="J42" s="3" t="s">
         <v>195</v>
       </c>
+      <c r="K42" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="P42" s="2" t="s">
         <v>43</v>
       </c>
@@ -6982,7 +6988,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>46</v>
@@ -7006,13 +7012,13 @@
         <v>10</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>43</v>
@@ -7101,7 +7107,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>62</v>
@@ -7125,16 +7131,16 @@
         <v>16</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>44</v>
@@ -7223,7 +7229,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>46</v>
@@ -7247,10 +7253,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>44</v>
@@ -7339,7 +7345,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>46</v>
@@ -7363,13 +7369,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>43</v>
@@ -7458,7 +7464,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>46</v>
@@ -7482,10 +7488,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>44</v>
@@ -7574,7 +7580,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>46</v>
@@ -7598,10 +7604,10 @@
         <v>10</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>44</v>
@@ -7690,7 +7696,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>46</v>
@@ -7714,10 +7720,10 @@
         <v>10</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>44</v>
@@ -7806,7 +7812,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>46</v>
@@ -7830,10 +7836,10 @@
         <v>10</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>43</v>
@@ -7922,7 +7928,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>62</v>
@@ -7946,10 +7952,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>44</v>
@@ -8038,7 +8044,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>46</v>
@@ -8062,13 +8068,13 @@
         <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>44</v>
@@ -8157,7 +8163,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>46</v>
@@ -8181,10 +8187,10 @@
         <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>43</v>
@@ -8273,7 +8279,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>46</v>
@@ -8297,10 +8303,10 @@
         <v>8</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>43</v>
@@ -8389,7 +8395,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>46</v>
@@ -8413,13 +8419,13 @@
         <v>10</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>44</v>
@@ -8508,7 +8514,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>62</v>
@@ -8532,13 +8538,13 @@
         <v>10</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>44</v>
@@ -8627,7 +8633,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -8648,13 +8654,13 @@
         <v>34</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>43</v>
@@ -8743,7 +8749,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -8764,13 +8770,13 @@
         <v>34</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>43</v>
@@ -8859,7 +8865,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -8880,7 +8886,7 @@
         <v>15</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>43</v>
@@ -8969,7 +8975,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -9079,7 +9085,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -9100,7 +9106,7 @@
         <v>15</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>43</v>
@@ -9189,7 +9195,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -9210,7 +9216,7 @@
         <v>15</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>44</v>
@@ -9299,7 +9305,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -9320,7 +9326,7 @@
         <v>15</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>44</v>
@@ -9409,7 +9415,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -9430,7 +9436,7 @@
         <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>44</v>
@@ -9519,7 +9525,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -9540,7 +9546,7 @@
         <v>15</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>43</v>
@@ -9629,7 +9635,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -9650,7 +9656,7 @@
         <v>15</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>43</v>
@@ -9739,7 +9745,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -9760,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -9849,7 +9855,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -9870,7 +9876,7 @@
         <v>10</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>44</v>
@@ -9959,7 +9965,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -9980,7 +9986,7 @@
         <v>15</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>44</v>
@@ -10069,7 +10075,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -10090,7 +10096,7 @@
         <v>15</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>43</v>
@@ -10179,7 +10185,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -10200,7 +10206,7 @@
         <v>20</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>44</v>
@@ -10289,7 +10295,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -10310,7 +10316,7 @@
         <v>15</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>44</v>
@@ -10399,7 +10405,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -10420,10 +10426,10 @@
         <v>15</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>43</v>
@@ -10512,7 +10518,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -10533,7 +10539,7 @@
         <v>15</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>43</v>
@@ -10622,7 +10628,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -10643,7 +10649,7 @@
         <v>15</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>43</v>
@@ -10866,13 +10872,13 @@
         <v>25</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>31</v>
@@ -10881,12 +10887,12 @@
         <v>33</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -10907,13 +10913,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -10972,7 +10978,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -10993,13 +10999,13 @@
         <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -11058,7 +11064,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -11079,16 +11085,16 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -11147,7 +11153,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>46</v>
@@ -11171,19 +11177,19 @@
         <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>43</v>
@@ -11242,7 +11248,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -11263,16 +11269,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>43</v>
@@ -11331,7 +11337,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>62</v>
@@ -11355,13 +11361,13 @@
         <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -11420,7 +11426,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -11441,10 +11447,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>43</v>
@@ -11503,7 +11509,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -11524,16 +11530,16 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>43</v>
@@ -11592,7 +11598,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -11613,16 +11619,16 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -11681,7 +11687,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -11702,16 +11708,16 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -11770,7 +11776,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>62</v>
@@ -11794,13 +11800,13 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>93</v>
@@ -11862,7 +11868,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -11883,16 +11889,16 @@
         <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -11951,7 +11957,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -11972,16 +11978,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -12040,7 +12046,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -12061,22 +12067,22 @@
         <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -12135,7 +12141,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -12156,16 +12162,16 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -12224,7 +12230,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -12245,16 +12251,16 @@
         <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -12313,7 +12319,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -12334,13 +12340,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -12399,7 +12405,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -12420,16 +12426,16 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>43</v>
@@ -12488,7 +12494,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -12512,16 +12518,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>43</v>
@@ -12580,7 +12586,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -12610,7 +12616,7 @@
         <v>188</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -12669,7 +12675,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -12690,16 +12696,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -12758,7 +12764,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -12779,16 +12785,16 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -12847,7 +12853,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -12868,16 +12874,16 @@
         <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -12936,7 +12942,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -12957,16 +12963,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>93</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -13025,7 +13031,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -13046,13 +13052,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -13111,7 +13117,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -13132,16 +13138,16 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>43</v>
@@ -13200,7 +13206,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -13221,16 +13227,16 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>129</v>
@@ -13292,7 +13298,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -13313,16 +13319,16 @@
         <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>188</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -13494,16 +13500,16 @@
         <v>21</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>31</v>
@@ -13511,7 +13517,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -13532,16 +13538,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -13576,7 +13582,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -13597,13 +13603,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -13638,7 +13644,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>62</v>
@@ -13662,19 +13668,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>43</v>
@@ -13709,7 +13715,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -13730,16 +13736,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>43</v>
@@ -13774,7 +13780,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -13795,16 +13801,16 @@
         <v>30</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>44</v>
@@ -13839,7 +13845,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -13860,16 +13866,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -13904,7 +13910,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>46</v>
@@ -13928,16 +13934,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -13972,7 +13978,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -13993,19 +13999,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>43</v>
@@ -14040,7 +14046,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>46</v>
@@ -14064,16 +14070,16 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -14108,7 +14114,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>62</v>
@@ -14132,13 +14138,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -14173,7 +14179,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
@@ -14197,19 +14203,19 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>43</v>
@@ -14244,7 +14250,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -14265,19 +14271,19 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -14312,7 +14318,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -14333,19 +14339,19 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -14380,7 +14386,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -14401,16 +14407,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>157</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>44</v>
@@ -14445,7 +14451,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -14466,19 +14472,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>43</v>
@@ -14513,7 +14519,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -14534,16 +14540,16 @@
         <v>35</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -14578,7 +14584,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -14599,16 +14605,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>44</v>
@@ -14643,7 +14649,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -14664,16 +14670,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -14708,7 +14714,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -14729,16 +14735,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -14773,7 +14779,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -14794,16 +14800,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>44</v>
@@ -14838,7 +14844,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -14859,16 +14865,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>44</v>
@@ -14903,7 +14909,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>46</v>
@@ -14927,19 +14933,19 @@
         <v>8</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -14974,7 +14980,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -14995,13 +15001,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>43</v>
@@ -15036,7 +15042,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -15057,16 +15063,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>43</v>
@@ -15101,7 +15107,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -15122,13 +15128,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>44</v>
@@ -15163,7 +15169,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -15184,16 +15190,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>188</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -15228,7 +15234,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
@@ -15252,16 +15258,16 @@
         <v>16</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>44</v>
@@ -15397,16 +15403,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>21</v>
@@ -15423,7 +15429,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -15447,7 +15453,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>43</v>
@@ -15479,7 +15485,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -15500,13 +15506,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>43</v>
@@ -15538,7 +15544,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>46</v>
@@ -15562,16 +15568,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>44</v>
@@ -15603,7 +15609,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>62</v>
@@ -15627,16 +15633,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>44</v>
@@ -15668,7 +15674,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -15689,13 +15695,13 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>43</v>
@@ -15727,7 +15733,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -15748,16 +15754,16 @@
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>44</v>
@@ -15789,7 +15795,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -15810,16 +15816,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
@@ -15851,7 +15857,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -15875,16 +15881,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>44</v>
@@ -15916,7 +15922,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -15937,16 +15943,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>43</v>
@@ -15978,7 +15984,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -15999,19 +16005,19 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>43</v>
@@ -16043,7 +16049,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -16064,16 +16070,16 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>44</v>
@@ -16105,7 +16111,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -16126,16 +16132,16 @@
         <v>37</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>43</v>
@@ -16167,7 +16173,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>62</v>
@@ -16191,13 +16197,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>43</v>
@@ -16229,7 +16235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -16253,16 +16259,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>43</v>
@@ -16294,7 +16300,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -16315,19 +16321,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>44</v>
@@ -16359,7 +16365,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -16380,16 +16386,16 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>43</v>
@@ -16421,7 +16427,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -16442,19 +16448,19 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>43</v>
@@ -16486,7 +16492,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -16507,19 +16513,19 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>44</v>
@@ -16551,7 +16557,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -16572,16 +16578,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>44</v>
@@ -16613,7 +16619,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -16634,13 +16640,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>43</v>
@@ -16672,7 +16678,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -16693,16 +16699,16 @@
         <v>31</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>43</v>
@@ -16734,7 +16740,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -16755,13 +16761,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>43</v>
@@ -16793,7 +16799,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -16814,7 +16820,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>44</v>
@@ -16846,7 +16852,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -16867,16 +16873,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>44</v>
@@ -16908,7 +16914,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -16929,13 +16935,13 @@
         <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -16967,7 +16973,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -16988,13 +16994,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>44</v>
@@ -17026,7 +17032,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -17047,13 +17053,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>43</v>
@@ -17085,7 +17091,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -17106,16 +17112,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>43</v>
@@ -17147,7 +17153,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>46</v>
@@ -17171,16 +17177,16 @@
         <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>43</v>
@@ -17212,7 +17218,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -17233,13 +17239,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>43</v>
@@ -17271,7 +17277,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -17292,13 +17298,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>43</v>
@@ -17330,7 +17336,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -17351,13 +17357,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>44</v>
@@ -17389,7 +17395,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -17410,13 +17416,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>44</v>
@@ -17448,7 +17454,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -17469,10 +17475,10 @@
         <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>188</v>
@@ -17507,7 +17513,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>46</v>
@@ -17531,16 +17537,16 @@
         <v>7</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>44</v>
@@ -17679,24 +17685,24 @@
         <v>18</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -17720,16 +17726,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>44</v>
@@ -17758,7 +17764,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -17779,13 +17785,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>44</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
   <si>
     <t>Materials</t>
   </si>
@@ -138,12 +138,24 @@
     <t>beneath_gold</t>
   </si>
   <si>
-    <t>gold 50 [1] / pyrite 40 / chalcopyrite 20</t>
+    <t>gold 50 [1] / pyrite 40 / chalcocite 20</t>
   </si>
   <si>
     <t>#tfg:nether/is_lush_hollow</t>
   </si>
   <si>
+    <t>beneath_phlogopite</t>
+  </si>
+  <si>
+    <t>phlogopite 15 [1] / sulfur 7 / apatite 3</t>
+  </si>
+  <si>
+    <t>26%</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_basalt_deltas</t>
+  </si>
+  <si>
     <t>beneath_phosphate</t>
   </si>
   <si>
@@ -225,7 +237,7 @@
     <t>beneath_copper_sulfide</t>
   </si>
   <si>
-    <t>chalcopyrite 12 [1] / pyrite 8 / bornite 4</t>
+    <t>chalcocite 12 [1] / pyrite 8 / bornite 4</t>
   </si>
   <si>
     <t>beneath_coal_lignite</t>
@@ -237,6 +249,18 @@
     <t>30%</t>
   </si>
   <si>
+    <t>beneath_psg</t>
+  </si>
+  <si>
+    <t>disc_vein</t>
+  </si>
+  <si>
+    <t>irarsite 30 [1] / ruarsite 28 / ferhodsite 22</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
     <t>beneath_realgar</t>
   </si>
   <si>
@@ -291,6 +315,15 @@
     <t>alunite 20 [1] / zeolite 12 / barite 8</t>
   </si>
   <si>
+    <t>beneath_bismuth</t>
+  </si>
+  <si>
+    <t>bismuth 20 [1] / sulfur 18 [1] / saltpeter 15</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
     <t>beneath_sulfur</t>
   </si>
   <si>
@@ -312,9 +345,6 @@
     <t>redstone 60 [1] / cinnabar 30 / nether_quartz 20 / ruby 10</t>
   </si>
   <si>
-    <t>#tfg:nether/is_basalt_deltas</t>
-  </si>
-  <si>
     <t>andesite</t>
   </si>
   <si>
@@ -336,9 +366,6 @@
     <t>venus_manual_salt</t>
   </si>
   <si>
-    <t>disc_vein</t>
-  </si>
-  <si>
     <t>salt 80 / rock_salt 10 / lepidolite 5 / spodumene 5</t>
   </si>
   <si>
@@ -585,9 +612,6 @@
     <t>basaltic_mineral_sand 8 / glauconite_sand 5 / garnet_sand 1</t>
   </si>
   <si>
-    <t>24%</t>
-  </si>
-  <si>
     <t>deep_graphite</t>
   </si>
   <si>
@@ -784,9 +808,6 @@
   </si>
   <si>
     <t>salt 60 [1] / rock_salt 30 / borax 10</t>
-  </si>
-  <si>
-    <t>26%</t>
   </si>
   <si>
     <t>#tfg:earth/is_shore_island</t>
@@ -1347,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.42856979370117" customWidth="1" style="4"/>
@@ -1709,46 +1730,46 @@
         <v>43</v>
       </c>
       <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
         <v>80</v>
-      </c>
-      <c r="E5" s="3">
-        <v>140</v>
       </c>
       <c r="G5" s="3">
         <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="I5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>34</v>
+      <c r="R5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>33</v>
@@ -1756,43 +1777,43 @@
       <c r="X5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>34</v>
+      <c r="Y5" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA5" s="1" t="s">
-        <v>34</v>
+      <c r="AA5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3">
+        <v>80</v>
+      </c>
+      <c r="E6" s="3">
         <v>140</v>
-      </c>
-      <c r="E6" s="3">
-        <v>190</v>
       </c>
       <c r="G6" s="3">
         <v>10</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -1809,26 +1830,26 @@
       <c r="S6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>33</v>
+      <c r="T6" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>34</v>
+      <c r="V6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z6" s="1" t="s">
-        <v>34</v>
+      <c r="Z6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>34</v>
@@ -1836,13 +1857,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3">
         <v>140</v>
@@ -1851,16 +1872,16 @@
         <v>190</v>
       </c>
       <c r="G7" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="I7" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>33</v>
@@ -1904,31 +1925,31 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E8" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G8" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -1945,26 +1966,26 @@
       <c r="S8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>34</v>
+      <c r="T8" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>33</v>
+      <c r="V8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z8" s="2" t="s">
-        <v>33</v>
+      <c r="Z8" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="AA8" s="1" t="s">
         <v>34</v>
@@ -1972,31 +1993,31 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" s="3">
+        <v>80</v>
+      </c>
+      <c r="E9" s="3">
         <v>140</v>
-      </c>
-      <c r="E9" s="3">
-        <v>190</v>
       </c>
       <c r="G9" s="3">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I9" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>33</v>
@@ -2013,26 +2034,26 @@
       <c r="S9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>33</v>
+      <c r="T9" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>34</v>
+      <c r="V9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z9" s="1" t="s">
-        <v>34</v>
+      <c r="Z9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="AA9" s="1" t="s">
         <v>34</v>
@@ -2040,31 +2061,31 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E10" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G10" s="3">
         <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I10" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>33</v>
@@ -2081,26 +2102,26 @@
       <c r="S10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>34</v>
+      <c r="T10" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="U10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>33</v>
+      <c r="V10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>33</v>
+      <c r="Z10" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="AA10" s="1" t="s">
         <v>34</v>
@@ -2108,10 +2129,10 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>61</v>
@@ -2126,13 +2147,10 @@
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="3">
-        <v>60</v>
-      </c>
-      <c r="K11" s="3">
-        <v>8</v>
+        <v>37</v>
+      </c>
+      <c r="I11" s="3">
+        <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>62</v>
@@ -2182,55 +2200,55 @@
         <v>63</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G12" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J12" s="3">
         <v>60</v>
       </c>
       <c r="K12" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>33</v>
+      <c r="R12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>33</v>
@@ -2238,34 +2256,34 @@
       <c r="X12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y12" s="2" t="s">
-        <v>33</v>
+      <c r="Y12" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA12" s="2" t="s">
-        <v>33</v>
+      <c r="AA12" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
         <v>80</v>
       </c>
-      <c r="E13" s="3">
-        <v>140</v>
-      </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>37</v>
@@ -2274,34 +2292,34 @@
         <v>60</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>34</v>
+      <c r="R13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>33</v>
@@ -2309,25 +2327,25 @@
       <c r="X13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>34</v>
+      <c r="Y13" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA13" s="1" t="s">
-        <v>34</v>
+      <c r="AA13" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" s="3">
         <v>80</v>
@@ -2339,10 +2357,13 @@
         <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="3">
-        <v>27</v>
+        <v>37</v>
+      </c>
+      <c r="J14" s="3">
+        <v>60</v>
+      </c>
+      <c r="K14" s="3">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>62</v>
@@ -2389,31 +2410,31 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D15" s="3">
+        <v>80</v>
+      </c>
+      <c r="E15" s="3">
         <v>140</v>
-      </c>
-      <c r="E15" s="3">
-        <v>190</v>
       </c>
       <c r="G15" s="3">
         <v>10</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I15" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -2430,26 +2451,26 @@
       <c r="S15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>33</v>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>34</v>
+      <c r="V15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>34</v>
+      <c r="Z15" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="AA15" s="1" t="s">
         <v>34</v>
@@ -2457,31 +2478,31 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G16" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="I16" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -2498,26 +2519,26 @@
       <c r="S16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>34</v>
+      <c r="T16" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>33</v>
+      <c r="V16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z16" s="2" t="s">
-        <v>33</v>
+      <c r="Z16" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>34</v>
@@ -2525,58 +2546,58 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
         <v>80</v>
       </c>
-      <c r="E17" s="3">
-        <v>140</v>
-      </c>
       <c r="G17" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>37</v>
+        <v>80</v>
+      </c>
+      <c r="I17" s="3">
+        <v>30</v>
       </c>
       <c r="J17" s="3">
-        <v>60</v>
-      </c>
-      <c r="K17" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>34</v>
+      <c r="R17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>33</v>
@@ -2584,25 +2605,25 @@
       <c r="X17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y17" s="1" t="s">
-        <v>34</v>
+      <c r="Y17" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA17" s="1" t="s">
-        <v>34</v>
+      <c r="AA17" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D18" s="3">
         <v>80</v>
@@ -2611,16 +2632,16 @@
         <v>140</v>
       </c>
       <c r="G18" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>33</v>
@@ -2664,55 +2685,58 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="3">
         <v>80</v>
       </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
       <c r="E19" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G19" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" s="3">
-        <v>23</v>
+        <v>37</v>
+      </c>
+      <c r="J19" s="3">
+        <v>60</v>
+      </c>
+      <c r="K19" s="3">
+        <v>15</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>33</v>
+      <c r="R19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>33</v>
@@ -2720,43 +2744,43 @@
       <c r="X19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y19" s="2" t="s">
-        <v>33</v>
+      <c r="Y19" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA19" s="2" t="s">
-        <v>33</v>
+      <c r="AA19" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D20" s="3">
+        <v>80</v>
+      </c>
+      <c r="E20" s="3">
         <v>140</v>
       </c>
-      <c r="E20" s="3">
-        <v>190</v>
-      </c>
       <c r="G20" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I20" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>33</v>
@@ -2773,26 +2797,26 @@
       <c r="S20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>33</v>
+      <c r="T20" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="U20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>34</v>
+      <c r="V20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z20" s="1" t="s">
-        <v>34</v>
+      <c r="Z20" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="AA20" s="1" t="s">
         <v>34</v>
@@ -2800,102 +2824,99 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D21" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="G21" s="3">
         <v>10</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="3">
-        <v>60</v>
-      </c>
-      <c r="K21" s="3">
-        <v>10</v>
+        <v>89</v>
+      </c>
+      <c r="I21" s="3">
+        <v>23</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>34</v>
+      <c r="R21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>34</v>
+      <c r="U21" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="V21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>34</v>
+      <c r="W21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E22" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G22" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="I22" s="3">
         <v>27</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -2912,26 +2933,26 @@
       <c r="S22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T22" s="1" t="s">
-        <v>34</v>
+      <c r="T22" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>33</v>
+      <c r="V22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z22" s="2" t="s">
-        <v>33</v>
+      <c r="Z22" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="AA22" s="1" t="s">
         <v>34</v>
@@ -2939,25 +2960,25 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D23" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E23" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G23" s="3">
         <v>10</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J23" s="3">
         <v>60</v>
@@ -2966,7 +2987,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>33</v>
@@ -2983,26 +3004,26 @@
       <c r="S23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T23" s="1" t="s">
-        <v>34</v>
+      <c r="T23" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="U23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>33</v>
+      <c r="V23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Y23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z23" s="2" t="s">
-        <v>33</v>
+      <c r="Z23" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="AA23" s="1" t="s">
         <v>34</v>
@@ -3010,55 +3031,55 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G24" s="3">
         <v>10</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I24" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>33</v>
+      <c r="R24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="W24" s="2" t="s">
         <v>33</v>
@@ -3066,43 +3087,46 @@
       <c r="X24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Y24" s="2" t="s">
-        <v>33</v>
+      <c r="Y24" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA24" s="2" t="s">
-        <v>33</v>
+      <c r="AA24" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D25" s="3">
+        <v>80</v>
+      </c>
+      <c r="E25" s="3">
         <v>140</v>
-      </c>
-      <c r="E25" s="3">
-        <v>190</v>
       </c>
       <c r="G25" s="3">
         <v>10</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="J25" s="3">
+        <v>60</v>
+      </c>
+      <c r="K25" s="3">
+        <v>10</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -3119,26 +3143,26 @@
       <c r="S25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>33</v>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="U25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>34</v>
+      <c r="V25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="Y25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z25" s="1" t="s">
-        <v>34</v>
+      <c r="Z25" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="AA25" s="1" t="s">
         <v>34</v>
@@ -3146,13 +3170,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
@@ -3164,54 +3188,261 @@
         <v>10</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="J26" s="3">
         <v>60</v>
       </c>
       <c r="K26" s="3">
+        <v>15</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>80</v>
+      </c>
+      <c r="G27" s="3">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="3">
+        <v>140</v>
+      </c>
+      <c r="E28" s="3">
+        <v>190</v>
+      </c>
+      <c r="G28" s="3">
+        <v>10</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3">
+        <v>25</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>80</v>
+      </c>
+      <c r="G29" s="3">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="3">
+        <v>60</v>
+      </c>
+      <c r="K29" s="3">
         <v>12</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA26" s="2" t="s">
+      <c r="M29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA29" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3330,39 +3561,39 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D2" s="3">
         <v>40</v>
@@ -3374,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I2" s="3">
         <v>20</v>
@@ -3383,7 +3614,7 @@
         <v>6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>34</v>
@@ -3412,13 +3643,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D3" s="3">
         <v>40</v>
@@ -3430,13 +3661,13 @@
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3">
         <v>20</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>34</v>
@@ -3578,13 +3809,13 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>18</v>
@@ -3593,30 +3824,30 @@
         <v>20</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="W1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -3634,7 +3865,7 @@
         <v>35</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -3669,13 +3900,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -3687,7 +3918,7 @@
         <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3">
         <v>35</v>
@@ -3696,7 +3927,7 @@
         <v>10</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -3731,13 +3962,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
@@ -3749,13 +3980,13 @@
         <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I4" s="3">
         <v>35</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>34</v>
@@ -3790,13 +4021,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>
@@ -3808,13 +4039,13 @@
         <v>215</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I5" s="3">
         <v>30</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>34</v>
@@ -3849,13 +4080,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D6" s="3">
         <v>10</v>
@@ -3867,13 +4098,13 @@
         <v>210</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I6" s="3">
         <v>35</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -3908,13 +4139,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
@@ -3926,13 +4157,13 @@
         <v>230</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I7" s="3">
         <v>30</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>34</v>
@@ -3967,13 +4198,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -3991,7 +4222,7 @@
         <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -4026,13 +4257,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D9" s="3">
         <v>20</v>
@@ -4044,13 +4275,13 @@
         <v>250</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I9" s="3">
         <v>35</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>34</v>
@@ -4085,13 +4316,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D10" s="3">
         <v>50</v>
@@ -4103,13 +4334,13 @@
         <v>190</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I10" s="3">
         <v>35</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>34</v>
@@ -4144,13 +4375,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -4162,13 +4393,13 @@
         <v>210</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3">
         <v>30</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>34</v>
@@ -4203,13 +4434,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -4221,13 +4452,13 @@
         <v>200</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I12" s="3">
         <v>40</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -4262,13 +4493,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -4280,13 +4511,13 @@
         <v>245</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I13" s="3">
         <v>35</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -4321,13 +4552,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -4339,13 +4570,13 @@
         <v>200</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I14" s="3">
         <v>20</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -4380,13 +4611,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D15" s="3">
         <v>20</v>
@@ -4398,13 +4629,13 @@
         <v>210</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I15" s="3">
         <v>30</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -4439,13 +4670,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -4457,7 +4688,7 @@
         <v>260</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J16" s="3">
         <v>60</v>
@@ -4466,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -4501,13 +4732,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D17" s="3">
         <v>10</v>
@@ -4519,13 +4750,13 @@
         <v>230</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I17" s="3">
         <v>45</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>34</v>
@@ -4560,13 +4791,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -4578,7 +4809,7 @@
         <v>210</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I18" s="3">
         <v>45</v>
@@ -4587,7 +4818,7 @@
         <v>16</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>34</v>
@@ -4622,13 +4853,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D19" s="3">
         <v>20</v>
@@ -4646,7 +4877,7 @@
         <v>35</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>34</v>
@@ -4681,13 +4912,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D20" s="3">
         <v>10</v>
@@ -4699,7 +4930,7 @@
         <v>230</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I20" s="3">
         <v>35</v>
@@ -4708,7 +4939,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>34</v>
@@ -4743,13 +4974,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D21" s="3">
         <v>5</v>
@@ -4761,13 +4992,13 @@
         <v>250</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I21" s="3">
         <v>45</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>33</v>
@@ -4802,13 +5033,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -4820,7 +5051,7 @@
         <v>260</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3">
         <v>70</v>
@@ -4829,7 +5060,7 @@
         <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -4864,13 +5095,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -4882,13 +5113,13 @@
         <v>260</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I23" s="3">
         <v>30</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>34</v>
@@ -4923,13 +5154,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -4941,7 +5172,7 @@
         <v>280</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I24" s="3">
         <v>28</v>
@@ -4950,7 +5181,7 @@
         <v>8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -4985,13 +5216,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
@@ -5003,13 +5234,13 @@
         <v>310</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I25" s="3">
         <v>40</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>34</v>
@@ -5044,13 +5275,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D26" s="3">
         <v>10</v>
@@ -5062,7 +5293,7 @@
         <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I26" s="3">
         <v>30</v>
@@ -5071,7 +5302,7 @@
         <v>9</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>33</v>
@@ -5106,13 +5337,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -5124,13 +5355,13 @@
         <v>250</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I27" s="3">
         <v>35</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>33</v>
@@ -5165,13 +5396,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -5189,7 +5420,7 @@
         <v>30</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>33</v>
@@ -5337,37 +5568,37 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AA1" s="5" t="s">
         <v>20</v>
@@ -5379,10 +5610,10 @@
         <v>22</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>23</v>
@@ -5391,22 +5622,22 @@
         <v>24</v>
       </c>
       <c r="AH1" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AL1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>26</v>
@@ -5415,21 +5646,21 @@
         <v>27</v>
       </c>
       <c r="AP1" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="AQ1" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D2" s="3">
         <v>-50</v>
@@ -5441,7 +5672,7 @@
         <v>130</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J2" s="3">
         <v>60</v>
@@ -5450,7 +5681,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -5539,13 +5770,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D3" s="3">
         <v>-5</v>
@@ -5560,13 +5791,13 @@
         <v>190</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="I3" s="3">
         <v>34</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -5655,13 +5886,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D4" s="3">
         <v>-64</v>
@@ -5673,7 +5904,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I4" s="3">
         <v>16</v>
@@ -5682,7 +5913,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>34</v>
@@ -5771,13 +6002,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D5" s="3">
         <v>-30</v>
@@ -5789,7 +6020,7 @@
         <v>190</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J5" s="3">
         <v>35</v>
@@ -5798,7 +6029,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>34</v>
@@ -5887,13 +6118,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D6" s="3">
         <v>-50</v>
@@ -5905,13 +6136,13 @@
         <v>210</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I6" s="3">
         <v>33</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -6000,13 +6231,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D7" s="3">
         <v>-50</v>
@@ -6018,13 +6249,13 @@
         <v>230</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="I7" s="3">
         <v>24</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>33</v>
@@ -6113,13 +6344,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D8" s="3">
         <v>10</v>
@@ -6131,7 +6362,7 @@
         <v>150</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I8" s="3">
         <v>18</v>
@@ -6140,7 +6371,7 @@
         <v>10</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -6229,13 +6460,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3">
         <v>-50</v>
@@ -6247,13 +6478,13 @@
         <v>420</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I9" s="3">
         <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>33</v>
@@ -6342,13 +6573,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D10" s="3">
         <v>-50</v>
@@ -6360,13 +6591,13 @@
         <v>210</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I10" s="3">
         <v>42</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>34</v>
@@ -6455,13 +6686,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
@@ -6473,7 +6704,7 @@
         <v>130</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3">
         <v>20</v>
@@ -6482,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>33</v>
@@ -6571,13 +6802,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D12" s="3">
         <v>-50</v>
@@ -6589,13 +6820,13 @@
         <v>270</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="I12" s="3">
         <v>31</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -6684,13 +6915,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D13" s="3">
         <v>-5</v>
@@ -6705,13 +6936,13 @@
         <v>270</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I13" s="3">
         <v>15</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -6800,13 +7031,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D14" s="3">
         <v>10</v>
@@ -6818,7 +7049,7 @@
         <v>230</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I14" s="3">
         <v>34</v>
@@ -6827,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -6916,13 +7147,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D15" s="3">
         <v>-30</v>
@@ -6937,13 +7168,13 @@
         <v>60</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3">
         <v>25</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>34</v>
@@ -7032,13 +7263,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D16" s="3">
         <v>-20</v>
@@ -7053,13 +7284,13 @@
         <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I16" s="3">
         <v>10</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>34</v>
@@ -7148,13 +7379,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D17" s="3">
         <v>-50</v>
@@ -7166,13 +7397,13 @@
         <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I17" s="3">
         <v>39</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>33</v>
@@ -7261,13 +7492,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D18" s="3">
         <v>-30</v>
@@ -7288,7 +7519,7 @@
         <v>25</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>34</v>
@@ -7377,13 +7608,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D19" s="3">
         <v>-20</v>
@@ -7404,7 +7635,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>34</v>
@@ -7493,13 +7724,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D20" s="3">
         <v>-20</v>
@@ -7520,7 +7751,7 @@
         <v>15</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>34</v>
@@ -7609,13 +7840,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D21" s="3">
         <v>-50</v>
@@ -7630,13 +7861,13 @@
         <v>50</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I21" s="3">
         <v>35</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>34</v>
@@ -7725,13 +7956,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D22" s="3">
         <v>-20</v>
@@ -7746,13 +7977,13 @@
         <v>80</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I22" s="3">
         <v>20</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>34</v>
@@ -7841,13 +8072,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D23" s="3">
         <v>90</v>
@@ -7859,13 +8090,13 @@
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I23" s="3">
         <v>30</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>34</v>
@@ -7954,13 +8185,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D24" s="3">
         <v>-50</v>
@@ -7981,7 +8212,7 @@
         <v>10</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -8070,13 +8301,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D25" s="3">
         <v>10</v>
@@ -8088,7 +8319,7 @@
         <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I25" s="3">
         <v>30</v>
@@ -8097,7 +8328,7 @@
         <v>10</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -8186,13 +8417,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D26" s="3">
         <v>-30</v>
@@ -8213,7 +8444,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>34</v>
@@ -8302,13 +8533,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D27" s="3">
         <v>-30</v>
@@ -8332,7 +8563,7 @@
         <v>12</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>34</v>
@@ -8421,13 +8652,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D28" s="3">
         <v>-20</v>
@@ -8442,13 +8673,13 @@
         <v>70</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I28" s="3">
         <v>15</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>34</v>
@@ -8537,13 +8768,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D29" s="3">
         <v>10</v>
@@ -8555,7 +8786,7 @@
         <v>150</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="I29" s="3">
         <v>23</v>
@@ -8564,7 +8795,7 @@
         <v>10</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>34</v>
@@ -8653,13 +8884,13 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D30" s="3">
         <v>-20</v>
@@ -8674,13 +8905,13 @@
         <v>80</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I30" s="3">
         <v>15</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>33</v>
@@ -8769,13 +9000,13 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -8787,7 +9018,7 @@
         <v>190</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>256</v>
+        <v>44</v>
       </c>
       <c r="I31" s="3">
         <v>25</v>
@@ -8796,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>34</v>
@@ -8885,13 +9116,13 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D32" s="3">
         <v>-50</v>
@@ -8909,7 +9140,7 @@
         <v>27</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>33</v>
@@ -8998,13 +9229,13 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D33" s="3">
         <v>10</v>
@@ -9016,7 +9247,7 @@
         <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I33" s="3">
         <v>21</v>
@@ -9025,7 +9256,7 @@
         <v>10</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>33</v>
@@ -9114,13 +9345,13 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D34" s="3">
         <v>-5</v>
@@ -9135,13 +9366,13 @@
         <v>190</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="I34" s="3">
         <v>34</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>33</v>
@@ -9230,13 +9461,13 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
@@ -9248,7 +9479,7 @@
         <v>150</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I35" s="3">
         <v>32</v>
@@ -9257,7 +9488,7 @@
         <v>10</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>34</v>
@@ -9346,13 +9577,13 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D36" s="3">
         <v>-60</v>
@@ -9364,7 +9595,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I36" s="3">
         <v>27</v>
@@ -9376,7 +9607,7 @@
         <v>34</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>33</v>
@@ -9465,13 +9696,13 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D37" s="3">
         <v>100</v>
@@ -9483,13 +9714,13 @@
         <v>30</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="I37" s="3">
         <v>15</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>34</v>
@@ -9578,13 +9809,13 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D38" s="3">
         <v>-30</v>
@@ -9596,7 +9827,7 @@
         <v>190</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J38" s="3">
         <v>30</v>
@@ -9605,7 +9836,7 @@
         <v>5</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>34</v>
@@ -9694,13 +9925,13 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D39" s="3">
         <v>-50</v>
@@ -9712,7 +9943,7 @@
         <v>140</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="J39" s="3">
         <v>150</v>
@@ -9721,7 +9952,7 @@
         <v>18</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>33</v>
@@ -9810,13 +10041,13 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D40" s="3">
         <v>-20</v>
@@ -9837,7 +10068,7 @@
         <v>15</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>33</v>
@@ -9926,13 +10157,13 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D41" s="3">
         <v>-50</v>
@@ -9944,7 +10175,7 @@
         <v>190</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3">
         <v>35</v>
@@ -9953,7 +10184,7 @@
         <v>5</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>33</v>
@@ -10042,13 +10273,13 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D42" s="3">
         <v>-50</v>
@@ -10066,7 +10297,7 @@
         <v>45</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>34</v>
@@ -10155,13 +10386,13 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D43" s="3">
         <v>10</v>
@@ -10173,7 +10404,7 @@
         <v>220</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I43" s="3">
         <v>20</v>
@@ -10182,7 +10413,7 @@
         <v>8</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>33</v>
@@ -10271,13 +10502,13 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D44" s="3">
         <v>90</v>
@@ -10289,13 +10520,13 @@
         <v>40</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I44" s="3">
         <v>15</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>34</v>
@@ -10384,13 +10615,13 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D45" s="3">
         <v>-50</v>
@@ -10402,13 +10633,13 @@
         <v>190</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I45" s="3">
         <v>37</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>33</v>
@@ -10497,13 +10728,13 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D46" s="3">
         <v>-60</v>
@@ -10515,7 +10746,7 @@
         <v>34</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="I46" s="3">
         <v>35</v>
@@ -10527,7 +10758,7 @@
         <v>34</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>34</v>
@@ -10616,13 +10847,13 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D47" s="3">
         <v>-50</v>
@@ -10640,7 +10871,7 @@
         <v>32</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>33</v>
@@ -10729,13 +10960,13 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D48" s="3">
         <v>-50</v>
@@ -10753,7 +10984,7 @@
         <v>38</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>33</v>
@@ -10842,13 +11073,13 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D49" s="3">
         <v>-50</v>
@@ -10860,7 +11091,7 @@
         <v>270</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="I49" s="3">
         <v>42</v>
@@ -10869,7 +11100,7 @@
         <v>5</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>33</v>
@@ -10958,13 +11189,13 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D50" s="3">
         <v>-50</v>
@@ -10976,13 +11207,13 @@
         <v>180</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I50" s="3">
         <v>28</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>33</v>
@@ -11071,13 +11302,13 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D51" s="3">
         <v>-20</v>
@@ -11092,13 +11323,13 @@
         <v>120</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3">
         <v>15</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>34</v>
@@ -11187,13 +11418,13 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D52" s="3">
         <v>-50</v>
@@ -11205,13 +11436,13 @@
         <v>420</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I52" s="3">
         <v>25</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>33</v>
@@ -11300,13 +11531,13 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D53" s="3">
         <v>10</v>
@@ -11318,7 +11549,7 @@
         <v>130</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I53" s="3">
         <v>24</v>
@@ -11327,7 +11558,7 @@
         <v>10</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>34</v>
@@ -11416,13 +11647,13 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D54" s="3">
         <v>10</v>
@@ -11434,7 +11665,7 @@
         <v>140</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I54" s="3">
         <v>24</v>
@@ -11443,7 +11674,7 @@
         <v>10</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>34</v>
@@ -11532,13 +11763,13 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D55" s="3">
         <v>-20</v>
@@ -11553,13 +11784,13 @@
         <v>75</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I55" s="3">
         <v>15</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>34</v>
@@ -11648,13 +11879,13 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D56" s="3">
         <v>-20</v>
@@ -11669,13 +11900,13 @@
         <v>70</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I56" s="3">
         <v>15</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>33</v>
@@ -11764,13 +11995,13 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D57" s="3">
         <v>-50</v>
@@ -11782,13 +12013,13 @@
         <v>230</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="I57" s="3">
         <v>27</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>33</v>
@@ -11877,13 +12108,13 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D58" s="3">
         <v>10</v>
@@ -11895,7 +12126,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I58" s="3">
         <v>21</v>
@@ -11904,7 +12135,7 @@
         <v>10</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>34</v>
@@ -11993,13 +12224,13 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D59" s="3">
         <v>-50</v>
@@ -12011,7 +12242,7 @@
         <v>140</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J59" s="3">
         <v>60</v>
@@ -12020,7 +12251,7 @@
         <v>10</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>33</v>
@@ -12109,13 +12340,13 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D60" s="3">
         <v>-50</v>
@@ -12127,13 +12358,13 @@
         <v>160</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I60" s="3">
         <v>37</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>34</v>
@@ -12222,13 +12453,13 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D61" s="3">
         <v>-20</v>
@@ -12243,13 +12474,13 @@
         <v>90</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="I61" s="3">
         <v>15</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>33</v>
@@ -12338,13 +12569,13 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D62" s="3">
         <v>-50</v>
@@ -12362,7 +12593,7 @@
         <v>37</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>33</v>
@@ -12451,13 +12682,13 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D63" s="3">
         <v>10</v>
@@ -12469,7 +12700,7 @@
         <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I63" s="3">
         <v>25</v>
@@ -12478,7 +12709,7 @@
         <v>10</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>33</v>
@@ -12567,13 +12798,13 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D64" s="3">
         <v>-50</v>
@@ -12585,13 +12816,13 @@
         <v>290</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I64" s="3">
         <v>31</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>33</v>
@@ -12680,13 +12911,13 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D65" s="3">
         <v>-20</v>
@@ -12701,13 +12932,13 @@
         <v>90</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I65" s="3">
         <v>15</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>33</v>
@@ -12796,13 +13027,13 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D66" s="3">
         <v>10</v>
@@ -12814,7 +13045,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J66" s="3">
         <v>60</v>
@@ -12823,10 +13054,10 @@
         <v>10</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>34</v>
@@ -12915,13 +13146,13 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D67" s="3">
         <v>-50</v>
@@ -12933,13 +13164,13 @@
         <v>280</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I67" s="3">
         <v>45</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>33</v>
@@ -13028,13 +13259,13 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D68" s="3">
         <v>-20</v>
@@ -13055,7 +13286,7 @@
         <v>15</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>33</v>
@@ -13144,13 +13375,13 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D69" s="3">
         <v>-20</v>
@@ -13165,13 +13396,13 @@
         <v>90</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I69" s="3">
         <v>15</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>33</v>
@@ -13260,13 +13491,13 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D70" s="3">
         <v>-50</v>
@@ -13284,7 +13515,7 @@
         <v>35</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>33</v>
@@ -13373,13 +13604,13 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D71" s="3">
         <v>-20</v>
@@ -13394,13 +13625,13 @@
         <v>70</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I71" s="3">
         <v>15</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>33</v>
@@ -13489,13 +13720,13 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D72" s="3">
         <v>-50</v>
@@ -13507,13 +13738,13 @@
         <v>160</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I72" s="3">
         <v>37</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>33</v>
@@ -13602,13 +13833,13 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D73" s="3">
         <v>-50</v>
@@ -13620,13 +13851,13 @@
         <v>160</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="I73" s="3">
         <v>41</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>34</v>
@@ -13715,13 +13946,13 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D74" s="3">
         <v>-50</v>
@@ -13739,7 +13970,7 @@
         <v>29</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>33</v>
@@ -13828,13 +14059,13 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D75" s="3">
         <v>-30</v>
@@ -13855,7 +14086,7 @@
         <v>15</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>34</v>
@@ -14057,31 +14288,31 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>20</v>
@@ -14090,36 +14321,36 @@
         <v>22</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -14131,13 +14362,13 @@
         <v>220</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="I2" s="3">
         <v>20</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -14196,13 +14427,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -14214,13 +14445,13 @@
         <v>280</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="I3" s="3">
         <v>50</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -14279,13 +14510,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -14297,13 +14528,13 @@
         <v>215</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="I4" s="3">
         <v>55</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>33</v>
@@ -14362,13 +14593,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D5" s="3">
         <v>80</v>
@@ -14386,7 +14617,7 @@
         <v>45</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>33</v>
@@ -14445,13 +14676,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -14463,7 +14694,7 @@
         <v>280</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I6" s="3">
         <v>65</v>
@@ -14472,7 +14703,7 @@
         <v>8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -14531,13 +14762,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D7" s="3">
         <v>80</v>
@@ -14555,7 +14786,7 @@
         <v>45</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>33</v>
@@ -14614,13 +14845,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D8" s="3">
         <v>-20</v>
@@ -14632,7 +14863,7 @@
         <v>350</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J8" s="3">
         <v>40</v>
@@ -14641,7 +14872,7 @@
         <v>8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>34</v>
@@ -14700,13 +14931,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -14718,13 +14949,13 @@
         <v>215</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I9" s="3">
         <v>45</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>33</v>
@@ -14783,13 +15014,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
@@ -14801,13 +15032,13 @@
         <v>215</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I10" s="3">
         <v>45</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>33</v>
@@ -14866,13 +15097,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -14884,7 +15115,7 @@
         <v>210</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I11" s="3">
         <v>40</v>
@@ -14893,7 +15124,7 @@
         <v>6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>33</v>
@@ -14952,13 +15183,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -14976,7 +15207,7 @@
         <v>40</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -15035,13 +15266,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -15059,7 +15290,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -15118,13 +15349,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -15136,13 +15367,13 @@
         <v>210</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I14" s="3">
         <v>40</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -15201,13 +15432,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D15" s="3">
         <v>-30</v>
@@ -15219,13 +15450,13 @@
         <v>370</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I15" s="3">
         <v>60</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -15284,13 +15515,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -15302,7 +15533,7 @@
         <v>220</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J16" s="3">
         <v>60</v>
@@ -15311,7 +15542,7 @@
         <v>9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -15370,13 +15601,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -15388,13 +15619,13 @@
         <v>230</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I17" s="3">
         <v>42</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>33</v>
@@ -15453,13 +15684,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -15477,7 +15708,7 @@
         <v>30</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>33</v>
@@ -15536,13 +15767,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D19" s="3">
         <v>0</v>
@@ -15554,13 +15785,13 @@
         <v>210</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I19" s="3">
         <v>40</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>33</v>
@@ -15619,13 +15850,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
@@ -15637,13 +15868,13 @@
         <v>215</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I20" s="3">
         <v>50</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>33</v>
@@ -15702,13 +15933,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D21" s="3">
         <v>80</v>
@@ -15726,7 +15957,7 @@
         <v>45</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>33</v>
@@ -15785,13 +16016,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D22" s="3">
         <v>80</v>
@@ -15809,7 +16040,7 @@
         <v>45</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -15868,13 +16099,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D23" s="3">
         <v>-30</v>
@@ -15886,13 +16117,13 @@
         <v>370</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I23" s="3">
         <v>60</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>33</v>
@@ -15951,13 +16182,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -15969,13 +16200,13 @@
         <v>230</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I24" s="3">
         <v>40</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -16034,13 +16265,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D25" s="3">
         <v>-30</v>
@@ -16052,13 +16283,13 @@
         <v>370</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I25" s="3">
         <v>60</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -16117,13 +16348,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D26" s="3">
         <v>80</v>
@@ -16141,7 +16372,7 @@
         <v>45</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>33</v>
@@ -16200,13 +16431,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -16218,13 +16449,13 @@
         <v>220</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3">
         <v>50</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>33</v>
@@ -16283,13 +16514,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -16301,13 +16532,13 @@
         <v>210</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3">
         <v>40</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>33</v>
@@ -16366,13 +16597,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -16384,13 +16615,13 @@
         <v>250</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I29" s="3">
         <v>55</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>33</v>
